--- a/data/england/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/england/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP244"/>
+  <dimension ref="A1:BP255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53747,6 +53747,2240 @@
         <v>212</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="n">
+        <v>45514.45833333334</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wembley stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F245" t="n">
+        <v>78146</v>
+      </c>
+      <c r="G245" t="n">
+        <v>2</v>
+      </c>
+      <c r="H245" t="n">
+        <v>1</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="K245" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L245" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M245" t="n">
+        <v>59</v>
+      </c>
+      <c r="N245" t="n">
+        <v>41</v>
+      </c>
+      <c r="O245" t="n">
+        <v>8</v>
+      </c>
+      <c r="P245" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>1</v>
+      </c>
+      <c r="R245" t="n">
+        <v>2</v>
+      </c>
+      <c r="S245" t="n">
+        <v>10</v>
+      </c>
+      <c r="T245" t="n">
+        <v>7</v>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="W245" t="n">
+        <v>48</v>
+      </c>
+      <c r="X245" t="n">
+        <v>482</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA245" t="inlineStr"/>
+      <c r="AB245" t="inlineStr"/>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="AE245" t="n">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="AF245" t="n">
+        <v>182.5454545454545</v>
+      </c>
+      <c r="AG245" t="n">
+        <v>2.454545454545455</v>
+      </c>
+      <c r="AH245" t="n">
+        <v>78.81818181818181</v>
+      </c>
+      <c r="AI245" t="n">
+        <v>47656818.18181818</v>
+      </c>
+      <c r="AJ245" t="n">
+        <v>85.54545454545455</v>
+      </c>
+      <c r="AK245" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="AL245" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AM245" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AN245" t="n">
+        <v>81.22222222222223</v>
+      </c>
+      <c r="AO245" t="n">
+        <v>35388888.88888889</v>
+      </c>
+      <c r="AP245" t="n">
+        <v>84.11111111111111</v>
+      </c>
+      <c r="AQ245" t="n">
+        <v>25.94444444444444</v>
+      </c>
+      <c r="AR245" t="n">
+        <v>180.3888888888889</v>
+      </c>
+      <c r="AS245" t="n">
+        <v>2.277777777777778</v>
+      </c>
+      <c r="AT245" t="n">
+        <v>79.33333333333333</v>
+      </c>
+      <c r="AU245" t="n">
+        <v>43516944.44444445</v>
+      </c>
+      <c r="AV245" t="n">
+        <v>83.94444444444444</v>
+      </c>
+      <c r="AW245" t="n">
+        <v>22.4375</v>
+      </c>
+      <c r="AX245" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AY245" t="n">
+        <v>1.9375</v>
+      </c>
+      <c r="AZ245" t="n">
+        <v>75</v>
+      </c>
+      <c r="BA245" t="n">
+        <v>19968750</v>
+      </c>
+      <c r="BB245" t="n">
+        <v>81.625</v>
+      </c>
+      <c r="BC245" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD245" t="n">
+        <v>191</v>
+      </c>
+      <c r="BE245" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF245" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG245" t="n">
+        <v>90</v>
+      </c>
+      <c r="BH245" t="n">
+        <v>129500000</v>
+      </c>
+      <c r="BI245" t="n">
+        <v>92</v>
+      </c>
+      <c r="BJ245" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="BK245" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="BL245" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BM245" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN245" t="n">
+        <v>396</v>
+      </c>
+      <c r="BO245" t="n">
+        <v>116500000</v>
+      </c>
+      <c r="BP245" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>8UHsapgU</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="n">
+        <v>45514.35416666666</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">davies a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>33280</v>
+      </c>
+      <c r="F246" t="n">
+        <v>21401</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>2</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="n">
+        <v>63</v>
+      </c>
+      <c r="N246" t="n">
+        <v>37</v>
+      </c>
+      <c r="O246" t="n">
+        <v>12</v>
+      </c>
+      <c r="P246" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>4</v>
+      </c>
+      <c r="R246" t="n">
+        <v>4</v>
+      </c>
+      <c r="S246" t="n">
+        <v>10</v>
+      </c>
+      <c r="T246" t="n">
+        <v>8</v>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>pYaUUJs1</t>
+        </is>
+      </c>
+      <c r="W246" t="n">
+        <v>48</v>
+      </c>
+      <c r="X246" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA246" t="inlineStr"/>
+      <c r="AB246" t="inlineStr"/>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="AE246" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AF246" t="n">
+        <v>181</v>
+      </c>
+      <c r="AG246" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH246" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AI246" t="n">
+        <v>2350000</v>
+      </c>
+      <c r="AJ246" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AK246" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="AL246" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AM246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN246" t="n">
+        <v>68.55555555555556</v>
+      </c>
+      <c r="AO246" t="n">
+        <v>2480555.555555556</v>
+      </c>
+      <c r="AP246" t="n">
+        <v>76.22222222222223</v>
+      </c>
+      <c r="AQ246" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AR246" t="n">
+        <v>184.9333333333333</v>
+      </c>
+      <c r="AS246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT246" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AU246" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="AV246" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="AW246" t="n">
+        <v>21.92857142857143</v>
+      </c>
+      <c r="AX246" t="n">
+        <v>180.3571428571429</v>
+      </c>
+      <c r="AY246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ246" t="n">
+        <v>65.35714285714286</v>
+      </c>
+      <c r="BA246" t="n">
+        <v>1471428.571428571</v>
+      </c>
+      <c r="BB246" t="n">
+        <v>73.57142857142857</v>
+      </c>
+      <c r="BC246" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BD246" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="BE246" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF246" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG246" t="n">
+        <v>135</v>
+      </c>
+      <c r="BH246" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="BI246" t="n">
+        <v>141</v>
+      </c>
+      <c r="BJ246" t="n">
+        <v>22</v>
+      </c>
+      <c r="BK246" t="n">
+        <v>180</v>
+      </c>
+      <c r="BL246" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM246" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN246" t="n">
+        <v>272</v>
+      </c>
+      <c r="BO246" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="BP246" t="n">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>2meCcXHP</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="n">
+        <v>45514.35416666666</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stroud k 
+  eng </t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mkm stadium
+  hull </t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>25586</v>
+      </c>
+      <c r="F247" t="n">
+        <v>21011</v>
+      </c>
+      <c r="G247" t="n">
+        <v>1</v>
+      </c>
+      <c r="H247" t="n">
+        <v>1</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>S66R0t75</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>MahqU27I</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="n">
+        <v>48</v>
+      </c>
+      <c r="N247" t="n">
+        <v>52</v>
+      </c>
+      <c r="O247" t="n">
+        <v>11</v>
+      </c>
+      <c r="P247" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>5</v>
+      </c>
+      <c r="R247" t="n">
+        <v>4</v>
+      </c>
+      <c r="S247" t="n">
+        <v>11</v>
+      </c>
+      <c r="T247" t="n">
+        <v>14</v>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+      <c r="W247" t="n">
+        <v>48</v>
+      </c>
+      <c r="X247" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA247" t="inlineStr"/>
+      <c r="AB247" t="inlineStr"/>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr"/>
+      <c r="AE247" t="n">
+        <v>23.55555555555556</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH247" t="n">
+        <v>68.88888888888889</v>
+      </c>
+      <c r="AI247" t="n">
+        <v>2530555.555555556</v>
+      </c>
+      <c r="AJ247" t="n">
+        <v>74.88888888888889</v>
+      </c>
+      <c r="AK247" t="n">
+        <v>23.625</v>
+      </c>
+      <c r="AL247" t="n">
+        <v>182.625</v>
+      </c>
+      <c r="AM247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN247" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AO247" t="n">
+        <v>2075000</v>
+      </c>
+      <c r="AP247" t="n">
+        <v>74.625</v>
+      </c>
+      <c r="AQ247" t="n">
+        <v>21.36363636363636</v>
+      </c>
+      <c r="AR247" t="n">
+        <v>178</v>
+      </c>
+      <c r="AS247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT247" t="n">
+        <v>63.81818181818182</v>
+      </c>
+      <c r="AU247" t="n">
+        <v>2020000</v>
+      </c>
+      <c r="AV247" t="n">
+        <v>72.36363636363636</v>
+      </c>
+      <c r="AW247" t="n">
+        <v>26.92307692307692</v>
+      </c>
+      <c r="AX247" t="n">
+        <v>179.8461538461538</v>
+      </c>
+      <c r="AY247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ247" t="n">
+        <v>68.30769230769231</v>
+      </c>
+      <c r="BA247" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="BB247" t="n">
+        <v>72.46153846153847</v>
+      </c>
+      <c r="BC247" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD247" t="n">
+        <v>183</v>
+      </c>
+      <c r="BE247" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF247" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG247" t="n">
+        <v>132</v>
+      </c>
+      <c r="BH247" t="n">
+        <v>3225000</v>
+      </c>
+      <c r="BI247" t="n">
+        <v>153</v>
+      </c>
+      <c r="BJ247" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK247" t="n">
+        <v>187</v>
+      </c>
+      <c r="BL247" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM247" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN247" t="n">
+        <v>70</v>
+      </c>
+      <c r="BO247" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="BP247" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>bJtrhBum</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="n">
+        <v>45514.35416666666</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langford o 
+  eng </t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">elland road
+  leeds </t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>37792</v>
+      </c>
+      <c r="F248" t="n">
+        <v>36432</v>
+      </c>
+      <c r="G248" t="n">
+        <v>3</v>
+      </c>
+      <c r="H248" t="n">
+        <v>3</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>zckREQFJ</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="n">
+        <v>65</v>
+      </c>
+      <c r="N248" t="n">
+        <v>35</v>
+      </c>
+      <c r="O248" t="n">
+        <v>23</v>
+      </c>
+      <c r="P248" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>10</v>
+      </c>
+      <c r="R248" t="n">
+        <v>4</v>
+      </c>
+      <c r="S248" t="n">
+        <v>21</v>
+      </c>
+      <c r="T248" t="n">
+        <v>18</v>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>djl0V3o6</t>
+        </is>
+      </c>
+      <c r="W248" t="n">
+        <v>48</v>
+      </c>
+      <c r="X248" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA248" t="inlineStr"/>
+      <c r="AB248" t="inlineStr"/>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr"/>
+      <c r="AE248" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AF248" t="n">
+        <v>184.6666666666667</v>
+      </c>
+      <c r="AG248" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AH248" t="n">
+        <v>74.33333333333333</v>
+      </c>
+      <c r="AI248" t="n">
+        <v>7633333.333333333</v>
+      </c>
+      <c r="AJ248" t="n">
+        <v>79.44444444444444</v>
+      </c>
+      <c r="AK248" t="inlineStr"/>
+      <c r="AL248" t="inlineStr"/>
+      <c r="AM248" t="inlineStr"/>
+      <c r="AN248" t="inlineStr"/>
+      <c r="AO248" t="inlineStr"/>
+      <c r="AP248" t="inlineStr"/>
+      <c r="AQ248" t="n">
+        <v>26.23076923076923</v>
+      </c>
+      <c r="AR248" t="n">
+        <v>183.3846153846154</v>
+      </c>
+      <c r="AS248" t="n">
+        <v>1.230769230769231</v>
+      </c>
+      <c r="AT248" t="n">
+        <v>72.69230769230769</v>
+      </c>
+      <c r="AU248" t="n">
+        <v>4407692.307692308</v>
+      </c>
+      <c r="AV248" t="n">
+        <v>75.61538461538461</v>
+      </c>
+      <c r="AW248" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX248" t="n">
+        <v>174.2</v>
+      </c>
+      <c r="AY248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ248" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="BA248" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BB248" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="BC248" t="inlineStr"/>
+      <c r="BD248" t="inlineStr"/>
+      <c r="BE248" t="inlineStr"/>
+      <c r="BF248" t="inlineStr"/>
+      <c r="BG248" t="inlineStr"/>
+      <c r="BH248" t="inlineStr"/>
+      <c r="BI248" t="inlineStr"/>
+      <c r="BJ248" t="inlineStr"/>
+      <c r="BK248" t="inlineStr"/>
+      <c r="BL248" t="inlineStr"/>
+      <c r="BM248" t="inlineStr"/>
+      <c r="BN248" t="inlineStr"/>
+      <c r="BO248" t="inlineStr"/>
+      <c r="BP248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>CrrhJmvn</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="n">
+        <v>45514.35416666666</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riverside stadium
+  middlesbrough </t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>34742</v>
+      </c>
+      <c r="F249" t="n">
+        <v>26610</v>
+      </c>
+      <c r="G249" t="n">
+        <v>1</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>6F0lvLNC</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="n">
+        <v>38</v>
+      </c>
+      <c r="N249" t="n">
+        <v>62</v>
+      </c>
+      <c r="O249" t="n">
+        <v>19</v>
+      </c>
+      <c r="P249" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>3</v>
+      </c>
+      <c r="R249" t="n">
+        <v>0</v>
+      </c>
+      <c r="S249" t="n">
+        <v>14</v>
+      </c>
+      <c r="T249" t="n">
+        <v>11</v>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="W249" t="n">
+        <v>48</v>
+      </c>
+      <c r="X249" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA249" t="inlineStr"/>
+      <c r="AB249" t="inlineStr"/>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="AE249" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AF249" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="AG249" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH249" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AI249" t="n">
+        <v>2820000</v>
+      </c>
+      <c r="AJ249" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AK249" t="inlineStr"/>
+      <c r="AL249" t="inlineStr"/>
+      <c r="AM249" t="inlineStr"/>
+      <c r="AN249" t="inlineStr"/>
+      <c r="AO249" t="inlineStr"/>
+      <c r="AP249" t="inlineStr"/>
+      <c r="AQ249" t="n">
+        <v>22.61538461538462</v>
+      </c>
+      <c r="AR249" t="n">
+        <v>185.3076923076923</v>
+      </c>
+      <c r="AS249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT249" t="n">
+        <v>67.30769230769231</v>
+      </c>
+      <c r="AU249" t="n">
+        <v>1992307.692307692</v>
+      </c>
+      <c r="AV249" t="n">
+        <v>74.61538461538461</v>
+      </c>
+      <c r="AW249" t="n">
+        <v>24.71428571428572</v>
+      </c>
+      <c r="AX249" t="n">
+        <v>179.2142857142857</v>
+      </c>
+      <c r="AY249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ249" t="n">
+        <v>63.78571428571428</v>
+      </c>
+      <c r="BA249" t="n">
+        <v>914285.7142857143</v>
+      </c>
+      <c r="BB249" t="n">
+        <v>70.92857142857143</v>
+      </c>
+      <c r="BC249" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD249" t="n">
+        <v>182</v>
+      </c>
+      <c r="BE249" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF249" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG249" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH249" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="BI249" t="n">
+        <v>76</v>
+      </c>
+      <c r="BJ249" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="BK249" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="BL249" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM249" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN249" t="n">
+        <v>138</v>
+      </c>
+      <c r="BO249" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="BP249" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>ILdqjkAa</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="n">
+        <v>45514.35416666666</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busby j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the den
+  london </t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>20146</v>
+      </c>
+      <c r="F250" t="n">
+        <v>16456</v>
+      </c>
+      <c r="G250" t="n">
+        <v>2</v>
+      </c>
+      <c r="H250" t="n">
+        <v>3</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="n">
+        <v>52</v>
+      </c>
+      <c r="N250" t="n">
+        <v>48</v>
+      </c>
+      <c r="O250" t="n">
+        <v>17</v>
+      </c>
+      <c r="P250" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>5</v>
+      </c>
+      <c r="R250" t="n">
+        <v>4</v>
+      </c>
+      <c r="S250" t="n">
+        <v>12</v>
+      </c>
+      <c r="T250" t="n">
+        <v>15</v>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="W250" t="n">
+        <v>48</v>
+      </c>
+      <c r="X250" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA250" t="inlineStr"/>
+      <c r="AB250" t="inlineStr"/>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="AE250" t="n">
+        <v>28.11111111111111</v>
+      </c>
+      <c r="AF250" t="n">
+        <v>178.7777777777778</v>
+      </c>
+      <c r="AG250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH250" t="n">
+        <v>69.11111111111111</v>
+      </c>
+      <c r="AI250" t="n">
+        <v>1491666.666666667</v>
+      </c>
+      <c r="AJ250" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AK250" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="AL250" t="n">
+        <v>184.4444444444445</v>
+      </c>
+      <c r="AM250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN250" t="n">
+        <v>69</v>
+      </c>
+      <c r="AO250" t="n">
+        <v>1866666.666666667</v>
+      </c>
+      <c r="AP250" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="AQ250" t="n">
+        <v>23.93333333333333</v>
+      </c>
+      <c r="AR250" t="n">
+        <v>178.5333333333333</v>
+      </c>
+      <c r="AS250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT250" t="n">
+        <v>66.26666666666667</v>
+      </c>
+      <c r="AU250" t="n">
+        <v>1445000</v>
+      </c>
+      <c r="AV250" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AW250" t="n">
+        <v>25.4375</v>
+      </c>
+      <c r="AX250" t="n">
+        <v>181.625</v>
+      </c>
+      <c r="AY250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ250" t="n">
+        <v>68.4375</v>
+      </c>
+      <c r="BA250" t="n">
+        <v>1762500</v>
+      </c>
+      <c r="BB250" t="n">
+        <v>72.1875</v>
+      </c>
+      <c r="BC250" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="BD250" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="BE250" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF250" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG250" t="n">
+        <v>348</v>
+      </c>
+      <c r="BH250" t="n">
+        <v>15575000</v>
+      </c>
+      <c r="BI250" t="n">
+        <v>374</v>
+      </c>
+      <c r="BJ250" t="inlineStr"/>
+      <c r="BK250" t="inlineStr"/>
+      <c r="BL250" t="inlineStr"/>
+      <c r="BM250" t="inlineStr"/>
+      <c r="BN250" t="inlineStr"/>
+      <c r="BO250" t="inlineStr"/>
+      <c r="BP250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>Qo0ilTvC</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="n">
+        <v>45514.35416666666</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kitchen a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kassam stadium
+  oxford </t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>12500</v>
+      </c>
+      <c r="F251" t="n">
+        <v>11333</v>
+      </c>
+      <c r="G251" t="n">
+        <v>2</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>vgOBT43c</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="n">
+        <v>52</v>
+      </c>
+      <c r="N251" t="n">
+        <v>48</v>
+      </c>
+      <c r="O251" t="n">
+        <v>13</v>
+      </c>
+      <c r="P251" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>5</v>
+      </c>
+      <c r="R251" t="n">
+        <v>2</v>
+      </c>
+      <c r="S251" t="n">
+        <v>4</v>
+      </c>
+      <c r="T251" t="n">
+        <v>15</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="W251" t="n">
+        <v>48</v>
+      </c>
+      <c r="X251" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA251" t="inlineStr"/>
+      <c r="AB251" t="inlineStr"/>
+      <c r="AC251" t="inlineStr"/>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr"/>
+      <c r="AF251" t="inlineStr"/>
+      <c r="AG251" t="inlineStr"/>
+      <c r="AH251" t="inlineStr"/>
+      <c r="AI251" t="inlineStr"/>
+      <c r="AJ251" t="inlineStr"/>
+      <c r="AK251" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AL251" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AM251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN251" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO251" t="n">
+        <v>3070000</v>
+      </c>
+      <c r="AP251" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="AQ251" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="AR251" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="AS251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT251" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="AU251" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AV251" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AW251" t="n">
+        <v>24.15384615384615</v>
+      </c>
+      <c r="AX251" t="n">
+        <v>184.3076923076923</v>
+      </c>
+      <c r="AY251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ251" t="n">
+        <v>68.38461538461539</v>
+      </c>
+      <c r="BA251" t="n">
+        <v>2001923.076923077</v>
+      </c>
+      <c r="BB251" t="n">
+        <v>73.30769230769231</v>
+      </c>
+      <c r="BC251" t="inlineStr"/>
+      <c r="BD251" t="inlineStr"/>
+      <c r="BE251" t="inlineStr"/>
+      <c r="BF251" t="inlineStr"/>
+      <c r="BG251" t="inlineStr"/>
+      <c r="BH251" t="inlineStr"/>
+      <c r="BI251" t="inlineStr"/>
+      <c r="BJ251" t="n">
+        <v>33</v>
+      </c>
+      <c r="BK251" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL251" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM251" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN251" t="n">
+        <v>71</v>
+      </c>
+      <c r="BO251" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="BP251" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>n1l0n79O</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="n">
+        <v>45514.35416666666</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webb d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">loftus road
+  london </t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>18439</v>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="n">
+        <v>1</v>
+      </c>
+      <c r="H252" t="n">
+        <v>3</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>CCBWpzjj</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="n">
+        <v>40</v>
+      </c>
+      <c r="N252" t="n">
+        <v>60</v>
+      </c>
+      <c r="O252" t="n">
+        <v>13</v>
+      </c>
+      <c r="P252" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>6</v>
+      </c>
+      <c r="R252" t="n">
+        <v>4</v>
+      </c>
+      <c r="S252" t="n">
+        <v>8</v>
+      </c>
+      <c r="T252" t="n">
+        <v>8</v>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="W252" t="n">
+        <v>48</v>
+      </c>
+      <c r="X252" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA252" t="inlineStr"/>
+      <c r="AB252" t="inlineStr"/>
+      <c r="AC252" t="inlineStr"/>
+      <c r="AD252" t="inlineStr"/>
+      <c r="AE252" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AF252" t="n">
+        <v>181</v>
+      </c>
+      <c r="AG252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH252" t="n">
+        <v>68.375</v>
+      </c>
+      <c r="AI252" t="n">
+        <v>1531250</v>
+      </c>
+      <c r="AJ252" t="n">
+        <v>72.125</v>
+      </c>
+      <c r="AK252" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AL252" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="AM252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN252" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AO252" t="n">
+        <v>2320000</v>
+      </c>
+      <c r="AP252" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AQ252" t="n">
+        <v>25.55555555555556</v>
+      </c>
+      <c r="AR252" t="n">
+        <v>183</v>
+      </c>
+      <c r="AS252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT252" t="n">
+        <v>66</v>
+      </c>
+      <c r="AU252" t="n">
+        <v>1219444.444444444</v>
+      </c>
+      <c r="AV252" t="n">
+        <v>70.44444444444444</v>
+      </c>
+      <c r="AW252" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX252" t="n">
+        <v>181.1428571428571</v>
+      </c>
+      <c r="AY252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ252" t="n">
+        <v>66.85714285714286</v>
+      </c>
+      <c r="BA252" t="n">
+        <v>2128571.428571429</v>
+      </c>
+      <c r="BB252" t="n">
+        <v>76</v>
+      </c>
+      <c r="BC252" t="inlineStr"/>
+      <c r="BD252" t="inlineStr"/>
+      <c r="BE252" t="inlineStr"/>
+      <c r="BF252" t="inlineStr"/>
+      <c r="BG252" t="inlineStr"/>
+      <c r="BH252" t="inlineStr"/>
+      <c r="BI252" t="inlineStr"/>
+      <c r="BJ252" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="BK252" t="n">
+        <v>183</v>
+      </c>
+      <c r="BL252" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM252" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN252" t="n">
+        <v>216</v>
+      </c>
+      <c r="BO252" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="BP252" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>xQT96Aft</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="n">
+        <v>45514.35416666666</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bet365 stadium
+  stoke on trent </t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>30089</v>
+      </c>
+      <c r="F253" t="n">
+        <v>25037</v>
+      </c>
+      <c r="G253" t="n">
+        <v>1</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="n">
+        <v>42</v>
+      </c>
+      <c r="N253" t="n">
+        <v>58</v>
+      </c>
+      <c r="O253" t="n">
+        <v>13</v>
+      </c>
+      <c r="P253" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>4</v>
+      </c>
+      <c r="R253" t="n">
+        <v>1</v>
+      </c>
+      <c r="S253" t="n">
+        <v>7</v>
+      </c>
+      <c r="T253" t="n">
+        <v>9</v>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
+      <c r="W253" t="n">
+        <v>48</v>
+      </c>
+      <c r="X253" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA253" t="inlineStr"/>
+      <c r="AB253" t="inlineStr"/>
+      <c r="AC253" t="inlineStr"/>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="AE253" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AF253" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AG253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH253" t="n">
+        <v>69</v>
+      </c>
+      <c r="AI253" t="n">
+        <v>2228125</v>
+      </c>
+      <c r="AJ253" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AK253" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AL253" t="n">
+        <v>182</v>
+      </c>
+      <c r="AM253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN253" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="AO253" t="n">
+        <v>3775000</v>
+      </c>
+      <c r="AP253" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AQ253" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR253" t="n">
+        <v>179.9333333333333</v>
+      </c>
+      <c r="AS253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT253" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AU253" t="n">
+        <v>1934000</v>
+      </c>
+      <c r="AV253" t="n">
+        <v>72.26666666666667</v>
+      </c>
+      <c r="AW253" t="n">
+        <v>24.15789473684211</v>
+      </c>
+      <c r="AX253" t="n">
+        <v>181.3684210526316</v>
+      </c>
+      <c r="AY253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ253" t="n">
+        <v>69.68421052631579</v>
+      </c>
+      <c r="BA253" t="n">
+        <v>2748684.210526316</v>
+      </c>
+      <c r="BB253" t="n">
+        <v>74.78947368421052</v>
+      </c>
+      <c r="BC253" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="BD253" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="BE253" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF253" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG253" t="n">
+        <v>209</v>
+      </c>
+      <c r="BH253" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="BI253" t="n">
+        <v>210</v>
+      </c>
+      <c r="BJ253" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK253" t="n">
+        <v>185</v>
+      </c>
+      <c r="BL253" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM253" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN253" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO253" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="BP253" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>04EZ06OH</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="n">
+        <v>45513.66666666666</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ewood park
+  blackburn </t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>31367</v>
+      </c>
+      <c r="F254" t="n">
+        <v>17975</v>
+      </c>
+      <c r="G254" t="n">
+        <v>4</v>
+      </c>
+      <c r="H254" t="n">
+        <v>2</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Iug0YO0Q</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="n">
+        <v>47</v>
+      </c>
+      <c r="N254" t="n">
+        <v>53</v>
+      </c>
+      <c r="O254" t="n">
+        <v>12</v>
+      </c>
+      <c r="P254" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>8</v>
+      </c>
+      <c r="R254" t="n">
+        <v>4</v>
+      </c>
+      <c r="S254" t="n">
+        <v>9</v>
+      </c>
+      <c r="T254" t="n">
+        <v>11</v>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
+      <c r="W254" t="n">
+        <v>48</v>
+      </c>
+      <c r="X254" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA254" t="inlineStr"/>
+      <c r="AB254" t="inlineStr"/>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr"/>
+      <c r="AE254" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AF254" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="AG254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH254" t="n">
+        <v>70</v>
+      </c>
+      <c r="AI254" t="n">
+        <v>2040000</v>
+      </c>
+      <c r="AJ254" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AK254" t="inlineStr"/>
+      <c r="AL254" t="inlineStr"/>
+      <c r="AM254" t="inlineStr"/>
+      <c r="AN254" t="inlineStr"/>
+      <c r="AO254" t="inlineStr"/>
+      <c r="AP254" t="inlineStr"/>
+      <c r="AQ254" t="n">
+        <v>26.70588235294118</v>
+      </c>
+      <c r="AR254" t="n">
+        <v>180.9411764705882</v>
+      </c>
+      <c r="AS254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT254" t="n">
+        <v>69.17647058823529</v>
+      </c>
+      <c r="AU254" t="n">
+        <v>2294117.647058824</v>
+      </c>
+      <c r="AV254" t="n">
+        <v>72.17647058823529</v>
+      </c>
+      <c r="AW254" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AX254" t="n">
+        <v>184</v>
+      </c>
+      <c r="AY254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ254" t="n">
+        <v>64.33333333333333</v>
+      </c>
+      <c r="BA254" t="n">
+        <v>958333.3333333334</v>
+      </c>
+      <c r="BB254" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BC254" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD254" t="n">
+        <v>183</v>
+      </c>
+      <c r="BE254" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF254" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG254" t="n">
+        <v>134</v>
+      </c>
+      <c r="BH254" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="BI254" t="n">
+        <v>148</v>
+      </c>
+      <c r="BJ254" t="n">
+        <v>26</v>
+      </c>
+      <c r="BK254" t="n">
+        <v>175</v>
+      </c>
+      <c r="BL254" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM254" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN254" t="n">
+        <v>70</v>
+      </c>
+      <c r="BO254" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="BP254" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>pCQRkLbJ</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="n">
+        <v>45513.66666666666</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deepdale
+  preston </t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>23408</v>
+      </c>
+      <c r="F255" t="n">
+        <v>17948</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" t="n">
+        <v>2</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>x8IDVcbi</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="n">
+        <v>50</v>
+      </c>
+      <c r="N255" t="n">
+        <v>50</v>
+      </c>
+      <c r="O255" t="n">
+        <v>8</v>
+      </c>
+      <c r="P255" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>2</v>
+      </c>
+      <c r="R255" t="n">
+        <v>3</v>
+      </c>
+      <c r="S255" t="n">
+        <v>12</v>
+      </c>
+      <c r="T255" t="n">
+        <v>15</v>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>6wEAqBAE</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="W255" t="n">
+        <v>48</v>
+      </c>
+      <c r="X255" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA255" t="inlineStr"/>
+      <c r="AB255" t="inlineStr"/>
+      <c r="AC255" t="inlineStr"/>
+      <c r="AD255" t="inlineStr"/>
+      <c r="AE255" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="AF255" t="n">
+        <v>186</v>
+      </c>
+      <c r="AG255" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AH255" t="n">
+        <v>71.125</v>
+      </c>
+      <c r="AI255" t="n">
+        <v>5921875</v>
+      </c>
+      <c r="AJ255" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="AK255" t="inlineStr"/>
+      <c r="AL255" t="inlineStr"/>
+      <c r="AM255" t="inlineStr"/>
+      <c r="AN255" t="inlineStr"/>
+      <c r="AO255" t="inlineStr"/>
+      <c r="AP255" t="inlineStr"/>
+      <c r="AQ255" t="n">
+        <v>22.83333333333333</v>
+      </c>
+      <c r="AR255" t="n">
+        <v>181.3888888888889</v>
+      </c>
+      <c r="AS255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT255" t="n">
+        <v>68.05555555555556</v>
+      </c>
+      <c r="AU255" t="n">
+        <v>2048611.111111111</v>
+      </c>
+      <c r="AV255" t="n">
+        <v>75.16666666666667</v>
+      </c>
+      <c r="AW255" t="n">
+        <v>22.46666666666667</v>
+      </c>
+      <c r="AX255" t="n">
+        <v>182.5333333333333</v>
+      </c>
+      <c r="AY255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ255" t="n">
+        <v>66.53333333333333</v>
+      </c>
+      <c r="BA255" t="n">
+        <v>2505000</v>
+      </c>
+      <c r="BB255" t="n">
+        <v>74.93333333333334</v>
+      </c>
+      <c r="BC255" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD255" t="n">
+        <v>176</v>
+      </c>
+      <c r="BE255" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF255" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG255" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH255" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="BI255" t="n">
+        <v>76</v>
+      </c>
+      <c r="BJ255" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK255" t="n">
+        <v>175.3333333333333</v>
+      </c>
+      <c r="BL255" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM255" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN255" t="n">
+        <v>208</v>
+      </c>
+      <c r="BO255" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="BP255" t="n">
+        <v>219</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/england/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP255"/>
+  <dimension ref="A1:BP313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55981,6 +55981,9936 @@
         <v>219</v>
       </c>
     </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>fmqtFMjD</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="n">
+        <v>45522.52083333334</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F256" t="n">
+        <v>39818</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" t="n">
+        <v>2</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="K256" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L256" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M256" t="n">
+        <v>48</v>
+      </c>
+      <c r="N256" t="n">
+        <v>52</v>
+      </c>
+      <c r="O256" t="n">
+        <v>10</v>
+      </c>
+      <c r="P256" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>3</v>
+      </c>
+      <c r="R256" t="n">
+        <v>5</v>
+      </c>
+      <c r="S256" t="n">
+        <v>12</v>
+      </c>
+      <c r="T256" t="n">
+        <v>9</v>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="W256" t="n">
+        <v>48</v>
+      </c>
+      <c r="X256" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA256" t="inlineStr"/>
+      <c r="AB256" t="inlineStr"/>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="AE256" t="n">
+        <v>21.90909090909091</v>
+      </c>
+      <c r="AF256" t="n">
+        <v>183.1818181818182</v>
+      </c>
+      <c r="AG256" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AH256" t="n">
+        <v>78.36363636363636</v>
+      </c>
+      <c r="AI256" t="n">
+        <v>26772727.27272727</v>
+      </c>
+      <c r="AJ256" t="n">
+        <v>84.63636363636364</v>
+      </c>
+      <c r="AK256" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AL256" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AM256" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AN256" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="AO256" t="n">
+        <v>71150000</v>
+      </c>
+      <c r="AP256" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="AQ256" t="n">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="AR256" t="n">
+        <v>179.8461538461538</v>
+      </c>
+      <c r="AS256" t="n">
+        <v>1.307692307692308</v>
+      </c>
+      <c r="AT256" t="n">
+        <v>78.07692307692308</v>
+      </c>
+      <c r="AU256" t="n">
+        <v>22576923.07692308</v>
+      </c>
+      <c r="AV256" t="n">
+        <v>82.92307692307692</v>
+      </c>
+      <c r="AW256" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX256" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AY256" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AZ256" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="BA256" t="n">
+        <v>46382500</v>
+      </c>
+      <c r="BB256" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="BC256" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD256" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BE256" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF256" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG256" t="n">
+        <v>139</v>
+      </c>
+      <c r="BH256" t="n">
+        <v>24625000</v>
+      </c>
+      <c r="BI256" t="n">
+        <v>159</v>
+      </c>
+      <c r="BJ256" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK256" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BL256" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM256" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN256" t="n">
+        <v>158</v>
+      </c>
+      <c r="BO256" t="n">
+        <v>132400000</v>
+      </c>
+      <c r="BP256" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>8WpYGrM0</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="n">
+        <v>45522.41666666666</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>17250</v>
+      </c>
+      <c r="F257" t="n">
+        <v>16988</v>
+      </c>
+      <c r="G257" t="n">
+        <v>2</v>
+      </c>
+      <c r="H257" t="n">
+        <v>1</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="K257" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L257" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="M257" t="n">
+        <v>46</v>
+      </c>
+      <c r="N257" t="n">
+        <v>54</v>
+      </c>
+      <c r="O257" t="n">
+        <v>9</v>
+      </c>
+      <c r="P257" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>5</v>
+      </c>
+      <c r="R257" t="n">
+        <v>6</v>
+      </c>
+      <c r="S257" t="n">
+        <v>6</v>
+      </c>
+      <c r="T257" t="n">
+        <v>15</v>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="W257" t="n">
+        <v>48</v>
+      </c>
+      <c r="X257" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA257" t="inlineStr"/>
+      <c r="AB257" t="inlineStr"/>
+      <c r="AC257" t="inlineStr"/>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="AE257" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AF257" t="n">
+        <v>185.9090909090909</v>
+      </c>
+      <c r="AG257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH257" t="n">
+        <v>76.27272727272727</v>
+      </c>
+      <c r="AI257" t="n">
+        <v>10918181.81818182</v>
+      </c>
+      <c r="AJ257" t="n">
+        <v>79.27272727272727</v>
+      </c>
+      <c r="AK257" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="AL257" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="AM257" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN257" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="AO257" t="n">
+        <v>14170000</v>
+      </c>
+      <c r="AP257" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="AQ257" t="n">
+        <v>23.84210526315789</v>
+      </c>
+      <c r="AR257" t="n">
+        <v>177.1578947368421</v>
+      </c>
+      <c r="AS257" t="n">
+        <v>1.315789473684211</v>
+      </c>
+      <c r="AT257" t="n">
+        <v>73.78947368421052</v>
+      </c>
+      <c r="AU257" t="n">
+        <v>8540789.47368421</v>
+      </c>
+      <c r="AV257" t="n">
+        <v>79.63157894736842</v>
+      </c>
+      <c r="AW257" t="n">
+        <v>26.78947368421053</v>
+      </c>
+      <c r="AX257" t="n">
+        <v>183</v>
+      </c>
+      <c r="AY257" t="n">
+        <v>1.263157894736842</v>
+      </c>
+      <c r="AZ257" t="n">
+        <v>75.89473684210526</v>
+      </c>
+      <c r="BA257" t="n">
+        <v>9857894.736842105</v>
+      </c>
+      <c r="BB257" t="n">
+        <v>78.10526315789474</v>
+      </c>
+      <c r="BC257" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BD257" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="BE257" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF257" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG257" t="n">
+        <v>233</v>
+      </c>
+      <c r="BH257" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="BI257" t="n">
+        <v>240</v>
+      </c>
+      <c r="BJ257" t="inlineStr"/>
+      <c r="BK257" t="inlineStr"/>
+      <c r="BL257" t="inlineStr"/>
+      <c r="BM257" t="inlineStr"/>
+      <c r="BN257" t="inlineStr"/>
+      <c r="BO257" t="inlineStr"/>
+      <c r="BP257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>nHdPI4il</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="n">
+        <v>45521.5625</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F258" t="n">
+        <v>62463</v>
+      </c>
+      <c r="G258" t="n">
+        <v>1</v>
+      </c>
+      <c r="H258" t="n">
+        <v>2</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="K258" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L258" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M258" t="n">
+        <v>51</v>
+      </c>
+      <c r="N258" t="n">
+        <v>49</v>
+      </c>
+      <c r="O258" t="n">
+        <v>14</v>
+      </c>
+      <c r="P258" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>3</v>
+      </c>
+      <c r="R258" t="n">
+        <v>3</v>
+      </c>
+      <c r="S258" t="n">
+        <v>18</v>
+      </c>
+      <c r="T258" t="n">
+        <v>11</v>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="W258" t="n">
+        <v>48</v>
+      </c>
+      <c r="X258" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA258" t="inlineStr"/>
+      <c r="AB258" t="inlineStr"/>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr"/>
+      <c r="AE258" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF258" t="n">
+        <v>183.2222222222222</v>
+      </c>
+      <c r="AG258" t="n">
+        <v>2.111111111111111</v>
+      </c>
+      <c r="AH258" t="n">
+        <v>79.22222222222223</v>
+      </c>
+      <c r="AI258" t="n">
+        <v>20333333.33333333</v>
+      </c>
+      <c r="AJ258" t="n">
+        <v>80.88888888888889</v>
+      </c>
+      <c r="AK258" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AL258" t="n">
+        <v>184</v>
+      </c>
+      <c r="AM258" t="n">
+        <v>2.090909090909091</v>
+      </c>
+      <c r="AN258" t="n">
+        <v>79.72727272727273</v>
+      </c>
+      <c r="AO258" t="n">
+        <v>25054545.45454545</v>
+      </c>
+      <c r="AP258" t="n">
+        <v>81.90909090909091</v>
+      </c>
+      <c r="AQ258" t="n">
+        <v>27.9375</v>
+      </c>
+      <c r="AR258" t="n">
+        <v>177.0625</v>
+      </c>
+      <c r="AS258" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AT258" t="n">
+        <v>77.9375</v>
+      </c>
+      <c r="AU258" t="n">
+        <v>15362500</v>
+      </c>
+      <c r="AV258" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="AW258" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AX258" t="n">
+        <v>179.952380952381</v>
+      </c>
+      <c r="AY258" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="AZ258" t="n">
+        <v>74.9047619047619</v>
+      </c>
+      <c r="BA258" t="n">
+        <v>13395238.0952381</v>
+      </c>
+      <c r="BB258" t="n">
+        <v>80.19047619047619</v>
+      </c>
+      <c r="BC258" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD258" t="n">
+        <v>187</v>
+      </c>
+      <c r="BE258" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF258" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG258" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH258" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="BI258" t="n">
+        <v>84</v>
+      </c>
+      <c r="BJ258" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BK258" t="n">
+        <v>190</v>
+      </c>
+      <c r="BL258" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM258" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN258" t="n">
+        <v>161</v>
+      </c>
+      <c r="BO258" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="BP258" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>CntkHiGq</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="n">
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>60704</v>
+      </c>
+      <c r="F259" t="n">
+        <v>60261</v>
+      </c>
+      <c r="G259" t="n">
+        <v>2</v>
+      </c>
+      <c r="H259" t="n">
+        <v>0</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="K259" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L259" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M259" t="n">
+        <v>53</v>
+      </c>
+      <c r="N259" t="n">
+        <v>47</v>
+      </c>
+      <c r="O259" t="n">
+        <v>18</v>
+      </c>
+      <c r="P259" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>6</v>
+      </c>
+      <c r="R259" t="n">
+        <v>3</v>
+      </c>
+      <c r="S259" t="n">
+        <v>17</v>
+      </c>
+      <c r="T259" t="n">
+        <v>14</v>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="W259" t="n">
+        <v>48</v>
+      </c>
+      <c r="X259" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA259" t="inlineStr"/>
+      <c r="AB259" t="inlineStr"/>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="AD259" t="inlineStr"/>
+      <c r="AE259" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AF259" t="n">
+        <v>182.875</v>
+      </c>
+      <c r="AG259" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AH259" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="AI259" t="n">
+        <v>66312500</v>
+      </c>
+      <c r="AJ259" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="AK259" t="inlineStr"/>
+      <c r="AL259" t="inlineStr"/>
+      <c r="AM259" t="inlineStr"/>
+      <c r="AN259" t="inlineStr"/>
+      <c r="AO259" t="inlineStr"/>
+      <c r="AP259" t="inlineStr"/>
+      <c r="AQ259" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="AR259" t="n">
+        <v>177.0625</v>
+      </c>
+      <c r="AS259" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="AT259" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="AU259" t="n">
+        <v>38125000</v>
+      </c>
+      <c r="AV259" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="AW259" t="n">
+        <v>27.05263157894737</v>
+      </c>
+      <c r="AX259" t="n">
+        <v>178.7894736842105</v>
+      </c>
+      <c r="AY259" t="n">
+        <v>1.526315789473684</v>
+      </c>
+      <c r="AZ259" t="n">
+        <v>75.52631578947368</v>
+      </c>
+      <c r="BA259" t="n">
+        <v>10021052.63157895</v>
+      </c>
+      <c r="BB259" t="n">
+        <v>78.21052631578948</v>
+      </c>
+      <c r="BC259" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BD259" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="BE259" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BF259" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG259" t="n">
+        <v>235</v>
+      </c>
+      <c r="BH259" t="n">
+        <v>60500000</v>
+      </c>
+      <c r="BI259" t="n">
+        <v>248</v>
+      </c>
+      <c r="BJ259" t="n">
+        <v>27</v>
+      </c>
+      <c r="BK259" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="BL259" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM259" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN259" t="n">
+        <v>156</v>
+      </c>
+      <c r="BO259" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="BP259" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>hdlcFVpd</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="n">
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>39572</v>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" t="n">
+        <v>3</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="K260" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L260" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M260" t="n">
+        <v>37</v>
+      </c>
+      <c r="N260" t="n">
+        <v>63</v>
+      </c>
+      <c r="O260" t="n">
+        <v>9</v>
+      </c>
+      <c r="P260" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>1</v>
+      </c>
+      <c r="R260" t="n">
+        <v>5</v>
+      </c>
+      <c r="S260" t="n">
+        <v>8</v>
+      </c>
+      <c r="T260" t="n">
+        <v>8</v>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="W260" t="n">
+        <v>48</v>
+      </c>
+      <c r="X260" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA260" t="inlineStr"/>
+      <c r="AB260" t="inlineStr"/>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="AE260" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF260" t="n">
+        <v>182.2727272727273</v>
+      </c>
+      <c r="AG260" t="n">
+        <v>1.636363636363636</v>
+      </c>
+      <c r="AH260" t="n">
+        <v>76.18181818181819</v>
+      </c>
+      <c r="AI260" t="n">
+        <v>9411363.636363637</v>
+      </c>
+      <c r="AJ260" t="n">
+        <v>78</v>
+      </c>
+      <c r="AK260" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="AL260" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="AM260" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN260" t="n">
+        <v>75.875</v>
+      </c>
+      <c r="AO260" t="n">
+        <v>9600000</v>
+      </c>
+      <c r="AP260" t="n">
+        <v>78.625</v>
+      </c>
+      <c r="AQ260" t="n">
+        <v>24.92307692307692</v>
+      </c>
+      <c r="AR260" t="n">
+        <v>186.5384615384615</v>
+      </c>
+      <c r="AS260" t="n">
+        <v>1.153846153846154</v>
+      </c>
+      <c r="AT260" t="n">
+        <v>73.38461538461539</v>
+      </c>
+      <c r="AU260" t="n">
+        <v>8673076.923076924</v>
+      </c>
+      <c r="AV260" t="n">
+        <v>76</v>
+      </c>
+      <c r="AW260" t="n">
+        <v>23.09523809523809</v>
+      </c>
+      <c r="AX260" t="n">
+        <v>178.1904761904762</v>
+      </c>
+      <c r="AY260" t="n">
+        <v>1.19047619047619</v>
+      </c>
+      <c r="AZ260" t="n">
+        <v>72.04761904761905</v>
+      </c>
+      <c r="BA260" t="n">
+        <v>7488095.238095238</v>
+      </c>
+      <c r="BB260" t="n">
+        <v>80.19047619047619</v>
+      </c>
+      <c r="BC260" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="BD260" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="BE260" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BF260" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG260" t="n">
+        <v>369</v>
+      </c>
+      <c r="BH260" t="n">
+        <v>39700000</v>
+      </c>
+      <c r="BI260" t="n">
+        <v>405</v>
+      </c>
+      <c r="BJ260" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="BK260" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="BL260" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM260" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN260" t="n">
+        <v>376</v>
+      </c>
+      <c r="BO260" t="n">
+        <v>62000000</v>
+      </c>
+      <c r="BP260" t="n">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>pjyqwZx3</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="n">
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>52305</v>
+      </c>
+      <c r="F261" t="n">
+        <v>52196</v>
+      </c>
+      <c r="G261" t="n">
+        <v>1</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="K261" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L261" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M261" t="n">
+        <v>22</v>
+      </c>
+      <c r="N261" t="n">
+        <v>78</v>
+      </c>
+      <c r="O261" t="n">
+        <v>3</v>
+      </c>
+      <c r="P261" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>1</v>
+      </c>
+      <c r="R261" t="n">
+        <v>5</v>
+      </c>
+      <c r="S261" t="n">
+        <v>15</v>
+      </c>
+      <c r="T261" t="n">
+        <v>16</v>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="W261" t="n">
+        <v>48</v>
+      </c>
+      <c r="X261" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA261" t="inlineStr"/>
+      <c r="AB261" t="inlineStr"/>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr"/>
+      <c r="AE261" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF261" t="n">
+        <v>186.6</v>
+      </c>
+      <c r="AG261" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH261" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="AI261" t="n">
+        <v>23880000</v>
+      </c>
+      <c r="AJ261" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="AK261" t="n">
+        <v>25.55555555555556</v>
+      </c>
+      <c r="AL261" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="AM261" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN261" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AO261" t="n">
+        <v>4811111.111111111</v>
+      </c>
+      <c r="AP261" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="AQ261" t="n">
+        <v>26.3125</v>
+      </c>
+      <c r="AR261" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AS261" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AT261" t="n">
+        <v>76.3125</v>
+      </c>
+      <c r="AU261" t="n">
+        <v>12568750</v>
+      </c>
+      <c r="AV261" t="n">
+        <v>78.3125</v>
+      </c>
+      <c r="AW261" t="n">
+        <v>21.22727272727273</v>
+      </c>
+      <c r="AX261" t="n">
+        <v>178.0909090909091</v>
+      </c>
+      <c r="AY261" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ261" t="n">
+        <v>67.95454545454545</v>
+      </c>
+      <c r="BA261" t="n">
+        <v>3354545.454545455</v>
+      </c>
+      <c r="BB261" t="n">
+        <v>78.13636363636364</v>
+      </c>
+      <c r="BC261" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="BD261" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="BE261" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF261" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG261" t="n">
+        <v>397</v>
+      </c>
+      <c r="BH261" t="n">
+        <v>166600000</v>
+      </c>
+      <c r="BI261" t="n">
+        <v>419</v>
+      </c>
+      <c r="BJ261" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="BK261" t="n">
+        <v>185</v>
+      </c>
+      <c r="BL261" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BM261" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN261" t="n">
+        <v>220</v>
+      </c>
+      <c r="BO261" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="BP261" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>tIUiyD7F</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="n">
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city ground
+  nottingham </t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>30404</v>
+      </c>
+      <c r="F262" t="n">
+        <v>29763</v>
+      </c>
+      <c r="G262" t="n">
+        <v>1</v>
+      </c>
+      <c r="H262" t="n">
+        <v>1</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="K262" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L262" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M262" t="n">
+        <v>54</v>
+      </c>
+      <c r="N262" t="n">
+        <v>47</v>
+      </c>
+      <c r="O262" t="n">
+        <v>14</v>
+      </c>
+      <c r="P262" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>8</v>
+      </c>
+      <c r="R262" t="n">
+        <v>5</v>
+      </c>
+      <c r="S262" t="n">
+        <v>18</v>
+      </c>
+      <c r="T262" t="n">
+        <v>9</v>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="W262" t="n">
+        <v>48</v>
+      </c>
+      <c r="X262" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA262" t="inlineStr"/>
+      <c r="AB262" t="inlineStr"/>
+      <c r="AC262" t="inlineStr"/>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="AE262" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AF262" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="AG262" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH262" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="AI262" t="n">
+        <v>10050000</v>
+      </c>
+      <c r="AJ262" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="AK262" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="AL262" t="n">
+        <v>179.5555555555555</v>
+      </c>
+      <c r="AM262" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN262" t="n">
+        <v>74.77777777777777</v>
+      </c>
+      <c r="AO262" t="n">
+        <v>8544444.444444444</v>
+      </c>
+      <c r="AP262" t="n">
+        <v>80.33333333333333</v>
+      </c>
+      <c r="AQ262" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="AR262" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="AS262" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT262" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AU262" t="n">
+        <v>8090000</v>
+      </c>
+      <c r="AV262" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="AW262" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AX262" t="n">
+        <v>182.35</v>
+      </c>
+      <c r="AY262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ262" t="n">
+        <v>73.45</v>
+      </c>
+      <c r="BA262" t="n">
+        <v>8025000</v>
+      </c>
+      <c r="BB262" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="BC262" t="inlineStr"/>
+      <c r="BD262" t="inlineStr"/>
+      <c r="BE262" t="inlineStr"/>
+      <c r="BF262" t="inlineStr"/>
+      <c r="BG262" t="inlineStr"/>
+      <c r="BH262" t="inlineStr"/>
+      <c r="BI262" t="inlineStr"/>
+      <c r="BJ262" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK262" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="BL262" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM262" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN262" t="n">
+        <v>232</v>
+      </c>
+      <c r="BO262" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="BP262" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>t4kJMDhM</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="n">
+        <v>45521.35416666666</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>29673</v>
+      </c>
+      <c r="F263" t="n">
+        <v>30014</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" t="n">
+        <v>2</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="K263" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L263" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M263" t="n">
+        <v>38</v>
+      </c>
+      <c r="N263" t="n">
+        <v>62</v>
+      </c>
+      <c r="O263" t="n">
+        <v>7</v>
+      </c>
+      <c r="P263" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>2</v>
+      </c>
+      <c r="R263" t="n">
+        <v>5</v>
+      </c>
+      <c r="S263" t="n">
+        <v>9</v>
+      </c>
+      <c r="T263" t="n">
+        <v>18</v>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="W263" t="n">
+        <v>48</v>
+      </c>
+      <c r="X263" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA263" t="inlineStr"/>
+      <c r="AB263" t="inlineStr"/>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="AE263" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>182</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH263" t="n">
+        <v>71.45454545454545</v>
+      </c>
+      <c r="AI263" t="n">
+        <v>3336363.636363636</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>76.27272727272727</v>
+      </c>
+      <c r="AK263" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AL263" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="AM263" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AN263" t="n">
+        <v>84</v>
+      </c>
+      <c r="AO263" t="n">
+        <v>55280000</v>
+      </c>
+      <c r="AP263" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="AQ263" t="n">
+        <v>25.38095238095238</v>
+      </c>
+      <c r="AR263" t="n">
+        <v>181.2380952380952</v>
+      </c>
+      <c r="AS263" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AT263" t="n">
+        <v>69.57142857142857</v>
+      </c>
+      <c r="AU263" t="n">
+        <v>2963095.238095238</v>
+      </c>
+      <c r="AV263" t="n">
+        <v>72.95238095238095</v>
+      </c>
+      <c r="AW263" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AX263" t="n">
+        <v>184.15</v>
+      </c>
+      <c r="AY263" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AZ263" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="BA263" t="n">
+        <v>30115000</v>
+      </c>
+      <c r="BB263" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="BC263" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="BD263" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="BE263" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF263" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG263" t="n">
+        <v>346</v>
+      </c>
+      <c r="BH263" t="n">
+        <v>10600000</v>
+      </c>
+      <c r="BI263" t="n">
+        <v>366</v>
+      </c>
+      <c r="BJ263" t="n">
+        <v>18</v>
+      </c>
+      <c r="BK263" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL263" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM263" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN263" t="n">
+        <v>62</v>
+      </c>
+      <c r="BO263" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="BP263" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>Kl1AOZN9</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="n">
+        <v>45520.66666666666</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>75635</v>
+      </c>
+      <c r="F264" t="n">
+        <v>73297</v>
+      </c>
+      <c r="G264" t="n">
+        <v>1</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="K264" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L264" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M264" t="n">
+        <v>55</v>
+      </c>
+      <c r="N264" t="n">
+        <v>45</v>
+      </c>
+      <c r="O264" t="n">
+        <v>14</v>
+      </c>
+      <c r="P264" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>5</v>
+      </c>
+      <c r="R264" t="n">
+        <v>2</v>
+      </c>
+      <c r="S264" t="n">
+        <v>12</v>
+      </c>
+      <c r="T264" t="n">
+        <v>10</v>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="W264" t="n">
+        <v>48</v>
+      </c>
+      <c r="X264" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA264" t="inlineStr"/>
+      <c r="AB264" t="inlineStr"/>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="AD264" t="inlineStr"/>
+      <c r="AE264" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH264" t="n">
+        <v>82</v>
+      </c>
+      <c r="AI264" t="n">
+        <v>39625000</v>
+      </c>
+      <c r="AJ264" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="AK264" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AL264" t="n">
+        <v>184</v>
+      </c>
+      <c r="AM264" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN264" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AO264" t="n">
+        <v>11410000</v>
+      </c>
+      <c r="AP264" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AQ264" t="n">
+        <v>25.53846153846154</v>
+      </c>
+      <c r="AR264" t="n">
+        <v>185.3846153846154</v>
+      </c>
+      <c r="AS264" t="n">
+        <v>1.769230769230769</v>
+      </c>
+      <c r="AT264" t="n">
+        <v>75.23076923076923</v>
+      </c>
+      <c r="AU264" t="n">
+        <v>11461538.46153846</v>
+      </c>
+      <c r="AV264" t="n">
+        <v>80.38461538461539</v>
+      </c>
+      <c r="AW264" t="n">
+        <v>26.81818181818182</v>
+      </c>
+      <c r="AX264" t="n">
+        <v>182.2727272727273</v>
+      </c>
+      <c r="AY264" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="AZ264" t="n">
+        <v>73.22727272727273</v>
+      </c>
+      <c r="BA264" t="n">
+        <v>5709090.909090909</v>
+      </c>
+      <c r="BB264" t="n">
+        <v>76.13636363636364</v>
+      </c>
+      <c r="BC264" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BD264" t="n">
+        <v>182</v>
+      </c>
+      <c r="BE264" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF264" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG264" t="n">
+        <v>316</v>
+      </c>
+      <c r="BH264" t="n">
+        <v>92000000</v>
+      </c>
+      <c r="BI264" t="n">
+        <v>333</v>
+      </c>
+      <c r="BJ264" t="inlineStr"/>
+      <c r="BK264" t="inlineStr"/>
+      <c r="BL264" t="inlineStr"/>
+      <c r="BM264" t="inlineStr"/>
+      <c r="BN264" t="inlineStr"/>
+      <c r="BO264" t="inlineStr"/>
+      <c r="BP264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>697ha3El</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="n">
+        <v>45518.66666666666</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backhouse a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">elland road
+  leeds </t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>37792</v>
+      </c>
+      <c r="F265" t="n">
+        <v>35150</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="n">
+        <v>3</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>6F0lvLNC</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="n">
+        <v>56</v>
+      </c>
+      <c r="N265" t="n">
+        <v>44</v>
+      </c>
+      <c r="O265" t="n">
+        <v>13</v>
+      </c>
+      <c r="P265" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>2</v>
+      </c>
+      <c r="R265" t="n">
+        <v>8</v>
+      </c>
+      <c r="S265" t="n">
+        <v>16</v>
+      </c>
+      <c r="T265" t="n">
+        <v>12</v>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="W265" t="n">
+        <v>48</v>
+      </c>
+      <c r="X265" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA265" t="inlineStr"/>
+      <c r="AB265" t="inlineStr"/>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="AE265" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>73</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>4787500</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>76.375</v>
+      </c>
+      <c r="AK265" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="AL265" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="AM265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN265" t="n">
+        <v>68.125</v>
+      </c>
+      <c r="AO265" t="n">
+        <v>1943750</v>
+      </c>
+      <c r="AP265" t="n">
+        <v>73.625</v>
+      </c>
+      <c r="AQ265" t="n">
+        <v>22.625</v>
+      </c>
+      <c r="AR265" t="n">
+        <v>183.4375</v>
+      </c>
+      <c r="AS265" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AT265" t="n">
+        <v>73.8125</v>
+      </c>
+      <c r="AU265" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="AV265" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW265" t="n">
+        <v>23.58823529411765</v>
+      </c>
+      <c r="AX265" t="n">
+        <v>181.2941176470588</v>
+      </c>
+      <c r="AY265" t="n">
+        <v>1.176470588235294</v>
+      </c>
+      <c r="AZ265" t="n">
+        <v>68.35294117647059</v>
+      </c>
+      <c r="BA265" t="n">
+        <v>2238235.294117647</v>
+      </c>
+      <c r="BB265" t="n">
+        <v>75.64705882352941</v>
+      </c>
+      <c r="BC265" t="inlineStr"/>
+      <c r="BD265" t="inlineStr"/>
+      <c r="BE265" t="inlineStr"/>
+      <c r="BF265" t="inlineStr"/>
+      <c r="BG265" t="inlineStr"/>
+      <c r="BH265" t="inlineStr"/>
+      <c r="BI265" t="inlineStr"/>
+      <c r="BJ265" t="inlineStr"/>
+      <c r="BK265" t="inlineStr"/>
+      <c r="BL265" t="inlineStr"/>
+      <c r="BM265" t="inlineStr"/>
+      <c r="BN265" t="inlineStr"/>
+      <c r="BO265" t="inlineStr"/>
+      <c r="BP265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="n">
+        <v>45518.65625</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nield t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mkm stadium
+  hull </t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>25586</v>
+      </c>
+      <c r="F266" t="n">
+        <v>9281</v>
+      </c>
+      <c r="G266" t="n">
+        <v>1</v>
+      </c>
+      <c r="H266" t="n">
+        <v>2</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>S66R0t75</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="n">
+        <v>59</v>
+      </c>
+      <c r="N266" t="n">
+        <v>41</v>
+      </c>
+      <c r="O266" t="n">
+        <v>12</v>
+      </c>
+      <c r="P266" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>4</v>
+      </c>
+      <c r="R266" t="n">
+        <v>3</v>
+      </c>
+      <c r="S266" t="n">
+        <v>15</v>
+      </c>
+      <c r="T266" t="n">
+        <v>10</v>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="W266" t="n">
+        <v>48</v>
+      </c>
+      <c r="X266" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA266" t="inlineStr"/>
+      <c r="AB266" t="inlineStr"/>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="AD266" t="inlineStr"/>
+      <c r="AE266" t="inlineStr"/>
+      <c r="AF266" t="inlineStr"/>
+      <c r="AG266" t="inlineStr"/>
+      <c r="AH266" t="inlineStr"/>
+      <c r="AI266" t="inlineStr"/>
+      <c r="AJ266" t="inlineStr"/>
+      <c r="AK266" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AM266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="AO266" t="n">
+        <v>725000</v>
+      </c>
+      <c r="AP266" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AQ266" t="n">
+        <v>24.17647058823529</v>
+      </c>
+      <c r="AR266" t="n">
+        <v>180.5882352941177</v>
+      </c>
+      <c r="AS266" t="n">
+        <v>1.176470588235294</v>
+      </c>
+      <c r="AT266" t="n">
+        <v>68.29411764705883</v>
+      </c>
+      <c r="AU266" t="n">
+        <v>2098529.411764706</v>
+      </c>
+      <c r="AV266" t="n">
+        <v>75.11764705882354</v>
+      </c>
+      <c r="AW266" t="n">
+        <v>23.38888888888889</v>
+      </c>
+      <c r="AX266" t="n">
+        <v>181.2777777777778</v>
+      </c>
+      <c r="AY266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ266" t="n">
+        <v>65.55555555555556</v>
+      </c>
+      <c r="BA266" t="n">
+        <v>1267500</v>
+      </c>
+      <c r="BB266" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="BC266" t="inlineStr"/>
+      <c r="BD266" t="inlineStr"/>
+      <c r="BE266" t="inlineStr"/>
+      <c r="BF266" t="inlineStr"/>
+      <c r="BG266" t="inlineStr"/>
+      <c r="BH266" t="inlineStr"/>
+      <c r="BI266" t="inlineStr"/>
+      <c r="BJ266" t="inlineStr"/>
+      <c r="BK266" t="inlineStr"/>
+      <c r="BL266" t="inlineStr"/>
+      <c r="BM266" t="inlineStr"/>
+      <c r="BN266" t="inlineStr"/>
+      <c r="BO266" t="inlineStr"/>
+      <c r="BP266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="n">
+        <v>45518.65625</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reeves t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">home park
+  plymouth </t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>17000</v>
+      </c>
+      <c r="F267" t="n">
+        <v>12058</v>
+      </c>
+      <c r="G267" t="n">
+        <v>3</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>jizXHcsM</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="n">
+        <v>71</v>
+      </c>
+      <c r="N267" t="n">
+        <v>29</v>
+      </c>
+      <c r="O267" t="n">
+        <v>33</v>
+      </c>
+      <c r="P267" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>8</v>
+      </c>
+      <c r="R267" t="n">
+        <v>2</v>
+      </c>
+      <c r="S267" t="n">
+        <v>13</v>
+      </c>
+      <c r="T267" t="n">
+        <v>20</v>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>WfXv1DCa</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>69Sy5B6h</t>
+        </is>
+      </c>
+      <c r="W267" t="n">
+        <v>48</v>
+      </c>
+      <c r="X267" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA267" t="inlineStr"/>
+      <c r="AB267" t="inlineStr"/>
+      <c r="AC267" t="inlineStr"/>
+      <c r="AD267" t="inlineStr"/>
+      <c r="AE267" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>67</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>1736111.111111111</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="AK267" t="inlineStr"/>
+      <c r="AL267" t="inlineStr"/>
+      <c r="AM267" t="inlineStr"/>
+      <c r="AN267" t="inlineStr"/>
+      <c r="AO267" t="inlineStr"/>
+      <c r="AP267" t="inlineStr"/>
+      <c r="AQ267" t="n">
+        <v>24.27777777777778</v>
+      </c>
+      <c r="AR267" t="n">
+        <v>181.9444444444445</v>
+      </c>
+      <c r="AS267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT267" t="n">
+        <v>67.94444444444444</v>
+      </c>
+      <c r="AU267" t="n">
+        <v>2138888.888888889</v>
+      </c>
+      <c r="AV267" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="AW267" t="inlineStr"/>
+      <c r="AX267" t="inlineStr"/>
+      <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr"/>
+      <c r="BA267" t="inlineStr"/>
+      <c r="BB267" t="inlineStr"/>
+      <c r="BC267" t="inlineStr"/>
+      <c r="BD267" t="inlineStr"/>
+      <c r="BE267" t="inlineStr"/>
+      <c r="BF267" t="inlineStr"/>
+      <c r="BG267" t="inlineStr"/>
+      <c r="BH267" t="inlineStr"/>
+      <c r="BI267" t="inlineStr"/>
+      <c r="BJ267" t="inlineStr"/>
+      <c r="BK267" t="inlineStr"/>
+      <c r="BL267" t="inlineStr"/>
+      <c r="BM267" t="inlineStr"/>
+      <c r="BN267" t="inlineStr"/>
+      <c r="BO267" t="inlineStr"/>
+      <c r="BP267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="n">
+        <v>45517.66666666666</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stroud k 
+  eng </t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bramall lane
+  sheffield </t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>32050</v>
+      </c>
+      <c r="F268" t="n">
+        <v>11446</v>
+      </c>
+      <c r="G268" t="n">
+        <v>4</v>
+      </c>
+      <c r="H268" t="n">
+        <v>2</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>IgO7K1ZA</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="n">
+        <v>66</v>
+      </c>
+      <c r="N268" t="n">
+        <v>34</v>
+      </c>
+      <c r="O268" t="n">
+        <v>21</v>
+      </c>
+      <c r="P268" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>8</v>
+      </c>
+      <c r="R268" t="n">
+        <v>6</v>
+      </c>
+      <c r="S268" t="n">
+        <v>7</v>
+      </c>
+      <c r="T268" t="n">
+        <v>12</v>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>WliJgncC</t>
+        </is>
+      </c>
+      <c r="W268" t="n">
+        <v>48</v>
+      </c>
+      <c r="X268" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA268" t="inlineStr"/>
+      <c r="AB268" t="inlineStr"/>
+      <c r="AC268" t="inlineStr"/>
+      <c r="AD268" t="inlineStr"/>
+      <c r="AE268" t="inlineStr"/>
+      <c r="AF268" t="inlineStr"/>
+      <c r="AG268" t="inlineStr"/>
+      <c r="AH268" t="inlineStr"/>
+      <c r="AI268" t="inlineStr"/>
+      <c r="AJ268" t="inlineStr"/>
+      <c r="AK268" t="inlineStr"/>
+      <c r="AL268" t="inlineStr"/>
+      <c r="AM268" t="inlineStr"/>
+      <c r="AN268" t="inlineStr"/>
+      <c r="AO268" t="inlineStr"/>
+      <c r="AP268" t="inlineStr"/>
+      <c r="AQ268" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AR268" t="n">
+        <v>178.7333333333333</v>
+      </c>
+      <c r="AS268" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT268" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="AU268" t="n">
+        <v>2351666.666666667</v>
+      </c>
+      <c r="AV268" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AW268" t="inlineStr"/>
+      <c r="AX268" t="inlineStr"/>
+      <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr"/>
+      <c r="BA268" t="inlineStr"/>
+      <c r="BB268" t="inlineStr"/>
+      <c r="BC268" t="inlineStr"/>
+      <c r="BD268" t="inlineStr"/>
+      <c r="BE268" t="inlineStr"/>
+      <c r="BF268" t="inlineStr"/>
+      <c r="BG268" t="inlineStr"/>
+      <c r="BH268" t="inlineStr"/>
+      <c r="BI268" t="inlineStr"/>
+      <c r="BJ268" t="inlineStr"/>
+      <c r="BK268" t="inlineStr"/>
+      <c r="BL268" t="inlineStr"/>
+      <c r="BM268" t="inlineStr"/>
+      <c r="BN268" t="inlineStr"/>
+      <c r="BO268" t="inlineStr"/>
+      <c r="BP268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jackson s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holker street
+  barrow in furness </t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F269" t="n">
+        <v>1711</v>
+      </c>
+      <c r="G269" t="n">
+        <v>3</v>
+      </c>
+      <c r="H269" t="n">
+        <v>2</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>KKJL7QXd</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>U3lM3y4e</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="n">
+        <v>43</v>
+      </c>
+      <c r="N269" t="n">
+        <v>57</v>
+      </c>
+      <c r="O269" t="n">
+        <v>20</v>
+      </c>
+      <c r="P269" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>6</v>
+      </c>
+      <c r="R269" t="n">
+        <v>6</v>
+      </c>
+      <c r="S269" t="n">
+        <v>10</v>
+      </c>
+      <c r="T269" t="n">
+        <v>8</v>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>joDBK9gn</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>QqM9cA4G</t>
+        </is>
+      </c>
+      <c r="W269" t="n">
+        <v>48</v>
+      </c>
+      <c r="X269" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA269" t="inlineStr"/>
+      <c r="AB269" t="inlineStr"/>
+      <c r="AC269" t="inlineStr"/>
+      <c r="AD269" t="inlineStr"/>
+      <c r="AE269" t="inlineStr"/>
+      <c r="AF269" t="inlineStr"/>
+      <c r="AG269" t="inlineStr"/>
+      <c r="AH269" t="inlineStr"/>
+      <c r="AI269" t="inlineStr"/>
+      <c r="AJ269" t="inlineStr"/>
+      <c r="AK269" t="inlineStr"/>
+      <c r="AL269" t="inlineStr"/>
+      <c r="AM269" t="inlineStr"/>
+      <c r="AN269" t="inlineStr"/>
+      <c r="AO269" t="inlineStr"/>
+      <c r="AP269" t="inlineStr"/>
+      <c r="AQ269" t="inlineStr"/>
+      <c r="AR269" t="inlineStr"/>
+      <c r="AS269" t="inlineStr"/>
+      <c r="AT269" t="inlineStr"/>
+      <c r="AU269" t="inlineStr"/>
+      <c r="AV269" t="inlineStr"/>
+      <c r="AW269" t="inlineStr"/>
+      <c r="AX269" t="inlineStr"/>
+      <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr"/>
+      <c r="BA269" t="inlineStr"/>
+      <c r="BB269" t="inlineStr"/>
+      <c r="BC269" t="inlineStr"/>
+      <c r="BD269" t="inlineStr"/>
+      <c r="BE269" t="inlineStr"/>
+      <c r="BF269" t="inlineStr"/>
+      <c r="BG269" t="inlineStr"/>
+      <c r="BH269" t="inlineStr"/>
+      <c r="BI269" t="inlineStr"/>
+      <c r="BJ269" t="inlineStr"/>
+      <c r="BK269" t="inlineStr"/>
+      <c r="BL269" t="inlineStr"/>
+      <c r="BM269" t="inlineStr"/>
+      <c r="BN269" t="inlineStr"/>
+      <c r="BO269" t="inlineStr"/>
+      <c r="BP269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">herczeg a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toughsheet community stadium
+  bolton </t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>28723</v>
+      </c>
+      <c r="F270" t="n">
+        <v>4131</v>
+      </c>
+      <c r="G270" t="n">
+        <v>2</v>
+      </c>
+      <c r="H270" t="n">
+        <v>1</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Or1bBrWD</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>t6G9wMZN</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="n">
+        <v>50</v>
+      </c>
+      <c r="N270" t="n">
+        <v>50</v>
+      </c>
+      <c r="O270" t="n">
+        <v>21</v>
+      </c>
+      <c r="P270" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>5</v>
+      </c>
+      <c r="R270" t="n">
+        <v>3</v>
+      </c>
+      <c r="S270" t="n">
+        <v>13</v>
+      </c>
+      <c r="T270" t="n">
+        <v>22</v>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>EosAlOi5</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>bZDu1Nqp</t>
+        </is>
+      </c>
+      <c r="W270" t="n">
+        <v>48</v>
+      </c>
+      <c r="X270" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA270" t="inlineStr"/>
+      <c r="AB270" t="inlineStr"/>
+      <c r="AC270" t="inlineStr"/>
+      <c r="AD270" t="inlineStr"/>
+      <c r="AE270" t="inlineStr"/>
+      <c r="AF270" t="inlineStr"/>
+      <c r="AG270" t="inlineStr"/>
+      <c r="AH270" t="inlineStr"/>
+      <c r="AI270" t="inlineStr"/>
+      <c r="AJ270" t="inlineStr"/>
+      <c r="AK270" t="inlineStr"/>
+      <c r="AL270" t="inlineStr"/>
+      <c r="AM270" t="inlineStr"/>
+      <c r="AN270" t="inlineStr"/>
+      <c r="AO270" t="inlineStr"/>
+      <c r="AP270" t="inlineStr"/>
+      <c r="AQ270" t="inlineStr"/>
+      <c r="AR270" t="inlineStr"/>
+      <c r="AS270" t="inlineStr"/>
+      <c r="AT270" t="inlineStr"/>
+      <c r="AU270" t="inlineStr"/>
+      <c r="AV270" t="inlineStr"/>
+      <c r="AW270" t="inlineStr"/>
+      <c r="AX270" t="inlineStr"/>
+      <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr"/>
+      <c r="BA270" t="inlineStr"/>
+      <c r="BB270" t="inlineStr"/>
+      <c r="BC270" t="inlineStr"/>
+      <c r="BD270" t="inlineStr"/>
+      <c r="BE270" t="inlineStr"/>
+      <c r="BF270" t="inlineStr"/>
+      <c r="BG270" t="inlineStr"/>
+      <c r="BH270" t="inlineStr"/>
+      <c r="BI270" t="inlineStr"/>
+      <c r="BJ270" t="inlineStr"/>
+      <c r="BK270" t="inlineStr"/>
+      <c r="BL270" t="inlineStr"/>
+      <c r="BM270" t="inlineStr"/>
+      <c r="BN270" t="inlineStr"/>
+      <c r="BO270" t="inlineStr"/>
+      <c r="BP270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ashton gate stadium
+  bristol </t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F271" t="n">
+        <v>10940</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="n">
+        <v>1</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>MahqU27I</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="n">
+        <v>53</v>
+      </c>
+      <c r="N271" t="n">
+        <v>47</v>
+      </c>
+      <c r="O271" t="n">
+        <v>16</v>
+      </c>
+      <c r="P271" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>6</v>
+      </c>
+      <c r="R271" t="n">
+        <v>4</v>
+      </c>
+      <c r="S271" t="n">
+        <v>9</v>
+      </c>
+      <c r="T271" t="n">
+        <v>10</v>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
+      <c r="W271" t="n">
+        <v>48</v>
+      </c>
+      <c r="X271" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA271" t="inlineStr"/>
+      <c r="AB271" t="inlineStr"/>
+      <c r="AC271" t="inlineStr"/>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="AE271" t="n">
+        <v>24.77777777777778</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>181.4444444444445</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH271" t="n">
+        <v>68.11111111111111</v>
+      </c>
+      <c r="AI271" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AJ271" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="AK271" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AL271" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AM271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN271" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AO271" t="n">
+        <v>2620000</v>
+      </c>
+      <c r="AP271" t="n">
+        <v>75</v>
+      </c>
+      <c r="AQ271" t="n">
+        <v>24.35714285714286</v>
+      </c>
+      <c r="AR271" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AS271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT271" t="n">
+        <v>67.92857142857143</v>
+      </c>
+      <c r="AU271" t="n">
+        <v>1914285.714285714</v>
+      </c>
+      <c r="AV271" t="n">
+        <v>74.21428571428571</v>
+      </c>
+      <c r="AW271" t="n">
+        <v>23.05555555555556</v>
+      </c>
+      <c r="AX271" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AY271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ271" t="n">
+        <v>70.11111111111111</v>
+      </c>
+      <c r="BA271" t="n">
+        <v>4223611.111111111</v>
+      </c>
+      <c r="BB271" t="n">
+        <v>76.66666666666667</v>
+      </c>
+      <c r="BC271" t="inlineStr"/>
+      <c r="BD271" t="inlineStr"/>
+      <c r="BE271" t="inlineStr"/>
+      <c r="BF271" t="inlineStr"/>
+      <c r="BG271" t="inlineStr"/>
+      <c r="BH271" t="inlineStr"/>
+      <c r="BI271" t="inlineStr"/>
+      <c r="BJ271" t="inlineStr"/>
+      <c r="BK271" t="inlineStr"/>
+      <c r="BL271" t="inlineStr"/>
+      <c r="BM271" t="inlineStr"/>
+      <c r="BN271" t="inlineStr"/>
+      <c r="BO271" t="inlineStr"/>
+      <c r="BP271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brook c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hayes lane
+  london </t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F272" t="n">
+        <v>3677</v>
+      </c>
+      <c r="G272" t="n">
+        <v>1</v>
+      </c>
+      <c r="H272" t="n">
+        <v>2</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Opdcd08Q</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>4KREuF43</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>45</v>
+      </c>
+      <c r="N272" t="n">
+        <v>55</v>
+      </c>
+      <c r="O272" t="n">
+        <v>13</v>
+      </c>
+      <c r="P272" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>4</v>
+      </c>
+      <c r="R272" t="n">
+        <v>6</v>
+      </c>
+      <c r="S272" t="n">
+        <v>7</v>
+      </c>
+      <c r="T272" t="n">
+        <v>13</v>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>dKVYSSZa</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>zHJOSLsG</t>
+        </is>
+      </c>
+      <c r="W272" t="n">
+        <v>48</v>
+      </c>
+      <c r="X272" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA272" t="inlineStr"/>
+      <c r="AB272" t="inlineStr"/>
+      <c r="AC272" t="inlineStr"/>
+      <c r="AD272" t="inlineStr"/>
+      <c r="AE272" t="inlineStr"/>
+      <c r="AF272" t="inlineStr"/>
+      <c r="AG272" t="inlineStr"/>
+      <c r="AH272" t="inlineStr"/>
+      <c r="AI272" t="inlineStr"/>
+      <c r="AJ272" t="inlineStr"/>
+      <c r="AK272" t="inlineStr"/>
+      <c r="AL272" t="inlineStr"/>
+      <c r="AM272" t="inlineStr"/>
+      <c r="AN272" t="inlineStr"/>
+      <c r="AO272" t="inlineStr"/>
+      <c r="AP272" t="inlineStr"/>
+      <c r="AQ272" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="AR272" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="AS272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT272" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="AU272" t="n">
+        <v>385000</v>
+      </c>
+      <c r="AV272" t="n">
+        <v>72</v>
+      </c>
+      <c r="AW272" t="inlineStr"/>
+      <c r="AX272" t="inlineStr"/>
+      <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr"/>
+      <c r="BA272" t="inlineStr"/>
+      <c r="BB272" t="inlineStr"/>
+      <c r="BC272" t="inlineStr"/>
+      <c r="BD272" t="inlineStr"/>
+      <c r="BE272" t="inlineStr"/>
+      <c r="BF272" t="inlineStr"/>
+      <c r="BG272" t="inlineStr"/>
+      <c r="BH272" t="inlineStr"/>
+      <c r="BI272" t="inlineStr"/>
+      <c r="BJ272" t="inlineStr"/>
+      <c r="BK272" t="inlineStr"/>
+      <c r="BL272" t="inlineStr"/>
+      <c r="BM272" t="inlineStr"/>
+      <c r="BN272" t="inlineStr"/>
+      <c r="BO272" t="inlineStr"/>
+      <c r="BP272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corlett m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pirelli stadium
+  burton upon trent </t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>6912</v>
+      </c>
+      <c r="F273" t="n">
+        <v>1522</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" t="n">
+        <v>4</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>nwCtJaJT</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>8EFIJthC</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>39</v>
+      </c>
+      <c r="N273" t="n">
+        <v>61</v>
+      </c>
+      <c r="O273" t="n">
+        <v>6</v>
+      </c>
+      <c r="P273" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>2</v>
+      </c>
+      <c r="R273" t="n">
+        <v>13</v>
+      </c>
+      <c r="S273" t="n">
+        <v>8</v>
+      </c>
+      <c r="T273" t="n">
+        <v>9</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>jRbkxQep</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>Sx94bg0H</t>
+        </is>
+      </c>
+      <c r="W273" t="n">
+        <v>48</v>
+      </c>
+      <c r="X273" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA273" t="inlineStr"/>
+      <c r="AB273" t="inlineStr"/>
+      <c r="AC273" t="inlineStr"/>
+      <c r="AD273" t="inlineStr"/>
+      <c r="AE273" t="inlineStr"/>
+      <c r="AF273" t="inlineStr"/>
+      <c r="AG273" t="inlineStr"/>
+      <c r="AH273" t="inlineStr"/>
+      <c r="AI273" t="inlineStr"/>
+      <c r="AJ273" t="inlineStr"/>
+      <c r="AK273" t="inlineStr"/>
+      <c r="AL273" t="inlineStr"/>
+      <c r="AM273" t="inlineStr"/>
+      <c r="AN273" t="inlineStr"/>
+      <c r="AO273" t="inlineStr"/>
+      <c r="AP273" t="inlineStr"/>
+      <c r="AQ273" t="inlineStr"/>
+      <c r="AR273" t="inlineStr"/>
+      <c r="AS273" t="inlineStr"/>
+      <c r="AT273" t="inlineStr"/>
+      <c r="AU273" t="inlineStr"/>
+      <c r="AV273" t="inlineStr"/>
+      <c r="AW273" t="n">
+        <v>26.22222222222222</v>
+      </c>
+      <c r="AX273" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AY273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ273" t="n">
+        <v>66.55555555555556</v>
+      </c>
+      <c r="BA273" t="n">
+        <v>1108333.333333333</v>
+      </c>
+      <c r="BB273" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="BC273" t="inlineStr"/>
+      <c r="BD273" t="inlineStr"/>
+      <c r="BE273" t="inlineStr"/>
+      <c r="BF273" t="inlineStr"/>
+      <c r="BG273" t="inlineStr"/>
+      <c r="BH273" t="inlineStr"/>
+      <c r="BI273" t="inlineStr"/>
+      <c r="BJ273" t="inlineStr"/>
+      <c r="BK273" t="inlineStr"/>
+      <c r="BL273" t="inlineStr"/>
+      <c r="BM273" t="inlineStr"/>
+      <c r="BN273" t="inlineStr"/>
+      <c r="BO273" t="inlineStr"/>
+      <c r="BP273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">howard p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abbey stadium
+  cambridge </t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>7937</v>
+      </c>
+      <c r="F274" t="n">
+        <v>4529</v>
+      </c>
+      <c r="G274" t="n">
+        <v>1</v>
+      </c>
+      <c r="H274" t="n">
+        <v>2</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>lnb8EJRp</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>57</v>
+      </c>
+      <c r="N274" t="n">
+        <v>43</v>
+      </c>
+      <c r="O274" t="n">
+        <v>17</v>
+      </c>
+      <c r="P274" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>4</v>
+      </c>
+      <c r="R274" t="n">
+        <v>4</v>
+      </c>
+      <c r="S274" t="n">
+        <v>10</v>
+      </c>
+      <c r="T274" t="n">
+        <v>15</v>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>QFc63Hf1</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="W274" t="n">
+        <v>48</v>
+      </c>
+      <c r="X274" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA274" t="inlineStr"/>
+      <c r="AB274" t="inlineStr"/>
+      <c r="AC274" t="inlineStr"/>
+      <c r="AD274" t="inlineStr"/>
+      <c r="AE274" t="inlineStr"/>
+      <c r="AF274" t="inlineStr"/>
+      <c r="AG274" t="inlineStr"/>
+      <c r="AH274" t="inlineStr"/>
+      <c r="AI274" t="inlineStr"/>
+      <c r="AJ274" t="inlineStr"/>
+      <c r="AK274" t="inlineStr"/>
+      <c r="AL274" t="inlineStr"/>
+      <c r="AM274" t="inlineStr"/>
+      <c r="AN274" t="inlineStr"/>
+      <c r="AO274" t="inlineStr"/>
+      <c r="AP274" t="inlineStr"/>
+      <c r="AQ274" t="inlineStr"/>
+      <c r="AR274" t="inlineStr"/>
+      <c r="AS274" t="inlineStr"/>
+      <c r="AT274" t="inlineStr"/>
+      <c r="AU274" t="inlineStr"/>
+      <c r="AV274" t="inlineStr"/>
+      <c r="AW274" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="AX274" t="n">
+        <v>184.5454545454545</v>
+      </c>
+      <c r="AY274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ274" t="n">
+        <v>68.72727272727273</v>
+      </c>
+      <c r="BA274" t="n">
+        <v>1704545.454545455</v>
+      </c>
+      <c r="BB274" t="n">
+        <v>72</v>
+      </c>
+      <c r="BC274" t="inlineStr"/>
+      <c r="BD274" t="inlineStr"/>
+      <c r="BE274" t="inlineStr"/>
+      <c r="BF274" t="inlineStr"/>
+      <c r="BG274" t="inlineStr"/>
+      <c r="BH274" t="inlineStr"/>
+      <c r="BI274" t="inlineStr"/>
+      <c r="BJ274" t="inlineStr"/>
+      <c r="BK274" t="inlineStr"/>
+      <c r="BL274" t="inlineStr"/>
+      <c r="BM274" t="inlineStr"/>
+      <c r="BN274" t="inlineStr"/>
+      <c r="BO274" t="inlineStr"/>
+      <c r="BP274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">breakspear c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>33280</v>
+      </c>
+      <c r="F275" t="n">
+        <v>5718</v>
+      </c>
+      <c r="G275" t="n">
+        <v>2</v>
+      </c>
+      <c r="H275" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>GILi6JC9</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>61</v>
+      </c>
+      <c r="N275" t="n">
+        <v>39</v>
+      </c>
+      <c r="O275" t="n">
+        <v>18</v>
+      </c>
+      <c r="P275" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>8</v>
+      </c>
+      <c r="R275" t="n">
+        <v>2</v>
+      </c>
+      <c r="S275" t="n">
+        <v>12</v>
+      </c>
+      <c r="T275" t="n">
+        <v>8</v>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>dSEBnGdt</t>
+        </is>
+      </c>
+      <c r="W275" t="n">
+        <v>48</v>
+      </c>
+      <c r="X275" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA275" t="inlineStr"/>
+      <c r="AB275" t="inlineStr"/>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr"/>
+      <c r="AE275" t="inlineStr"/>
+      <c r="AF275" t="inlineStr"/>
+      <c r="AG275" t="inlineStr"/>
+      <c r="AH275" t="inlineStr"/>
+      <c r="AI275" t="inlineStr"/>
+      <c r="AJ275" t="inlineStr"/>
+      <c r="AK275" t="inlineStr"/>
+      <c r="AL275" t="inlineStr"/>
+      <c r="AM275" t="inlineStr"/>
+      <c r="AN275" t="inlineStr"/>
+      <c r="AO275" t="inlineStr"/>
+      <c r="AP275" t="inlineStr"/>
+      <c r="AQ275" t="inlineStr"/>
+      <c r="AR275" t="inlineStr"/>
+      <c r="AS275" t="inlineStr"/>
+      <c r="AT275" t="inlineStr"/>
+      <c r="AU275" t="inlineStr"/>
+      <c r="AV275" t="inlineStr"/>
+      <c r="AW275" t="inlineStr"/>
+      <c r="AX275" t="inlineStr"/>
+      <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr"/>
+      <c r="BA275" t="inlineStr"/>
+      <c r="BB275" t="inlineStr"/>
+      <c r="BC275" t="inlineStr"/>
+      <c r="BD275" t="inlineStr"/>
+      <c r="BE275" t="inlineStr"/>
+      <c r="BF275" t="inlineStr"/>
+      <c r="BG275" t="inlineStr"/>
+      <c r="BH275" t="inlineStr"/>
+      <c r="BI275" t="inlineStr"/>
+      <c r="BJ275" t="inlineStr"/>
+      <c r="BK275" t="inlineStr"/>
+      <c r="BL275" t="inlineStr"/>
+      <c r="BM275" t="inlineStr"/>
+      <c r="BN275" t="inlineStr"/>
+      <c r="BO275" t="inlineStr"/>
+      <c r="BP275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chilowicz a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the valley
+  london </t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>27111</v>
+      </c>
+      <c r="F276" t="n">
+        <v>5899</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" t="n">
+        <v>1</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>fXf5mQ7t</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>SWk4muv7</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>36</v>
+      </c>
+      <c r="N276" t="n">
+        <v>64</v>
+      </c>
+      <c r="O276" t="n">
+        <v>11</v>
+      </c>
+      <c r="P276" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>1</v>
+      </c>
+      <c r="R276" t="n">
+        <v>7</v>
+      </c>
+      <c r="S276" t="n">
+        <v>24</v>
+      </c>
+      <c r="T276" t="n">
+        <v>8</v>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>UXQtpeyg</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>Uu6L6Igl</t>
+        </is>
+      </c>
+      <c r="W276" t="n">
+        <v>48</v>
+      </c>
+      <c r="X276" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA276" t="inlineStr"/>
+      <c r="AB276" t="inlineStr"/>
+      <c r="AC276" t="inlineStr"/>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr"/>
+      <c r="AF276" t="inlineStr"/>
+      <c r="AG276" t="inlineStr"/>
+      <c r="AH276" t="inlineStr"/>
+      <c r="AI276" t="inlineStr"/>
+      <c r="AJ276" t="inlineStr"/>
+      <c r="AK276" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="AL276" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="AM276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN276" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="AO276" t="n">
+        <v>1371875</v>
+      </c>
+      <c r="AP276" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AQ276" t="n">
+        <v>25.14285714285714</v>
+      </c>
+      <c r="AR276" t="n">
+        <v>180.4285714285714</v>
+      </c>
+      <c r="AS276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT276" t="n">
+        <v>67.28571428571429</v>
+      </c>
+      <c r="AU276" t="n">
+        <v>1428571.428571429</v>
+      </c>
+      <c r="AV276" t="n">
+        <v>70.42857142857143</v>
+      </c>
+      <c r="AW276" t="n">
+        <v>25.16666666666667</v>
+      </c>
+      <c r="AX276" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AY276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ276" t="n">
+        <v>69.58333333333333</v>
+      </c>
+      <c r="BA276" t="n">
+        <v>2468750</v>
+      </c>
+      <c r="BB276" t="n">
+        <v>73</v>
+      </c>
+      <c r="BC276" t="inlineStr"/>
+      <c r="BD276" t="inlineStr"/>
+      <c r="BE276" t="inlineStr"/>
+      <c r="BF276" t="inlineStr"/>
+      <c r="BG276" t="inlineStr"/>
+      <c r="BH276" t="inlineStr"/>
+      <c r="BI276" t="inlineStr"/>
+      <c r="BJ276" t="inlineStr"/>
+      <c r="BK276" t="inlineStr"/>
+      <c r="BL276" t="inlineStr"/>
+      <c r="BM276" t="inlineStr"/>
+      <c r="BN276" t="inlineStr"/>
+      <c r="BO276" t="inlineStr"/>
+      <c r="BP276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hair n 
+  eng </t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colchester community stadium
+  colchester </t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>10105</v>
+      </c>
+      <c r="F277" t="n">
+        <v>3123</v>
+      </c>
+      <c r="G277" t="n">
+        <v>3</v>
+      </c>
+      <c r="H277" t="n">
+        <v>2</v>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>xYu73rNn</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>EmlVDpVP</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>38</v>
+      </c>
+      <c r="N277" t="n">
+        <v>62</v>
+      </c>
+      <c r="O277" t="n">
+        <v>7</v>
+      </c>
+      <c r="P277" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>4</v>
+      </c>
+      <c r="R277" t="n">
+        <v>4</v>
+      </c>
+      <c r="S277" t="n">
+        <v>8</v>
+      </c>
+      <c r="T277" t="n">
+        <v>14</v>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>MiVxbVgA</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>dOPGcOzA</t>
+        </is>
+      </c>
+      <c r="W277" t="n">
+        <v>48</v>
+      </c>
+      <c r="X277" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z277" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA277" t="inlineStr"/>
+      <c r="AB277" t="inlineStr"/>
+      <c r="AC277" t="inlineStr"/>
+      <c r="AD277" t="inlineStr"/>
+      <c r="AE277" t="inlineStr"/>
+      <c r="AF277" t="inlineStr"/>
+      <c r="AG277" t="inlineStr"/>
+      <c r="AH277" t="inlineStr"/>
+      <c r="AI277" t="inlineStr"/>
+      <c r="AJ277" t="inlineStr"/>
+      <c r="AK277" t="inlineStr"/>
+      <c r="AL277" t="inlineStr"/>
+      <c r="AM277" t="inlineStr"/>
+      <c r="AN277" t="inlineStr"/>
+      <c r="AO277" t="inlineStr"/>
+      <c r="AP277" t="inlineStr"/>
+      <c r="AQ277" t="inlineStr"/>
+      <c r="AR277" t="inlineStr"/>
+      <c r="AS277" t="inlineStr"/>
+      <c r="AT277" t="inlineStr"/>
+      <c r="AU277" t="inlineStr"/>
+      <c r="AV277" t="inlineStr"/>
+      <c r="AW277" t="inlineStr"/>
+      <c r="AX277" t="inlineStr"/>
+      <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr"/>
+      <c r="BA277" t="inlineStr"/>
+      <c r="BB277" t="inlineStr"/>
+      <c r="BC277" t="inlineStr"/>
+      <c r="BD277" t="inlineStr"/>
+      <c r="BE277" t="inlineStr"/>
+      <c r="BF277" t="inlineStr"/>
+      <c r="BG277" t="inlineStr"/>
+      <c r="BH277" t="inlineStr"/>
+      <c r="BI277" t="inlineStr"/>
+      <c r="BJ277" t="inlineStr"/>
+      <c r="BK277" t="inlineStr"/>
+      <c r="BL277" t="inlineStr"/>
+      <c r="BM277" t="inlineStr"/>
+      <c r="BN277" t="inlineStr"/>
+      <c r="BO277" t="inlineStr"/>
+      <c r="BP277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkinson b 
+  eng </t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the broadfield stadium
+  crawley </t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>6134</v>
+      </c>
+      <c r="F278" t="n">
+        <v>2396</v>
+      </c>
+      <c r="G278" t="n">
+        <v>4</v>
+      </c>
+      <c r="H278" t="n">
+        <v>2</v>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>QVmLl54o</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>xSloasB8</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>64</v>
+      </c>
+      <c r="N278" t="n">
+        <v>36</v>
+      </c>
+      <c r="O278" t="n">
+        <v>15</v>
+      </c>
+      <c r="P278" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>9</v>
+      </c>
+      <c r="R278" t="n">
+        <v>6</v>
+      </c>
+      <c r="S278" t="n">
+        <v>12</v>
+      </c>
+      <c r="T278" t="n">
+        <v>8</v>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>COqtASrJ</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>r597nj0B</t>
+        </is>
+      </c>
+      <c r="W278" t="n">
+        <v>48</v>
+      </c>
+      <c r="X278" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y278" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z278" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA278" t="inlineStr"/>
+      <c r="AB278" t="inlineStr"/>
+      <c r="AC278" t="inlineStr"/>
+      <c r="AD278" t="inlineStr"/>
+      <c r="AE278" t="inlineStr"/>
+      <c r="AF278" t="inlineStr"/>
+      <c r="AG278" t="inlineStr"/>
+      <c r="AH278" t="inlineStr"/>
+      <c r="AI278" t="inlineStr"/>
+      <c r="AJ278" t="inlineStr"/>
+      <c r="AK278" t="inlineStr"/>
+      <c r="AL278" t="inlineStr"/>
+      <c r="AM278" t="inlineStr"/>
+      <c r="AN278" t="inlineStr"/>
+      <c r="AO278" t="inlineStr"/>
+      <c r="AP278" t="inlineStr"/>
+      <c r="AQ278" t="inlineStr"/>
+      <c r="AR278" t="inlineStr"/>
+      <c r="AS278" t="inlineStr"/>
+      <c r="AT278" t="inlineStr"/>
+      <c r="AU278" t="inlineStr"/>
+      <c r="AV278" t="inlineStr"/>
+      <c r="AW278" t="inlineStr"/>
+      <c r="AX278" t="inlineStr"/>
+      <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr"/>
+      <c r="BA278" t="inlineStr"/>
+      <c r="BB278" t="inlineStr"/>
+      <c r="BC278" t="inlineStr"/>
+      <c r="BD278" t="inlineStr"/>
+      <c r="BE278" t="inlineStr"/>
+      <c r="BF278" t="inlineStr"/>
+      <c r="BG278" t="inlineStr"/>
+      <c r="BH278" t="inlineStr"/>
+      <c r="BI278" t="inlineStr"/>
+      <c r="BJ278" t="inlineStr"/>
+      <c r="BK278" t="inlineStr"/>
+      <c r="BL278" t="inlineStr"/>
+      <c r="BM278" t="inlineStr"/>
+      <c r="BN278" t="inlineStr"/>
+      <c r="BO278" t="inlineStr"/>
+      <c r="BP278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doughty l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pride park
+  derby </t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>33597</v>
+      </c>
+      <c r="F279" t="n">
+        <v>8538</v>
+      </c>
+      <c r="G279" t="n">
+        <v>2</v>
+      </c>
+      <c r="H279" t="n">
+        <v>1</v>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Iug0YO0Q</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>dQIMIN5n</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>47</v>
+      </c>
+      <c r="N279" t="n">
+        <v>53</v>
+      </c>
+      <c r="O279" t="n">
+        <v>12</v>
+      </c>
+      <c r="P279" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>4</v>
+      </c>
+      <c r="R279" t="n">
+        <v>2</v>
+      </c>
+      <c r="S279" t="n">
+        <v>13</v>
+      </c>
+      <c r="T279" t="n">
+        <v>8</v>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>rNqEQiVq</t>
+        </is>
+      </c>
+      <c r="W279" t="n">
+        <v>48</v>
+      </c>
+      <c r="X279" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y279" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z279" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA279" t="inlineStr"/>
+      <c r="AB279" t="inlineStr"/>
+      <c r="AC279" t="inlineStr"/>
+      <c r="AD279" t="inlineStr"/>
+      <c r="AE279" t="inlineStr"/>
+      <c r="AF279" t="inlineStr"/>
+      <c r="AG279" t="inlineStr"/>
+      <c r="AH279" t="inlineStr"/>
+      <c r="AI279" t="inlineStr"/>
+      <c r="AJ279" t="inlineStr"/>
+      <c r="AK279" t="inlineStr"/>
+      <c r="AL279" t="inlineStr"/>
+      <c r="AM279" t="inlineStr"/>
+      <c r="AN279" t="inlineStr"/>
+      <c r="AO279" t="inlineStr"/>
+      <c r="AP279" t="inlineStr"/>
+      <c r="AQ279" t="n">
+        <v>27.42857142857143</v>
+      </c>
+      <c r="AR279" t="n">
+        <v>180.8571428571429</v>
+      </c>
+      <c r="AS279" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT279" t="n">
+        <v>65.85714285714286</v>
+      </c>
+      <c r="AU279" t="n">
+        <v>1057142.857142857</v>
+      </c>
+      <c r="AV279" t="n">
+        <v>67.85714285714286</v>
+      </c>
+      <c r="AW279" t="inlineStr"/>
+      <c r="AX279" t="inlineStr"/>
+      <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr"/>
+      <c r="BA279" t="inlineStr"/>
+      <c r="BB279" t="inlineStr"/>
+      <c r="BC279" t="inlineStr"/>
+      <c r="BD279" t="inlineStr"/>
+      <c r="BE279" t="inlineStr"/>
+      <c r="BF279" t="inlineStr"/>
+      <c r="BG279" t="inlineStr"/>
+      <c r="BH279" t="inlineStr"/>
+      <c r="BI279" t="inlineStr"/>
+      <c r="BJ279" t="inlineStr"/>
+      <c r="BK279" t="inlineStr"/>
+      <c r="BL279" t="inlineStr"/>
+      <c r="BM279" t="inlineStr"/>
+      <c r="BN279" t="inlineStr"/>
+      <c r="BO279" t="inlineStr"/>
+      <c r="BP279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kirk t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">highbury stadium
+  fleetwood </t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>5327</v>
+      </c>
+      <c r="F280" t="n">
+        <v>2611</v>
+      </c>
+      <c r="G280" t="n">
+        <v>2</v>
+      </c>
+      <c r="H280" t="n">
+        <v>1</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>tCZ3D68d</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>CCBWpzjj</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>25</v>
+      </c>
+      <c r="N280" t="n">
+        <v>75</v>
+      </c>
+      <c r="O280" t="n">
+        <v>5</v>
+      </c>
+      <c r="P280" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>3</v>
+      </c>
+      <c r="R280" t="n">
+        <v>3</v>
+      </c>
+      <c r="S280" t="n">
+        <v>11</v>
+      </c>
+      <c r="T280" t="n">
+        <v>15</v>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>d6KwHx8i</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="W280" t="n">
+        <v>48</v>
+      </c>
+      <c r="X280" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y280" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z280" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA280" t="inlineStr"/>
+      <c r="AB280" t="inlineStr"/>
+      <c r="AC280" t="inlineStr"/>
+      <c r="AD280" t="inlineStr"/>
+      <c r="AE280" t="inlineStr"/>
+      <c r="AF280" t="inlineStr"/>
+      <c r="AG280" t="inlineStr"/>
+      <c r="AH280" t="inlineStr"/>
+      <c r="AI280" t="inlineStr"/>
+      <c r="AJ280" t="inlineStr"/>
+      <c r="AK280" t="inlineStr"/>
+      <c r="AL280" t="inlineStr"/>
+      <c r="AM280" t="inlineStr"/>
+      <c r="AN280" t="inlineStr"/>
+      <c r="AO280" t="inlineStr"/>
+      <c r="AP280" t="inlineStr"/>
+      <c r="AQ280" t="inlineStr"/>
+      <c r="AR280" t="inlineStr"/>
+      <c r="AS280" t="inlineStr"/>
+      <c r="AT280" t="inlineStr"/>
+      <c r="AU280" t="inlineStr"/>
+      <c r="AV280" t="inlineStr"/>
+      <c r="AW280" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX280" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="AY280" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ280" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="BA280" t="n">
+        <v>1130000</v>
+      </c>
+      <c r="BB280" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="BC280" t="inlineStr"/>
+      <c r="BD280" t="inlineStr"/>
+      <c r="BE280" t="inlineStr"/>
+      <c r="BF280" t="inlineStr"/>
+      <c r="BG280" t="inlineStr"/>
+      <c r="BH280" t="inlineStr"/>
+      <c r="BI280" t="inlineStr"/>
+      <c r="BJ280" t="inlineStr"/>
+      <c r="BK280" t="inlineStr"/>
+      <c r="BL280" t="inlineStr"/>
+      <c r="BM280" t="inlineStr"/>
+      <c r="BN280" t="inlineStr"/>
+      <c r="BO280" t="inlineStr"/>
+      <c r="BP280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blundell park
+  cleethorpes </t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>9052</v>
+      </c>
+      <c r="F281" t="n">
+        <v>3082</v>
+      </c>
+      <c r="G281" t="n">
+        <v>2</v>
+      </c>
+      <c r="H281" t="n">
+        <v>1</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>OEaiS3za</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>bsc3EJ27</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>53</v>
+      </c>
+      <c r="N281" t="n">
+        <v>47</v>
+      </c>
+      <c r="O281" t="n">
+        <v>9</v>
+      </c>
+      <c r="P281" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>3</v>
+      </c>
+      <c r="R281" t="n">
+        <v>10</v>
+      </c>
+      <c r="S281" t="n">
+        <v>16</v>
+      </c>
+      <c r="T281" t="n">
+        <v>18</v>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>SGvTSGmc</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>zRvwlU0b</t>
+        </is>
+      </c>
+      <c r="W281" t="n">
+        <v>48</v>
+      </c>
+      <c r="X281" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y281" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z281" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA281" t="inlineStr"/>
+      <c r="AB281" t="inlineStr"/>
+      <c r="AC281" t="inlineStr"/>
+      <c r="AD281" t="inlineStr"/>
+      <c r="AE281" t="inlineStr"/>
+      <c r="AF281" t="inlineStr"/>
+      <c r="AG281" t="inlineStr"/>
+      <c r="AH281" t="inlineStr"/>
+      <c r="AI281" t="inlineStr"/>
+      <c r="AJ281" t="inlineStr"/>
+      <c r="AK281" t="inlineStr"/>
+      <c r="AL281" t="inlineStr"/>
+      <c r="AM281" t="inlineStr"/>
+      <c r="AN281" t="inlineStr"/>
+      <c r="AO281" t="inlineStr"/>
+      <c r="AP281" t="inlineStr"/>
+      <c r="AQ281" t="inlineStr"/>
+      <c r="AR281" t="inlineStr"/>
+      <c r="AS281" t="inlineStr"/>
+      <c r="AT281" t="inlineStr"/>
+      <c r="AU281" t="inlineStr"/>
+      <c r="AV281" t="inlineStr"/>
+      <c r="AW281" t="inlineStr"/>
+      <c r="AX281" t="inlineStr"/>
+      <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr"/>
+      <c r="BA281" t="inlineStr"/>
+      <c r="BB281" t="inlineStr"/>
+      <c r="BC281" t="inlineStr"/>
+      <c r="BD281" t="inlineStr"/>
+      <c r="BE281" t="inlineStr"/>
+      <c r="BF281" t="inlineStr"/>
+      <c r="BG281" t="inlineStr"/>
+      <c r="BH281" t="inlineStr"/>
+      <c r="BI281" t="inlineStr"/>
+      <c r="BJ281" t="inlineStr"/>
+      <c r="BK281" t="inlineStr"/>
+      <c r="BL281" t="inlineStr"/>
+      <c r="BM281" t="inlineStr"/>
+      <c r="BN281" t="inlineStr"/>
+      <c r="BO281" t="inlineStr"/>
+      <c r="BP281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mather s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">john smith s stadium
+  huddersfield </t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>24121</v>
+      </c>
+      <c r="F282" t="n">
+        <v>5111</v>
+      </c>
+      <c r="G282" t="n">
+        <v>3</v>
+      </c>
+      <c r="H282" t="n">
+        <v>0</v>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>zmKRcPKu</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="n">
+        <v>70</v>
+      </c>
+      <c r="N282" t="n">
+        <v>30</v>
+      </c>
+      <c r="O282" t="n">
+        <v>20</v>
+      </c>
+      <c r="P282" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>7</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" t="n">
+        <v>15</v>
+      </c>
+      <c r="T282" t="n">
+        <v>8</v>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>KGX2o9A5</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>C2z7zmRI</t>
+        </is>
+      </c>
+      <c r="W282" t="n">
+        <v>48</v>
+      </c>
+      <c r="X282" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y282" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z282" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA282" t="inlineStr"/>
+      <c r="AB282" t="inlineStr"/>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="AD282" t="inlineStr"/>
+      <c r="AE282" t="inlineStr"/>
+      <c r="AF282" t="inlineStr"/>
+      <c r="AG282" t="inlineStr"/>
+      <c r="AH282" t="inlineStr"/>
+      <c r="AI282" t="inlineStr"/>
+      <c r="AJ282" t="inlineStr"/>
+      <c r="AK282" t="inlineStr"/>
+      <c r="AL282" t="inlineStr"/>
+      <c r="AM282" t="inlineStr"/>
+      <c r="AN282" t="inlineStr"/>
+      <c r="AO282" t="inlineStr"/>
+      <c r="AP282" t="inlineStr"/>
+      <c r="AQ282" t="n">
+        <v>26.57894736842105</v>
+      </c>
+      <c r="AR282" t="n">
+        <v>179.7894736842105</v>
+      </c>
+      <c r="AS282" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT282" t="n">
+        <v>65.36842105263158</v>
+      </c>
+      <c r="AU282" t="n">
+        <v>905263.1578947369</v>
+      </c>
+      <c r="AV282" t="n">
+        <v>69.52631578947368</v>
+      </c>
+      <c r="AW282" t="inlineStr"/>
+      <c r="AX282" t="inlineStr"/>
+      <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr"/>
+      <c r="BA282" t="inlineStr"/>
+      <c r="BB282" t="inlineStr"/>
+      <c r="BC282" t="inlineStr"/>
+      <c r="BD282" t="inlineStr"/>
+      <c r="BE282" t="inlineStr"/>
+      <c r="BF282" t="inlineStr"/>
+      <c r="BG282" t="inlineStr"/>
+      <c r="BH282" t="inlineStr"/>
+      <c r="BI282" t="inlineStr"/>
+      <c r="BJ282" t="inlineStr"/>
+      <c r="BK282" t="inlineStr"/>
+      <c r="BL282" t="inlineStr"/>
+      <c r="BM282" t="inlineStr"/>
+      <c r="BN282" t="inlineStr"/>
+      <c r="BO282" t="inlineStr"/>
+      <c r="BP282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tallis s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lner stadium
+  lincoln </t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>10669</v>
+      </c>
+      <c r="F283" t="n">
+        <v>3507</v>
+      </c>
+      <c r="G283" t="n">
+        <v>1</v>
+      </c>
+      <c r="H283" t="n">
+        <v>2</v>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>hrHTRs5B</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>CQv5qrFt</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="n">
+        <v>65</v>
+      </c>
+      <c r="N283" t="n">
+        <v>35</v>
+      </c>
+      <c r="O283" t="n">
+        <v>18</v>
+      </c>
+      <c r="P283" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q283" t="n">
+        <v>3</v>
+      </c>
+      <c r="R283" t="n">
+        <v>4</v>
+      </c>
+      <c r="S283" t="n">
+        <v>15</v>
+      </c>
+      <c r="T283" t="n">
+        <v>8</v>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>zLZktkzH</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>ANwVL1Tp</t>
+        </is>
+      </c>
+      <c r="W283" t="n">
+        <v>48</v>
+      </c>
+      <c r="X283" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z283" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA283" t="inlineStr"/>
+      <c r="AB283" t="inlineStr"/>
+      <c r="AC283" t="inlineStr"/>
+      <c r="AD283" t="inlineStr"/>
+      <c r="AE283" t="inlineStr"/>
+      <c r="AF283" t="inlineStr"/>
+      <c r="AG283" t="inlineStr"/>
+      <c r="AH283" t="inlineStr"/>
+      <c r="AI283" t="inlineStr"/>
+      <c r="AJ283" t="inlineStr"/>
+      <c r="AK283" t="inlineStr"/>
+      <c r="AL283" t="inlineStr"/>
+      <c r="AM283" t="inlineStr"/>
+      <c r="AN283" t="inlineStr"/>
+      <c r="AO283" t="inlineStr"/>
+      <c r="AP283" t="inlineStr"/>
+      <c r="AQ283" t="inlineStr"/>
+      <c r="AR283" t="inlineStr"/>
+      <c r="AS283" t="inlineStr"/>
+      <c r="AT283" t="inlineStr"/>
+      <c r="AU283" t="inlineStr"/>
+      <c r="AV283" t="inlineStr"/>
+      <c r="AW283" t="inlineStr"/>
+      <c r="AX283" t="inlineStr"/>
+      <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr"/>
+      <c r="BA283" t="inlineStr"/>
+      <c r="BB283" t="inlineStr"/>
+      <c r="BC283" t="inlineStr"/>
+      <c r="BD283" t="inlineStr"/>
+      <c r="BE283" t="inlineStr"/>
+      <c r="BF283" t="inlineStr"/>
+      <c r="BG283" t="inlineStr"/>
+      <c r="BH283" t="inlineStr"/>
+      <c r="BI283" t="inlineStr"/>
+      <c r="BJ283" t="inlineStr"/>
+      <c r="BK283" t="inlineStr"/>
+      <c r="BL283" t="inlineStr"/>
+      <c r="BM283" t="inlineStr"/>
+      <c r="BN283" t="inlineStr"/>
+      <c r="BO283" t="inlineStr"/>
+      <c r="BP283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>xUXzYQFk</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bourne d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sixfields stadium
+  northampton </t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>7798</v>
+      </c>
+      <c r="F284" t="n">
+        <v>2012</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" t="n">
+        <v>2</v>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>l4P6dwRR</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>hl2V5JIl</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="n">
+        <v>65</v>
+      </c>
+      <c r="N284" t="n">
+        <v>35</v>
+      </c>
+      <c r="O284" t="n">
+        <v>7</v>
+      </c>
+      <c r="P284" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>1</v>
+      </c>
+      <c r="R284" t="n">
+        <v>8</v>
+      </c>
+      <c r="S284" t="n">
+        <v>9</v>
+      </c>
+      <c r="T284" t="n">
+        <v>12</v>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>YTUs4j89</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>65pf39vc</t>
+        </is>
+      </c>
+      <c r="W284" t="n">
+        <v>48</v>
+      </c>
+      <c r="X284" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y284" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z284" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA284" t="inlineStr"/>
+      <c r="AB284" t="inlineStr"/>
+      <c r="AC284" t="inlineStr"/>
+      <c r="AD284" t="inlineStr"/>
+      <c r="AE284" t="inlineStr"/>
+      <c r="AF284" t="inlineStr"/>
+      <c r="AG284" t="inlineStr"/>
+      <c r="AH284" t="inlineStr"/>
+      <c r="AI284" t="inlineStr"/>
+      <c r="AJ284" t="inlineStr"/>
+      <c r="AK284" t="inlineStr"/>
+      <c r="AL284" t="inlineStr"/>
+      <c r="AM284" t="inlineStr"/>
+      <c r="AN284" t="inlineStr"/>
+      <c r="AO284" t="inlineStr"/>
+      <c r="AP284" t="inlineStr"/>
+      <c r="AQ284" t="inlineStr"/>
+      <c r="AR284" t="inlineStr"/>
+      <c r="AS284" t="inlineStr"/>
+      <c r="AT284" t="inlineStr"/>
+      <c r="AU284" t="inlineStr"/>
+      <c r="AV284" t="inlineStr"/>
+      <c r="AW284" t="inlineStr"/>
+      <c r="AX284" t="inlineStr"/>
+      <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr"/>
+      <c r="BA284" t="inlineStr"/>
+      <c r="BB284" t="inlineStr"/>
+      <c r="BC284" t="inlineStr"/>
+      <c r="BD284" t="inlineStr"/>
+      <c r="BE284" t="inlineStr"/>
+      <c r="BF284" t="inlineStr"/>
+      <c r="BG284" t="inlineStr"/>
+      <c r="BH284" t="inlineStr"/>
+      <c r="BI284" t="inlineStr"/>
+      <c r="BJ284" t="inlineStr"/>
+      <c r="BK284" t="inlineStr"/>
+      <c r="BL284" t="inlineStr"/>
+      <c r="BM284" t="inlineStr"/>
+      <c r="BN284" t="inlineStr"/>
+      <c r="BO284" t="inlineStr"/>
+      <c r="BP284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gill s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carrow road
+  norwich </t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>27137</v>
+      </c>
+      <c r="F285" t="n">
+        <v>13054</v>
+      </c>
+      <c r="G285" t="n">
+        <v>4</v>
+      </c>
+      <c r="H285" t="n">
+        <v>3</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>ANwyQM2M</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="n">
+        <v>66</v>
+      </c>
+      <c r="N285" t="n">
+        <v>34</v>
+      </c>
+      <c r="O285" t="n">
+        <v>12</v>
+      </c>
+      <c r="P285" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>6</v>
+      </c>
+      <c r="R285" t="n">
+        <v>4</v>
+      </c>
+      <c r="S285" t="n">
+        <v>12</v>
+      </c>
+      <c r="T285" t="n">
+        <v>18</v>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>QVLHq5Li</t>
+        </is>
+      </c>
+      <c r="W285" t="n">
+        <v>48</v>
+      </c>
+      <c r="X285" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y285" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z285" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA285" t="inlineStr"/>
+      <c r="AB285" t="inlineStr"/>
+      <c r="AC285" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="AD285" t="inlineStr"/>
+      <c r="AE285" t="inlineStr"/>
+      <c r="AF285" t="inlineStr"/>
+      <c r="AG285" t="inlineStr"/>
+      <c r="AH285" t="inlineStr"/>
+      <c r="AI285" t="inlineStr"/>
+      <c r="AJ285" t="inlineStr"/>
+      <c r="AK285" t="inlineStr"/>
+      <c r="AL285" t="inlineStr"/>
+      <c r="AM285" t="inlineStr"/>
+      <c r="AN285" t="inlineStr"/>
+      <c r="AO285" t="inlineStr"/>
+      <c r="AP285" t="inlineStr"/>
+      <c r="AQ285" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="AR285" t="n">
+        <v>183.4166666666667</v>
+      </c>
+      <c r="AS285" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT285" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AU285" t="n">
+        <v>2225000</v>
+      </c>
+      <c r="AV285" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AW285" t="inlineStr"/>
+      <c r="AX285" t="inlineStr"/>
+      <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr"/>
+      <c r="BA285" t="inlineStr"/>
+      <c r="BB285" t="inlineStr"/>
+      <c r="BC285" t="inlineStr"/>
+      <c r="BD285" t="inlineStr"/>
+      <c r="BE285" t="inlineStr"/>
+      <c r="BF285" t="inlineStr"/>
+      <c r="BG285" t="inlineStr"/>
+      <c r="BH285" t="inlineStr"/>
+      <c r="BI285" t="inlineStr"/>
+      <c r="BJ285" t="inlineStr"/>
+      <c r="BK285" t="inlineStr"/>
+      <c r="BL285" t="inlineStr"/>
+      <c r="BM285" t="inlineStr"/>
+      <c r="BN285" t="inlineStr"/>
+      <c r="BO285" t="inlineStr"/>
+      <c r="BP285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kassam stadium
+  oxford </t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>12500</v>
+      </c>
+      <c r="F286" t="n">
+        <v>3693</v>
+      </c>
+      <c r="G286" t="n">
+        <v>2</v>
+      </c>
+      <c r="H286" t="n">
+        <v>0</v>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>vgOBT43c</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>tWeI85kh</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="n">
+        <v>51</v>
+      </c>
+      <c r="N286" t="n">
+        <v>49</v>
+      </c>
+      <c r="O286" t="n">
+        <v>10</v>
+      </c>
+      <c r="P286" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q286" t="n">
+        <v>7</v>
+      </c>
+      <c r="R286" t="n">
+        <v>6</v>
+      </c>
+      <c r="S286" t="n">
+        <v>13</v>
+      </c>
+      <c r="T286" t="n">
+        <v>7</v>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>plXkbArs</t>
+        </is>
+      </c>
+      <c r="W286" t="n">
+        <v>48</v>
+      </c>
+      <c r="X286" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z286" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA286" t="inlineStr"/>
+      <c r="AB286" t="inlineStr"/>
+      <c r="AC286" t="inlineStr"/>
+      <c r="AD286" t="inlineStr"/>
+      <c r="AE286" t="inlineStr"/>
+      <c r="AF286" t="inlineStr"/>
+      <c r="AG286" t="inlineStr"/>
+      <c r="AH286" t="inlineStr"/>
+      <c r="AI286" t="inlineStr"/>
+      <c r="AJ286" t="inlineStr"/>
+      <c r="AK286" t="inlineStr"/>
+      <c r="AL286" t="inlineStr"/>
+      <c r="AM286" t="inlineStr"/>
+      <c r="AN286" t="inlineStr"/>
+      <c r="AO286" t="inlineStr"/>
+      <c r="AP286" t="inlineStr"/>
+      <c r="AQ286" t="n">
+        <v>25.14285714285714</v>
+      </c>
+      <c r="AR286" t="n">
+        <v>182.5714285714286</v>
+      </c>
+      <c r="AS286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT286" t="n">
+        <v>67</v>
+      </c>
+      <c r="AU286" t="n">
+        <v>1417857.142857143</v>
+      </c>
+      <c r="AV286" t="n">
+        <v>72.57142857142857</v>
+      </c>
+      <c r="AW286" t="inlineStr"/>
+      <c r="AX286" t="inlineStr"/>
+      <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr"/>
+      <c r="BA286" t="inlineStr"/>
+      <c r="BB286" t="inlineStr"/>
+      <c r="BC286" t="inlineStr"/>
+      <c r="BD286" t="inlineStr"/>
+      <c r="BE286" t="inlineStr"/>
+      <c r="BF286" t="inlineStr"/>
+      <c r="BG286" t="inlineStr"/>
+      <c r="BH286" t="inlineStr"/>
+      <c r="BI286" t="inlineStr"/>
+      <c r="BJ286" t="inlineStr"/>
+      <c r="BK286" t="inlineStr"/>
+      <c r="BL286" t="inlineStr"/>
+      <c r="BM286" t="inlineStr"/>
+      <c r="BN286" t="inlineStr"/>
+      <c r="BO286" t="inlineStr"/>
+      <c r="BP286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whitestone d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fratton park
+  portsmouth </t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>21944</v>
+      </c>
+      <c r="F287" t="n">
+        <v>13913</v>
+      </c>
+      <c r="G287" t="n">
+        <v>0</v>
+      </c>
+      <c r="H287" t="n">
+        <v>1</v>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>zckREQFJ</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="n">
+        <v>59</v>
+      </c>
+      <c r="N287" t="n">
+        <v>41</v>
+      </c>
+      <c r="O287" t="n">
+        <v>7</v>
+      </c>
+      <c r="P287" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>2</v>
+      </c>
+      <c r="R287" t="n">
+        <v>2</v>
+      </c>
+      <c r="S287" t="n">
+        <v>13</v>
+      </c>
+      <c r="T287" t="n">
+        <v>12</v>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>djl0V3o6</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="W287" t="n">
+        <v>48</v>
+      </c>
+      <c r="X287" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z287" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA287" t="inlineStr"/>
+      <c r="AB287" t="inlineStr"/>
+      <c r="AC287" t="inlineStr"/>
+      <c r="AD287" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr"/>
+      <c r="AF287" t="inlineStr"/>
+      <c r="AG287" t="inlineStr"/>
+      <c r="AH287" t="inlineStr"/>
+      <c r="AI287" t="inlineStr"/>
+      <c r="AJ287" t="inlineStr"/>
+      <c r="AK287" t="inlineStr"/>
+      <c r="AL287" t="inlineStr"/>
+      <c r="AM287" t="inlineStr"/>
+      <c r="AN287" t="inlineStr"/>
+      <c r="AO287" t="inlineStr"/>
+      <c r="AP287" t="inlineStr"/>
+      <c r="AQ287" t="n">
+        <v>27.57142857142857</v>
+      </c>
+      <c r="AR287" t="n">
+        <v>176.4285714285714</v>
+      </c>
+      <c r="AS287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT287" t="n">
+        <v>68.85714285714286</v>
+      </c>
+      <c r="AU287" t="n">
+        <v>1514285.714285714</v>
+      </c>
+      <c r="AV287" t="n">
+        <v>72.14285714285714</v>
+      </c>
+      <c r="AW287" t="n">
+        <v>29.26315789473684</v>
+      </c>
+      <c r="AX287" t="n">
+        <v>180.9473684210526</v>
+      </c>
+      <c r="AY287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ287" t="n">
+        <v>69.36842105263158</v>
+      </c>
+      <c r="BA287" t="n">
+        <v>1378947.368421053</v>
+      </c>
+      <c r="BB287" t="n">
+        <v>70.21052631578948</v>
+      </c>
+      <c r="BC287" t="inlineStr"/>
+      <c r="BD287" t="inlineStr"/>
+      <c r="BE287" t="inlineStr"/>
+      <c r="BF287" t="inlineStr"/>
+      <c r="BG287" t="inlineStr"/>
+      <c r="BH287" t="inlineStr"/>
+      <c r="BI287" t="inlineStr"/>
+      <c r="BJ287" t="inlineStr"/>
+      <c r="BK287" t="inlineStr"/>
+      <c r="BL287" t="inlineStr"/>
+      <c r="BM287" t="inlineStr"/>
+      <c r="BN287" t="inlineStr"/>
+      <c r="BO287" t="inlineStr"/>
+      <c r="BP287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yates o 
+  eng </t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deepdale
+  preston </t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>23408</v>
+      </c>
+      <c r="F288" t="n">
+        <v>7231</v>
+      </c>
+      <c r="G288" t="n">
+        <v>2</v>
+      </c>
+      <c r="H288" t="n">
+        <v>0</v>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>x8IDVcbi</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="n">
+        <v>44</v>
+      </c>
+      <c r="N288" t="n">
+        <v>56</v>
+      </c>
+      <c r="O288" t="n">
+        <v>9</v>
+      </c>
+      <c r="P288" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>7</v>
+      </c>
+      <c r="R288" t="n">
+        <v>6</v>
+      </c>
+      <c r="S288" t="inlineStr"/>
+      <c r="T288" t="inlineStr"/>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>dtwAbyJ5</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>pYaUUJs1</t>
+        </is>
+      </c>
+      <c r="W288" t="n">
+        <v>48</v>
+      </c>
+      <c r="X288" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA288" t="inlineStr"/>
+      <c r="AB288" t="inlineStr"/>
+      <c r="AC288" t="inlineStr"/>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="AE288" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="AF288" t="n">
+        <v>185.8888888888889</v>
+      </c>
+      <c r="AG288" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AH288" t="n">
+        <v>71.22222222222223</v>
+      </c>
+      <c r="AI288" t="n">
+        <v>5530555.555555556</v>
+      </c>
+      <c r="AJ288" t="n">
+        <v>72.88888888888889</v>
+      </c>
+      <c r="AK288" t="n">
+        <v>21.55555555555556</v>
+      </c>
+      <c r="AL288" t="n">
+        <v>183.8888888888889</v>
+      </c>
+      <c r="AM288" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN288" t="n">
+        <v>65.11111111111111</v>
+      </c>
+      <c r="AO288" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="AP288" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AQ288" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AR288" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AS288" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT288" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AU288" t="n">
+        <v>3663750</v>
+      </c>
+      <c r="AV288" t="n">
+        <v>74.45</v>
+      </c>
+      <c r="AW288" t="n">
+        <v>20.53846153846154</v>
+      </c>
+      <c r="AX288" t="n">
+        <v>181.4615384615385</v>
+      </c>
+      <c r="AY288" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ288" t="n">
+        <v>63.76923076923077</v>
+      </c>
+      <c r="BA288" t="n">
+        <v>1623076.923076923</v>
+      </c>
+      <c r="BB288" t="n">
+        <v>73.23076923076923</v>
+      </c>
+      <c r="BC288" t="inlineStr"/>
+      <c r="BD288" t="inlineStr"/>
+      <c r="BE288" t="inlineStr"/>
+      <c r="BF288" t="inlineStr"/>
+      <c r="BG288" t="inlineStr"/>
+      <c r="BH288" t="inlineStr"/>
+      <c r="BI288" t="inlineStr"/>
+      <c r="BJ288" t="inlineStr"/>
+      <c r="BK288" t="inlineStr"/>
+      <c r="BL288" t="inlineStr"/>
+      <c r="BM288" t="inlineStr"/>
+      <c r="BN288" t="inlineStr"/>
+      <c r="BO288" t="inlineStr"/>
+      <c r="BP288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oldham s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aesseal new york stadium
+  rotherham </t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>12021</v>
+      </c>
+      <c r="F289" t="n">
+        <v>2182</v>
+      </c>
+      <c r="G289" t="n">
+        <v>2</v>
+      </c>
+      <c r="H289" t="n">
+        <v>1</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>KMfM7P4b</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>YacqHHdS</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="n">
+        <v>51</v>
+      </c>
+      <c r="N289" t="n">
+        <v>49</v>
+      </c>
+      <c r="O289" t="n">
+        <v>28</v>
+      </c>
+      <c r="P289" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>10</v>
+      </c>
+      <c r="R289" t="n">
+        <v>5</v>
+      </c>
+      <c r="S289" t="n">
+        <v>19</v>
+      </c>
+      <c r="T289" t="n">
+        <v>10</v>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>v9wEyhMe</t>
+        </is>
+      </c>
+      <c r="W289" t="n">
+        <v>48</v>
+      </c>
+      <c r="X289" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA289" t="inlineStr"/>
+      <c r="AB289" t="inlineStr"/>
+      <c r="AC289" t="inlineStr"/>
+      <c r="AD289" t="inlineStr"/>
+      <c r="AE289" t="inlineStr"/>
+      <c r="AF289" t="inlineStr"/>
+      <c r="AG289" t="inlineStr"/>
+      <c r="AH289" t="inlineStr"/>
+      <c r="AI289" t="inlineStr"/>
+      <c r="AJ289" t="inlineStr"/>
+      <c r="AK289" t="inlineStr"/>
+      <c r="AL289" t="inlineStr"/>
+      <c r="AM289" t="inlineStr"/>
+      <c r="AN289" t="inlineStr"/>
+      <c r="AO289" t="inlineStr"/>
+      <c r="AP289" t="inlineStr"/>
+      <c r="AQ289" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AR289" t="n">
+        <v>185</v>
+      </c>
+      <c r="AS289" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT289" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="AU289" t="n">
+        <v>1121875</v>
+      </c>
+      <c r="AV289" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="AW289" t="inlineStr"/>
+      <c r="AX289" t="inlineStr"/>
+      <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr"/>
+      <c r="BA289" t="inlineStr"/>
+      <c r="BB289" t="inlineStr"/>
+      <c r="BC289" t="inlineStr"/>
+      <c r="BD289" t="inlineStr"/>
+      <c r="BE289" t="inlineStr"/>
+      <c r="BF289" t="inlineStr"/>
+      <c r="BG289" t="inlineStr"/>
+      <c r="BH289" t="inlineStr"/>
+      <c r="BI289" t="inlineStr"/>
+      <c r="BJ289" t="inlineStr"/>
+      <c r="BK289" t="inlineStr"/>
+      <c r="BL289" t="inlineStr"/>
+      <c r="BM289" t="inlineStr"/>
+      <c r="BN289" t="inlineStr"/>
+      <c r="BO289" t="inlineStr"/>
+      <c r="BP289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stockbridge s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">peninsula stadium
+  salford </t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>5108</v>
+      </c>
+      <c r="F290" t="n">
+        <v>1328</v>
+      </c>
+      <c r="G290" t="n">
+        <v>0</v>
+      </c>
+      <c r="H290" t="n">
+        <v>2</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>W4AadhN3</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>hlzYDy5q</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="n">
+        <v>58</v>
+      </c>
+      <c r="N290" t="n">
+        <v>42</v>
+      </c>
+      <c r="O290" t="n">
+        <v>18</v>
+      </c>
+      <c r="P290" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>1</v>
+      </c>
+      <c r="R290" t="n">
+        <v>4</v>
+      </c>
+      <c r="S290" t="n">
+        <v>11</v>
+      </c>
+      <c r="T290" t="n">
+        <v>14</v>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>hbhFfSs6</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>pSZhI8SM</t>
+        </is>
+      </c>
+      <c r="W290" t="n">
+        <v>48</v>
+      </c>
+      <c r="X290" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA290" t="inlineStr"/>
+      <c r="AB290" t="inlineStr"/>
+      <c r="AC290" t="inlineStr"/>
+      <c r="AD290" t="inlineStr"/>
+      <c r="AE290" t="inlineStr"/>
+      <c r="AF290" t="inlineStr"/>
+      <c r="AG290" t="inlineStr"/>
+      <c r="AH290" t="inlineStr"/>
+      <c r="AI290" t="inlineStr"/>
+      <c r="AJ290" t="inlineStr"/>
+      <c r="AK290" t="inlineStr"/>
+      <c r="AL290" t="inlineStr"/>
+      <c r="AM290" t="inlineStr"/>
+      <c r="AN290" t="inlineStr"/>
+      <c r="AO290" t="inlineStr"/>
+      <c r="AP290" t="inlineStr"/>
+      <c r="AQ290" t="inlineStr"/>
+      <c r="AR290" t="inlineStr"/>
+      <c r="AS290" t="inlineStr"/>
+      <c r="AT290" t="inlineStr"/>
+      <c r="AU290" t="inlineStr"/>
+      <c r="AV290" t="inlineStr"/>
+      <c r="AW290" t="inlineStr"/>
+      <c r="AX290" t="inlineStr"/>
+      <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr"/>
+      <c r="BA290" t="inlineStr"/>
+      <c r="BB290" t="inlineStr"/>
+      <c r="BC290" t="inlineStr"/>
+      <c r="BD290" t="inlineStr"/>
+      <c r="BE290" t="inlineStr"/>
+      <c r="BF290" t="inlineStr"/>
+      <c r="BG290" t="inlineStr"/>
+      <c r="BH290" t="inlineStr"/>
+      <c r="BI290" t="inlineStr"/>
+      <c r="BJ290" t="inlineStr"/>
+      <c r="BK290" t="inlineStr"/>
+      <c r="BL290" t="inlineStr"/>
+      <c r="BM290" t="inlineStr"/>
+      <c r="BN290" t="inlineStr"/>
+      <c r="BO290" t="inlineStr"/>
+      <c r="BP290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">speedie b 
+  eng </t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the croud meadow
+  shrewsbury </t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>9877</v>
+      </c>
+      <c r="F291" t="n">
+        <v>2914</v>
+      </c>
+      <c r="G291" t="n">
+        <v>4</v>
+      </c>
+      <c r="H291" t="n">
+        <v>3</v>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>EqfQ6qK4</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>EwJVdqzn</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="n">
+        <v>38</v>
+      </c>
+      <c r="N291" t="n">
+        <v>62</v>
+      </c>
+      <c r="O291" t="n">
+        <v>16</v>
+      </c>
+      <c r="P291" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>7</v>
+      </c>
+      <c r="R291" t="n">
+        <v>5</v>
+      </c>
+      <c r="S291" t="n">
+        <v>15</v>
+      </c>
+      <c r="T291" t="n">
+        <v>5</v>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>EqN1jJFK</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>WMFFMcKh</t>
+        </is>
+      </c>
+      <c r="W291" t="n">
+        <v>48</v>
+      </c>
+      <c r="X291" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z291" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA291" t="inlineStr"/>
+      <c r="AB291" t="inlineStr"/>
+      <c r="AC291" t="inlineStr"/>
+      <c r="AD291" t="inlineStr"/>
+      <c r="AE291" t="inlineStr"/>
+      <c r="AF291" t="inlineStr"/>
+      <c r="AG291" t="inlineStr"/>
+      <c r="AH291" t="inlineStr"/>
+      <c r="AI291" t="inlineStr"/>
+      <c r="AJ291" t="inlineStr"/>
+      <c r="AK291" t="inlineStr"/>
+      <c r="AL291" t="inlineStr"/>
+      <c r="AM291" t="inlineStr"/>
+      <c r="AN291" t="inlineStr"/>
+      <c r="AO291" t="inlineStr"/>
+      <c r="AP291" t="inlineStr"/>
+      <c r="AQ291" t="inlineStr"/>
+      <c r="AR291" t="inlineStr"/>
+      <c r="AS291" t="inlineStr"/>
+      <c r="AT291" t="inlineStr"/>
+      <c r="AU291" t="inlineStr"/>
+      <c r="AV291" t="inlineStr"/>
+      <c r="AW291" t="inlineStr"/>
+      <c r="AX291" t="inlineStr"/>
+      <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr"/>
+      <c r="BA291" t="inlineStr"/>
+      <c r="BB291" t="inlineStr"/>
+      <c r="BC291" t="inlineStr"/>
+      <c r="BD291" t="inlineStr"/>
+      <c r="BE291" t="inlineStr"/>
+      <c r="BF291" t="inlineStr"/>
+      <c r="BG291" t="inlineStr"/>
+      <c r="BH291" t="inlineStr"/>
+      <c r="BI291" t="inlineStr"/>
+      <c r="BJ291" t="inlineStr"/>
+      <c r="BK291" t="inlineStr"/>
+      <c r="BL291" t="inlineStr"/>
+      <c r="BM291" t="inlineStr"/>
+      <c r="BN291" t="inlineStr"/>
+      <c r="BO291" t="inlineStr"/>
+      <c r="BP291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rock d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>21088</v>
+      </c>
+      <c r="F292" t="n">
+        <v>6019</v>
+      </c>
+      <c r="G292" t="n">
+        <v>3</v>
+      </c>
+      <c r="H292" t="n">
+        <v>1</v>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>WvZyDeKk</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="n">
+        <v>80</v>
+      </c>
+      <c r="N292" t="n">
+        <v>20</v>
+      </c>
+      <c r="O292" t="n">
+        <v>11</v>
+      </c>
+      <c r="P292" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>7</v>
+      </c>
+      <c r="R292" t="n">
+        <v>2</v>
+      </c>
+      <c r="S292" t="n">
+        <v>10</v>
+      </c>
+      <c r="T292" t="n">
+        <v>10</v>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>6oc32lpR</t>
+        </is>
+      </c>
+      <c r="W292" t="n">
+        <v>48</v>
+      </c>
+      <c r="X292" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z292" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA292" t="inlineStr"/>
+      <c r="AB292" t="inlineStr"/>
+      <c r="AC292" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="AD292" t="inlineStr"/>
+      <c r="AE292" t="inlineStr"/>
+      <c r="AF292" t="inlineStr"/>
+      <c r="AG292" t="inlineStr"/>
+      <c r="AH292" t="inlineStr"/>
+      <c r="AI292" t="inlineStr"/>
+      <c r="AJ292" t="inlineStr"/>
+      <c r="AK292" t="inlineStr"/>
+      <c r="AL292" t="inlineStr"/>
+      <c r="AM292" t="inlineStr"/>
+      <c r="AN292" t="inlineStr"/>
+      <c r="AO292" t="inlineStr"/>
+      <c r="AP292" t="inlineStr"/>
+      <c r="AQ292" t="n">
+        <v>24.15384615384615</v>
+      </c>
+      <c r="AR292" t="n">
+        <v>178.7692307692308</v>
+      </c>
+      <c r="AS292" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT292" t="n">
+        <v>67.07692307692308</v>
+      </c>
+      <c r="AU292" t="n">
+        <v>1532692.307692308</v>
+      </c>
+      <c r="AV292" t="n">
+        <v>72.30769230769231</v>
+      </c>
+      <c r="AW292" t="inlineStr"/>
+      <c r="AX292" t="inlineStr"/>
+      <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr"/>
+      <c r="BA292" t="inlineStr"/>
+      <c r="BB292" t="inlineStr"/>
+      <c r="BC292" t="inlineStr"/>
+      <c r="BD292" t="inlineStr"/>
+      <c r="BE292" t="inlineStr"/>
+      <c r="BF292" t="inlineStr"/>
+      <c r="BG292" t="inlineStr"/>
+      <c r="BH292" t="inlineStr"/>
+      <c r="BI292" t="inlineStr"/>
+      <c r="BJ292" t="inlineStr"/>
+      <c r="BK292" t="inlineStr"/>
+      <c r="BL292" t="inlineStr"/>
+      <c r="BM292" t="inlineStr"/>
+      <c r="BN292" t="inlineStr"/>
+      <c r="BO292" t="inlineStr"/>
+      <c r="BP292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simpson s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prenton park
+  birkenhead </t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>16587</v>
+      </c>
+      <c r="F293" t="n">
+        <v>2288</v>
+      </c>
+      <c r="G293" t="n">
+        <v>3</v>
+      </c>
+      <c r="H293" t="n">
+        <v>0</v>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>jVhkb1QE</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>6ZvdGuYf</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="n">
+        <v>47</v>
+      </c>
+      <c r="N293" t="n">
+        <v>53</v>
+      </c>
+      <c r="O293" t="n">
+        <v>13</v>
+      </c>
+      <c r="P293" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>4</v>
+      </c>
+      <c r="R293" t="n">
+        <v>4</v>
+      </c>
+      <c r="S293" t="n">
+        <v>10</v>
+      </c>
+      <c r="T293" t="n">
+        <v>14</v>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>2L1wFbM5</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>pQTmYFAh</t>
+        </is>
+      </c>
+      <c r="W293" t="n">
+        <v>48</v>
+      </c>
+      <c r="X293" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z293" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA293" t="inlineStr"/>
+      <c r="AB293" t="inlineStr"/>
+      <c r="AC293" t="inlineStr"/>
+      <c r="AD293" t="inlineStr"/>
+      <c r="AE293" t="inlineStr"/>
+      <c r="AF293" t="inlineStr"/>
+      <c r="AG293" t="inlineStr"/>
+      <c r="AH293" t="inlineStr"/>
+      <c r="AI293" t="inlineStr"/>
+      <c r="AJ293" t="inlineStr"/>
+      <c r="AK293" t="inlineStr"/>
+      <c r="AL293" t="inlineStr"/>
+      <c r="AM293" t="inlineStr"/>
+      <c r="AN293" t="inlineStr"/>
+      <c r="AO293" t="inlineStr"/>
+      <c r="AP293" t="inlineStr"/>
+      <c r="AQ293" t="inlineStr"/>
+      <c r="AR293" t="inlineStr"/>
+      <c r="AS293" t="inlineStr"/>
+      <c r="AT293" t="inlineStr"/>
+      <c r="AU293" t="inlineStr"/>
+      <c r="AV293" t="inlineStr"/>
+      <c r="AW293" t="inlineStr"/>
+      <c r="AX293" t="inlineStr"/>
+      <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr"/>
+      <c r="BA293" t="inlineStr"/>
+      <c r="BB293" t="inlineStr"/>
+      <c r="BC293" t="inlineStr"/>
+      <c r="BD293" t="inlineStr"/>
+      <c r="BE293" t="inlineStr"/>
+      <c r="BF293" t="inlineStr"/>
+      <c r="BG293" t="inlineStr"/>
+      <c r="BH293" t="inlineStr"/>
+      <c r="BI293" t="inlineStr"/>
+      <c r="BJ293" t="inlineStr"/>
+      <c r="BK293" t="inlineStr"/>
+      <c r="BL293" t="inlineStr"/>
+      <c r="BM293" t="inlineStr"/>
+      <c r="BN293" t="inlineStr"/>
+      <c r="BO293" t="inlineStr"/>
+      <c r="BP293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">miles j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bescot stadium
+  walsall </t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>11300</v>
+      </c>
+      <c r="F294" t="n">
+        <v>2352</v>
+      </c>
+      <c r="G294" t="n">
+        <v>2</v>
+      </c>
+      <c r="H294" t="n">
+        <v>1</v>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>YgrfcLuL</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>ve14a3l4</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="n">
+        <v>36</v>
+      </c>
+      <c r="N294" t="n">
+        <v>64</v>
+      </c>
+      <c r="O294" t="n">
+        <v>16</v>
+      </c>
+      <c r="P294" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>5</v>
+      </c>
+      <c r="R294" t="n">
+        <v>2</v>
+      </c>
+      <c r="S294" t="n">
+        <v>5</v>
+      </c>
+      <c r="T294" t="n">
+        <v>11</v>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>YTxm48Ng</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>prPkSBdq</t>
+        </is>
+      </c>
+      <c r="W294" t="n">
+        <v>48</v>
+      </c>
+      <c r="X294" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA294" t="inlineStr"/>
+      <c r="AB294" t="inlineStr"/>
+      <c r="AC294" t="inlineStr"/>
+      <c r="AD294" t="inlineStr"/>
+      <c r="AE294" t="inlineStr"/>
+      <c r="AF294" t="inlineStr"/>
+      <c r="AG294" t="inlineStr"/>
+      <c r="AH294" t="inlineStr"/>
+      <c r="AI294" t="inlineStr"/>
+      <c r="AJ294" t="inlineStr"/>
+      <c r="AK294" t="inlineStr"/>
+      <c r="AL294" t="inlineStr"/>
+      <c r="AM294" t="inlineStr"/>
+      <c r="AN294" t="inlineStr"/>
+      <c r="AO294" t="inlineStr"/>
+      <c r="AP294" t="inlineStr"/>
+      <c r="AQ294" t="inlineStr"/>
+      <c r="AR294" t="inlineStr"/>
+      <c r="AS294" t="inlineStr"/>
+      <c r="AT294" t="inlineStr"/>
+      <c r="AU294" t="inlineStr"/>
+      <c r="AV294" t="inlineStr"/>
+      <c r="AW294" t="inlineStr"/>
+      <c r="AX294" t="inlineStr"/>
+      <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr"/>
+      <c r="BA294" t="inlineStr"/>
+      <c r="BB294" t="inlineStr"/>
+      <c r="BC294" t="inlineStr"/>
+      <c r="BD294" t="inlineStr"/>
+      <c r="BE294" t="inlineStr"/>
+      <c r="BF294" t="inlineStr"/>
+      <c r="BG294" t="inlineStr"/>
+      <c r="BH294" t="inlineStr"/>
+      <c r="BI294" t="inlineStr"/>
+      <c r="BJ294" t="inlineStr"/>
+      <c r="BK294" t="inlineStr"/>
+      <c r="BL294" t="inlineStr"/>
+      <c r="BM294" t="inlineStr"/>
+      <c r="BN294" t="inlineStr"/>
+      <c r="BO294" t="inlineStr"/>
+      <c r="BP294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vicarage road
+  watford </t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>22200</v>
+      </c>
+      <c r="F295" t="n">
+        <v>6885</v>
+      </c>
+      <c r="G295" t="n">
+        <v>5</v>
+      </c>
+      <c r="H295" t="n">
+        <v>0</v>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>f9KDxtkU</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="n">
+        <v>54</v>
+      </c>
+      <c r="N295" t="n">
+        <v>46</v>
+      </c>
+      <c r="O295" t="n">
+        <v>26</v>
+      </c>
+      <c r="P295" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>12</v>
+      </c>
+      <c r="R295" t="n">
+        <v>2</v>
+      </c>
+      <c r="S295" t="n">
+        <v>10</v>
+      </c>
+      <c r="T295" t="n">
+        <v>7</v>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>SIMjXslg</t>
+        </is>
+      </c>
+      <c r="W295" t="n">
+        <v>48</v>
+      </c>
+      <c r="X295" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z295" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA295" t="inlineStr"/>
+      <c r="AB295" t="inlineStr"/>
+      <c r="AC295" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="AD295" t="inlineStr"/>
+      <c r="AE295" t="n">
+        <v>24.125</v>
+      </c>
+      <c r="AF295" t="n">
+        <v>182.875</v>
+      </c>
+      <c r="AG295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH295" t="n">
+        <v>68.375</v>
+      </c>
+      <c r="AI295" t="n">
+        <v>1962500</v>
+      </c>
+      <c r="AJ295" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="AK295" t="inlineStr"/>
+      <c r="AL295" t="inlineStr"/>
+      <c r="AM295" t="inlineStr"/>
+      <c r="AN295" t="inlineStr"/>
+      <c r="AO295" t="inlineStr"/>
+      <c r="AP295" t="inlineStr"/>
+      <c r="AQ295" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AR295" t="n">
+        <v>182.4166666666667</v>
+      </c>
+      <c r="AS295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT295" t="n">
+        <v>67.16666666666667</v>
+      </c>
+      <c r="AU295" t="n">
+        <v>1608333.333333333</v>
+      </c>
+      <c r="AV295" t="n">
+        <v>73.08333333333333</v>
+      </c>
+      <c r="AW295" t="inlineStr"/>
+      <c r="AX295" t="inlineStr"/>
+      <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr"/>
+      <c r="BA295" t="inlineStr"/>
+      <c r="BB295" t="inlineStr"/>
+      <c r="BC295" t="inlineStr"/>
+      <c r="BD295" t="inlineStr"/>
+      <c r="BE295" t="inlineStr"/>
+      <c r="BF295" t="inlineStr"/>
+      <c r="BG295" t="inlineStr"/>
+      <c r="BH295" t="inlineStr"/>
+      <c r="BI295" t="inlineStr"/>
+      <c r="BJ295" t="inlineStr"/>
+      <c r="BK295" t="inlineStr"/>
+      <c r="BL295" t="inlineStr"/>
+      <c r="BM295" t="inlineStr"/>
+      <c r="BN295" t="inlineStr"/>
+      <c r="BO295" t="inlineStr"/>
+      <c r="BP295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">finnie w 
+  eng </t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the brick community stadium
+  wigan </t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>25133</v>
+      </c>
+      <c r="F296" t="n">
+        <v>1990</v>
+      </c>
+      <c r="G296" t="n">
+        <v>1</v>
+      </c>
+      <c r="H296" t="n">
+        <v>2</v>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>MgHlK2Na</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>UNGEKMx6</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="n">
+        <v>49</v>
+      </c>
+      <c r="N296" t="n">
+        <v>51</v>
+      </c>
+      <c r="O296" t="n">
+        <v>9</v>
+      </c>
+      <c r="P296" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>4</v>
+      </c>
+      <c r="R296" t="n">
+        <v>5</v>
+      </c>
+      <c r="S296" t="n">
+        <v>14</v>
+      </c>
+      <c r="T296" t="n">
+        <v>16</v>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>tMOy79y1</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>bNLzN2wB</t>
+        </is>
+      </c>
+      <c r="W296" t="n">
+        <v>48</v>
+      </c>
+      <c r="X296" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y296" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z296" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA296" t="inlineStr"/>
+      <c r="AB296" t="inlineStr"/>
+      <c r="AC296" t="inlineStr"/>
+      <c r="AD296" t="inlineStr"/>
+      <c r="AE296" t="inlineStr"/>
+      <c r="AF296" t="inlineStr"/>
+      <c r="AG296" t="inlineStr"/>
+      <c r="AH296" t="inlineStr"/>
+      <c r="AI296" t="inlineStr"/>
+      <c r="AJ296" t="inlineStr"/>
+      <c r="AK296" t="inlineStr"/>
+      <c r="AL296" t="inlineStr"/>
+      <c r="AM296" t="inlineStr"/>
+      <c r="AN296" t="inlineStr"/>
+      <c r="AO296" t="inlineStr"/>
+      <c r="AP296" t="inlineStr"/>
+      <c r="AQ296" t="inlineStr"/>
+      <c r="AR296" t="inlineStr"/>
+      <c r="AS296" t="inlineStr"/>
+      <c r="AT296" t="inlineStr"/>
+      <c r="AU296" t="inlineStr"/>
+      <c r="AV296" t="inlineStr"/>
+      <c r="AW296" t="inlineStr"/>
+      <c r="AX296" t="inlineStr"/>
+      <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr"/>
+      <c r="BA296" t="inlineStr"/>
+      <c r="BB296" t="inlineStr"/>
+      <c r="BC296" t="inlineStr"/>
+      <c r="BD296" t="inlineStr"/>
+      <c r="BE296" t="inlineStr"/>
+      <c r="BF296" t="inlineStr"/>
+      <c r="BG296" t="inlineStr"/>
+      <c r="BH296" t="inlineStr"/>
+      <c r="BI296" t="inlineStr"/>
+      <c r="BJ296" t="inlineStr"/>
+      <c r="BK296" t="inlineStr"/>
+      <c r="BL296" t="inlineStr"/>
+      <c r="BM296" t="inlineStr"/>
+      <c r="BN296" t="inlineStr"/>
+      <c r="BO296" t="inlineStr"/>
+      <c r="BP296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>OMDVg8x9</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="n">
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toner b 
+  eng </t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brunton park
+  carlisle </t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>17949</v>
+      </c>
+      <c r="F297" t="n">
+        <v>4441</v>
+      </c>
+      <c r="G297" t="n">
+        <v>0</v>
+      </c>
+      <c r="H297" t="n">
+        <v>2</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>dUzTIwSF</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="n">
+        <v>37</v>
+      </c>
+      <c r="N297" t="n">
+        <v>63</v>
+      </c>
+      <c r="O297" t="n">
+        <v>7</v>
+      </c>
+      <c r="P297" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q297" t="n">
+        <v>3</v>
+      </c>
+      <c r="R297" t="n">
+        <v>7</v>
+      </c>
+      <c r="S297" t="n">
+        <v>14</v>
+      </c>
+      <c r="T297" t="n">
+        <v>12</v>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>2V2qkCe8</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="W297" t="n">
+        <v>48</v>
+      </c>
+      <c r="X297" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y297" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z297" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA297" t="inlineStr"/>
+      <c r="AB297" t="inlineStr"/>
+      <c r="AC297" t="inlineStr"/>
+      <c r="AD297" t="inlineStr"/>
+      <c r="AE297" t="inlineStr"/>
+      <c r="AF297" t="inlineStr"/>
+      <c r="AG297" t="inlineStr"/>
+      <c r="AH297" t="inlineStr"/>
+      <c r="AI297" t="inlineStr"/>
+      <c r="AJ297" t="inlineStr"/>
+      <c r="AK297" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL297" t="n">
+        <v>182</v>
+      </c>
+      <c r="AM297" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN297" t="n">
+        <v>67</v>
+      </c>
+      <c r="AO297" t="n">
+        <v>1915000</v>
+      </c>
+      <c r="AP297" t="n">
+        <v>74.22222222222223</v>
+      </c>
+      <c r="AQ297" t="inlineStr"/>
+      <c r="AR297" t="inlineStr"/>
+      <c r="AS297" t="inlineStr"/>
+      <c r="AT297" t="inlineStr"/>
+      <c r="AU297" t="inlineStr"/>
+      <c r="AV297" t="inlineStr"/>
+      <c r="AW297" t="n">
+        <v>24.125</v>
+      </c>
+      <c r="AX297" t="n">
+        <v>180.1875</v>
+      </c>
+      <c r="AY297" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ297" t="n">
+        <v>66.8125</v>
+      </c>
+      <c r="BA297" t="n">
+        <v>1587500</v>
+      </c>
+      <c r="BB297" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="BC297" t="inlineStr"/>
+      <c r="BD297" t="inlineStr"/>
+      <c r="BE297" t="inlineStr"/>
+      <c r="BF297" t="inlineStr"/>
+      <c r="BG297" t="inlineStr"/>
+      <c r="BH297" t="inlineStr"/>
+      <c r="BI297" t="inlineStr"/>
+      <c r="BJ297" t="inlineStr"/>
+      <c r="BK297" t="inlineStr"/>
+      <c r="BL297" t="inlineStr"/>
+      <c r="BM297" t="inlineStr"/>
+      <c r="BN297" t="inlineStr"/>
+      <c r="BO297" t="inlineStr"/>
+      <c r="BP297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="n">
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hicks c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisbane road
+  london </t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>9271</v>
+      </c>
+      <c r="F298" t="n">
+        <v>2141</v>
+      </c>
+      <c r="G298" t="n">
+        <v>4</v>
+      </c>
+      <c r="H298" t="n">
+        <v>1</v>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>KKyYcus9</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>ChwgcrNJ</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="n">
+        <v>48</v>
+      </c>
+      <c r="N298" t="n">
+        <v>52</v>
+      </c>
+      <c r="O298" t="n">
+        <v>12</v>
+      </c>
+      <c r="P298" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>6</v>
+      </c>
+      <c r="R298" t="n">
+        <v>1</v>
+      </c>
+      <c r="S298" t="n">
+        <v>17</v>
+      </c>
+      <c r="T298" t="n">
+        <v>7</v>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>C6Wq1Q6e</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>6watkf6m</t>
+        </is>
+      </c>
+      <c r="W298" t="n">
+        <v>48</v>
+      </c>
+      <c r="X298" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y298" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z298" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA298" t="inlineStr"/>
+      <c r="AB298" t="inlineStr"/>
+      <c r="AC298" t="inlineStr"/>
+      <c r="AD298" t="inlineStr"/>
+      <c r="AE298" t="inlineStr"/>
+      <c r="AF298" t="inlineStr"/>
+      <c r="AG298" t="inlineStr"/>
+      <c r="AH298" t="inlineStr"/>
+      <c r="AI298" t="inlineStr"/>
+      <c r="AJ298" t="inlineStr"/>
+      <c r="AK298" t="inlineStr"/>
+      <c r="AL298" t="inlineStr"/>
+      <c r="AM298" t="inlineStr"/>
+      <c r="AN298" t="inlineStr"/>
+      <c r="AO298" t="inlineStr"/>
+      <c r="AP298" t="inlineStr"/>
+      <c r="AQ298" t="n">
+        <v>20.42857142857143</v>
+      </c>
+      <c r="AR298" t="n">
+        <v>179.2857142857143</v>
+      </c>
+      <c r="AS298" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT298" t="n">
+        <v>59.71428571428572</v>
+      </c>
+      <c r="AU298" t="n">
+        <v>675000</v>
+      </c>
+      <c r="AV298" t="n">
+        <v>71.28571428571429</v>
+      </c>
+      <c r="AW298" t="inlineStr"/>
+      <c r="AX298" t="inlineStr"/>
+      <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr"/>
+      <c r="BA298" t="inlineStr"/>
+      <c r="BB298" t="inlineStr"/>
+      <c r="BC298" t="inlineStr"/>
+      <c r="BD298" t="inlineStr"/>
+      <c r="BE298" t="inlineStr"/>
+      <c r="BF298" t="inlineStr"/>
+      <c r="BG298" t="inlineStr"/>
+      <c r="BH298" t="inlineStr"/>
+      <c r="BI298" t="inlineStr"/>
+      <c r="BJ298" t="inlineStr"/>
+      <c r="BK298" t="inlineStr"/>
+      <c r="BL298" t="inlineStr"/>
+      <c r="BM298" t="inlineStr"/>
+      <c r="BN298" t="inlineStr"/>
+      <c r="BO298" t="inlineStr"/>
+      <c r="BP298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="n">
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joyce r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edgeley park
+  stockport </t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>10841</v>
+      </c>
+      <c r="F299" t="n">
+        <v>5790</v>
+      </c>
+      <c r="G299" t="n">
+        <v>1</v>
+      </c>
+      <c r="H299" t="n">
+        <v>6</v>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>IX6WjNvr</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="n">
+        <v>26</v>
+      </c>
+      <c r="N299" t="n">
+        <v>74</v>
+      </c>
+      <c r="O299" t="n">
+        <v>3</v>
+      </c>
+      <c r="P299" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>1</v>
+      </c>
+      <c r="R299" t="n">
+        <v>12</v>
+      </c>
+      <c r="S299" t="n">
+        <v>6</v>
+      </c>
+      <c r="T299" t="n">
+        <v>3</v>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>zsU8tQ8I</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="W299" t="n">
+        <v>48</v>
+      </c>
+      <c r="X299" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA299" t="inlineStr"/>
+      <c r="AB299" t="inlineStr"/>
+      <c r="AC299" t="inlineStr"/>
+      <c r="AD299" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="AE299" t="inlineStr"/>
+      <c r="AF299" t="inlineStr"/>
+      <c r="AG299" t="inlineStr"/>
+      <c r="AH299" t="inlineStr"/>
+      <c r="AI299" t="inlineStr"/>
+      <c r="AJ299" t="inlineStr"/>
+      <c r="AK299" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AL299" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="AM299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN299" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AO299" t="n">
+        <v>2220000</v>
+      </c>
+      <c r="AP299" t="n">
+        <v>73</v>
+      </c>
+      <c r="AQ299" t="inlineStr"/>
+      <c r="AR299" t="inlineStr"/>
+      <c r="AS299" t="inlineStr"/>
+      <c r="AT299" t="inlineStr"/>
+      <c r="AU299" t="inlineStr"/>
+      <c r="AV299" t="inlineStr"/>
+      <c r="AW299" t="n">
+        <v>26.44444444444444</v>
+      </c>
+      <c r="AX299" t="n">
+        <v>182.2222222222222</v>
+      </c>
+      <c r="AY299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ299" t="n">
+        <v>68.16666666666667</v>
+      </c>
+      <c r="BA299" t="n">
+        <v>1675000</v>
+      </c>
+      <c r="BB299" t="n">
+        <v>71.94444444444444</v>
+      </c>
+      <c r="BC299" t="inlineStr"/>
+      <c r="BD299" t="inlineStr"/>
+      <c r="BE299" t="inlineStr"/>
+      <c r="BF299" t="inlineStr"/>
+      <c r="BG299" t="inlineStr"/>
+      <c r="BH299" t="inlineStr"/>
+      <c r="BI299" t="inlineStr"/>
+      <c r="BJ299" t="inlineStr"/>
+      <c r="BK299" t="inlineStr"/>
+      <c r="BL299" t="inlineStr"/>
+      <c r="BM299" t="inlineStr"/>
+      <c r="BN299" t="inlineStr"/>
+      <c r="BO299" t="inlineStr"/>
+      <c r="BP299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>fcYYQ80U</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="n">
+        <v>45522.33333333334</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whitestone d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium of light
+  sunderland </t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>48707</v>
+      </c>
+      <c r="F300" t="n">
+        <v>40022</v>
+      </c>
+      <c r="G300" t="n">
+        <v>4</v>
+      </c>
+      <c r="H300" t="n">
+        <v>0</v>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="n">
+        <v>49</v>
+      </c>
+      <c r="N300" t="n">
+        <v>51</v>
+      </c>
+      <c r="O300" t="n">
+        <v>16</v>
+      </c>
+      <c r="P300" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>7</v>
+      </c>
+      <c r="R300" t="n">
+        <v>3</v>
+      </c>
+      <c r="S300" t="n">
+        <v>9</v>
+      </c>
+      <c r="T300" t="n">
+        <v>11</v>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>pYaUUJs1</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="W300" t="n">
+        <v>48</v>
+      </c>
+      <c r="X300" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y300" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z300" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA300" t="inlineStr"/>
+      <c r="AB300" t="inlineStr"/>
+      <c r="AC300" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="AD300" t="inlineStr"/>
+      <c r="AE300" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF300" t="n">
+        <v>182</v>
+      </c>
+      <c r="AG300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH300" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="AI300" t="n">
+        <v>2553125</v>
+      </c>
+      <c r="AJ300" t="n">
+        <v>76.875</v>
+      </c>
+      <c r="AK300" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AL300" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AM300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN300" t="n">
+        <v>68.375</v>
+      </c>
+      <c r="AO300" t="n">
+        <v>1634375</v>
+      </c>
+      <c r="AP300" t="n">
+        <v>73.125</v>
+      </c>
+      <c r="AQ300" t="n">
+        <v>21.52941176470588</v>
+      </c>
+      <c r="AR300" t="n">
+        <v>180.8823529411765</v>
+      </c>
+      <c r="AS300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT300" t="n">
+        <v>65.88235294117646</v>
+      </c>
+      <c r="AU300" t="n">
+        <v>1682352.941176471</v>
+      </c>
+      <c r="AV300" t="n">
+        <v>74.29411764705883</v>
+      </c>
+      <c r="AW300" t="n">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="AX300" t="n">
+        <v>182.5454545454545</v>
+      </c>
+      <c r="AY300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ300" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="BA300" t="n">
+        <v>1146590.909090909</v>
+      </c>
+      <c r="BB300" t="n">
+        <v>69.31818181818181</v>
+      </c>
+      <c r="BC300" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD300" t="n">
+        <v>180</v>
+      </c>
+      <c r="BE300" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF300" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG300" t="n">
+        <v>272</v>
+      </c>
+      <c r="BH300" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="BI300" t="n">
+        <v>311</v>
+      </c>
+      <c r="BJ300" t="n">
+        <v>35</v>
+      </c>
+      <c r="BK300" t="n">
+        <v>193</v>
+      </c>
+      <c r="BL300" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM300" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN300" t="n">
+        <v>69</v>
+      </c>
+      <c r="BO300" t="n">
+        <v>150000</v>
+      </c>
+      <c r="BP300" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>vm3yIDHa</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="n">
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gill s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ashton gate stadium
+  bristol </t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F301" t="n">
+        <v>20733</v>
+      </c>
+      <c r="G301" t="n">
+        <v>4</v>
+      </c>
+      <c r="H301" t="n">
+        <v>3</v>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>MahqU27I</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="n">
+        <v>61</v>
+      </c>
+      <c r="N301" t="n">
+        <v>39</v>
+      </c>
+      <c r="O301" t="n">
+        <v>13</v>
+      </c>
+      <c r="P301" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>7</v>
+      </c>
+      <c r="R301" t="n">
+        <v>4</v>
+      </c>
+      <c r="S301" t="n">
+        <v>11</v>
+      </c>
+      <c r="T301" t="n">
+        <v>12</v>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="W301" t="n">
+        <v>48</v>
+      </c>
+      <c r="X301" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y301" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z301" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA301" t="inlineStr"/>
+      <c r="AB301" t="inlineStr"/>
+      <c r="AC301" t="inlineStr"/>
+      <c r="AD301" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="AE301" t="n">
+        <v>23.625</v>
+      </c>
+      <c r="AF301" t="n">
+        <v>182.625</v>
+      </c>
+      <c r="AG301" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH301" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AI301" t="n">
+        <v>2075000</v>
+      </c>
+      <c r="AJ301" t="n">
+        <v>74.625</v>
+      </c>
+      <c r="AK301" t="n">
+        <v>28.11111111111111</v>
+      </c>
+      <c r="AL301" t="n">
+        <v>178.7777777777778</v>
+      </c>
+      <c r="AM301" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN301" t="n">
+        <v>69.11111111111111</v>
+      </c>
+      <c r="AO301" t="n">
+        <v>1491666.666666667</v>
+      </c>
+      <c r="AP301" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AQ301" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR301" t="n">
+        <v>178.9333333333333</v>
+      </c>
+      <c r="AS301" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT301" t="n">
+        <v>66.53333333333333</v>
+      </c>
+      <c r="AU301" t="n">
+        <v>1681666.666666667</v>
+      </c>
+      <c r="AV301" t="n">
+        <v>74.33333333333333</v>
+      </c>
+      <c r="AW301" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AX301" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="AY301" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ301" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="BA301" t="n">
+        <v>1048333.333333333</v>
+      </c>
+      <c r="BB301" t="n">
+        <v>71.86666666666666</v>
+      </c>
+      <c r="BC301" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD301" t="n">
+        <v>187</v>
+      </c>
+      <c r="BE301" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF301" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG301" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH301" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="BI301" t="n">
+        <v>73</v>
+      </c>
+      <c r="BJ301" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK301" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="BL301" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM301" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN301" t="n">
+        <v>287</v>
+      </c>
+      <c r="BO301" t="n">
+        <v>14800000</v>
+      </c>
+      <c r="BP301" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>KxZpVZPG</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="n">
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">salisbury m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turf moor
+  burnley </t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>22546</v>
+      </c>
+      <c r="F302" t="n">
+        <v>19759</v>
+      </c>
+      <c r="G302" t="n">
+        <v>5</v>
+      </c>
+      <c r="H302" t="n">
+        <v>0</v>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="n">
+        <v>50</v>
+      </c>
+      <c r="N302" t="n">
+        <v>50</v>
+      </c>
+      <c r="O302" t="n">
+        <v>10</v>
+      </c>
+      <c r="P302" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>4</v>
+      </c>
+      <c r="R302" t="n">
+        <v>4</v>
+      </c>
+      <c r="S302" t="n">
+        <v>22</v>
+      </c>
+      <c r="T302" t="n">
+        <v>7</v>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
+      <c r="W302" t="n">
+        <v>48</v>
+      </c>
+      <c r="X302" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z302" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA302" t="inlineStr"/>
+      <c r="AB302" t="inlineStr"/>
+      <c r="AC302" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="AD302" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="AE302" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AF302" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="AG302" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH302" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AI302" t="n">
+        <v>4450000</v>
+      </c>
+      <c r="AJ302" t="n">
+        <v>77</v>
+      </c>
+      <c r="AK302" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL302" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="AM302" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN302" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AO302" t="n">
+        <v>2360000</v>
+      </c>
+      <c r="AP302" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AQ302" t="n">
+        <v>23.18181818181818</v>
+      </c>
+      <c r="AR302" t="n">
+        <v>178.3636363636364</v>
+      </c>
+      <c r="AS302" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AT302" t="n">
+        <v>71.18181818181819</v>
+      </c>
+      <c r="AU302" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="AV302" t="n">
+        <v>78.36363636363636</v>
+      </c>
+      <c r="AW302" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="AX302" t="n">
+        <v>184</v>
+      </c>
+      <c r="AY302" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AZ302" t="n">
+        <v>66.6875</v>
+      </c>
+      <c r="BA302" t="n">
+        <v>1392187.5</v>
+      </c>
+      <c r="BB302" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BC302" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="BD302" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="BE302" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF302" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG302" t="n">
+        <v>296</v>
+      </c>
+      <c r="BH302" t="n">
+        <v>21200000</v>
+      </c>
+      <c r="BI302" t="n">
+        <v>308</v>
+      </c>
+      <c r="BJ302" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BK302" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="BL302" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM302" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN302" t="n">
+        <v>135</v>
+      </c>
+      <c r="BO302" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="BP302" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>Ohp1YY1t</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="n">
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carrow road
+  norwich </t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>27137</v>
+      </c>
+      <c r="F303" t="n">
+        <v>26400</v>
+      </c>
+      <c r="G303" t="n">
+        <v>2</v>
+      </c>
+      <c r="H303" t="n">
+        <v>2</v>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="n">
+        <v>46</v>
+      </c>
+      <c r="N303" t="n">
+        <v>54</v>
+      </c>
+      <c r="O303" t="n">
+        <v>14</v>
+      </c>
+      <c r="P303" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>5</v>
+      </c>
+      <c r="R303" t="n">
+        <v>3</v>
+      </c>
+      <c r="S303" t="n">
+        <v>12</v>
+      </c>
+      <c r="T303" t="n">
+        <v>14</v>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="W303" t="n">
+        <v>48</v>
+      </c>
+      <c r="X303" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y303" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z303" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA303" t="inlineStr"/>
+      <c r="AB303" t="inlineStr"/>
+      <c r="AC303" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="AD303" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="AE303" t="inlineStr"/>
+      <c r="AF303" t="inlineStr"/>
+      <c r="AG303" t="inlineStr"/>
+      <c r="AH303" t="inlineStr"/>
+      <c r="AI303" t="inlineStr"/>
+      <c r="AJ303" t="inlineStr"/>
+      <c r="AK303" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AL303" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="AM303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN303" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO303" t="n">
+        <v>2040000</v>
+      </c>
+      <c r="AP303" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AQ303" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR303" t="n">
+        <v>179.4615384615385</v>
+      </c>
+      <c r="AS303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT303" t="n">
+        <v>66.76923076923077</v>
+      </c>
+      <c r="AU303" t="n">
+        <v>1882692.307692308</v>
+      </c>
+      <c r="AV303" t="n">
+        <v>73.15384615384616</v>
+      </c>
+      <c r="AW303" t="n">
+        <v>26.57894736842105</v>
+      </c>
+      <c r="AX303" t="n">
+        <v>182.6315789473684</v>
+      </c>
+      <c r="AY303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ303" t="n">
+        <v>68.57894736842105</v>
+      </c>
+      <c r="BA303" t="n">
+        <v>1634210.526315789</v>
+      </c>
+      <c r="BB303" t="n">
+        <v>72.26315789473684</v>
+      </c>
+      <c r="BC303" t="n">
+        <v>33</v>
+      </c>
+      <c r="BD303" t="n">
+        <v>186</v>
+      </c>
+      <c r="BE303" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF303" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG303" t="n">
+        <v>71</v>
+      </c>
+      <c r="BH303" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="BI303" t="n">
+        <v>71</v>
+      </c>
+      <c r="BJ303" t="n">
+        <v>22</v>
+      </c>
+      <c r="BK303" t="n">
+        <v>183</v>
+      </c>
+      <c r="BL303" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM303" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN303" t="n">
+        <v>134</v>
+      </c>
+      <c r="BO303" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="BP303" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>KKwAWCWh</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="n">
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doughty l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">home park
+  plymouth </t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>17000</v>
+      </c>
+      <c r="F304" t="n">
+        <v>16306</v>
+      </c>
+      <c r="G304" t="n">
+        <v>1</v>
+      </c>
+      <c r="H304" t="n">
+        <v>1</v>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>S66R0t75</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="n">
+        <v>50</v>
+      </c>
+      <c r="N304" t="n">
+        <v>50</v>
+      </c>
+      <c r="O304" t="n">
+        <v>16</v>
+      </c>
+      <c r="P304" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>7</v>
+      </c>
+      <c r="R304" t="n">
+        <v>2</v>
+      </c>
+      <c r="S304" t="n">
+        <v>15</v>
+      </c>
+      <c r="T304" t="n">
+        <v>18</v>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>WfXv1DCa</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="W304" t="n">
+        <v>48</v>
+      </c>
+      <c r="X304" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z304" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA304" t="inlineStr"/>
+      <c r="AB304" t="inlineStr"/>
+      <c r="AC304" t="inlineStr"/>
+      <c r="AD304" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="AE304" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AF304" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="AG304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH304" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AI304" t="n">
+        <v>2105000</v>
+      </c>
+      <c r="AJ304" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AK304" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="AL304" t="n">
+        <v>181.7777777777778</v>
+      </c>
+      <c r="AM304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN304" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="AO304" t="n">
+        <v>2888888.888888889</v>
+      </c>
+      <c r="AP304" t="n">
+        <v>76.11111111111111</v>
+      </c>
+      <c r="AQ304" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="AR304" t="n">
+        <v>184.1111111111111</v>
+      </c>
+      <c r="AS304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT304" t="n">
+        <v>66.11111111111111</v>
+      </c>
+      <c r="AU304" t="n">
+        <v>1447222.222222222</v>
+      </c>
+      <c r="AV304" t="n">
+        <v>72.83333333333333</v>
+      </c>
+      <c r="AW304" t="n">
+        <v>21.61538461538462</v>
+      </c>
+      <c r="AX304" t="n">
+        <v>178.5384615384615</v>
+      </c>
+      <c r="AY304" t="n">
+        <v>1.076923076923077</v>
+      </c>
+      <c r="AZ304" t="n">
+        <v>62.84615384615385</v>
+      </c>
+      <c r="BA304" t="n">
+        <v>1403461.538461538</v>
+      </c>
+      <c r="BB304" t="n">
+        <v>71.84615384615384</v>
+      </c>
+      <c r="BC304" t="inlineStr"/>
+      <c r="BD304" t="inlineStr"/>
+      <c r="BE304" t="inlineStr"/>
+      <c r="BF304" t="inlineStr"/>
+      <c r="BG304" t="inlineStr"/>
+      <c r="BH304" t="inlineStr"/>
+      <c r="BI304" t="inlineStr"/>
+      <c r="BJ304" t="n">
+        <v>22</v>
+      </c>
+      <c r="BK304" t="n">
+        <v>181</v>
+      </c>
+      <c r="BL304" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM304" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN304" t="n">
+        <v>198</v>
+      </c>
+      <c r="BO304" t="n">
+        <v>5125000</v>
+      </c>
+      <c r="BP304" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>l0VQSUVH</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="n">
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backhouse a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bramall lane
+  sheffield </t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>32050</v>
+      </c>
+      <c r="F305" t="n">
+        <v>27527</v>
+      </c>
+      <c r="G305" t="n">
+        <v>2</v>
+      </c>
+      <c r="H305" t="n">
+        <v>2</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="n">
+        <v>50</v>
+      </c>
+      <c r="N305" t="n">
+        <v>50</v>
+      </c>
+      <c r="O305" t="n">
+        <v>14</v>
+      </c>
+      <c r="P305" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>3</v>
+      </c>
+      <c r="R305" t="n">
+        <v>3</v>
+      </c>
+      <c r="S305" t="n">
+        <v>15</v>
+      </c>
+      <c r="T305" t="n">
+        <v>9</v>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="W305" t="n">
+        <v>48</v>
+      </c>
+      <c r="X305" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA305" t="inlineStr"/>
+      <c r="AB305" t="inlineStr"/>
+      <c r="AC305" t="inlineStr"/>
+      <c r="AD305" t="inlineStr"/>
+      <c r="AE305" t="inlineStr"/>
+      <c r="AF305" t="inlineStr"/>
+      <c r="AG305" t="inlineStr"/>
+      <c r="AH305" t="inlineStr"/>
+      <c r="AI305" t="inlineStr"/>
+      <c r="AJ305" t="inlineStr"/>
+      <c r="AK305" t="inlineStr"/>
+      <c r="AL305" t="inlineStr"/>
+      <c r="AM305" t="inlineStr"/>
+      <c r="AN305" t="inlineStr"/>
+      <c r="AO305" t="inlineStr"/>
+      <c r="AP305" t="inlineStr"/>
+      <c r="AQ305" t="n">
+        <v>22.11764705882353</v>
+      </c>
+      <c r="AR305" t="n">
+        <v>184.0588235294118</v>
+      </c>
+      <c r="AS305" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT305" t="n">
+        <v>68.94117647058823</v>
+      </c>
+      <c r="AU305" t="n">
+        <v>2958823.529411765</v>
+      </c>
+      <c r="AV305" t="n">
+        <v>76.23529411764706</v>
+      </c>
+      <c r="AW305" t="n">
+        <v>27.23076923076923</v>
+      </c>
+      <c r="AX305" t="n">
+        <v>180.9230769230769</v>
+      </c>
+      <c r="AY305" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ305" t="n">
+        <v>67.61538461538461</v>
+      </c>
+      <c r="BA305" t="n">
+        <v>1201923.076923077</v>
+      </c>
+      <c r="BB305" t="n">
+        <v>69.30769230769231</v>
+      </c>
+      <c r="BC305" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD305" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="BE305" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF305" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG305" t="n">
+        <v>130</v>
+      </c>
+      <c r="BH305" t="n">
+        <v>2625000</v>
+      </c>
+      <c r="BI305" t="n">
+        <v>145</v>
+      </c>
+      <c r="BJ305" t="inlineStr"/>
+      <c r="BK305" t="inlineStr"/>
+      <c r="BL305" t="inlineStr"/>
+      <c r="BM305" t="inlineStr"/>
+      <c r="BN305" t="inlineStr"/>
+      <c r="BO305" t="inlineStr"/>
+      <c r="BP305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>S2xgTDfT</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="n">
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">martin s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>21088</v>
+      </c>
+      <c r="F306" t="n">
+        <v>14037</v>
+      </c>
+      <c r="G306" t="n">
+        <v>3</v>
+      </c>
+      <c r="H306" t="n">
+        <v>0</v>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>x8IDVcbi</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="n">
+        <v>63</v>
+      </c>
+      <c r="N306" t="n">
+        <v>37</v>
+      </c>
+      <c r="O306" t="n">
+        <v>13</v>
+      </c>
+      <c r="P306" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>7</v>
+      </c>
+      <c r="R306" t="n">
+        <v>2</v>
+      </c>
+      <c r="S306" t="n">
+        <v>11</v>
+      </c>
+      <c r="T306" t="n">
+        <v>23</v>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>dtwAbyJ5</t>
+        </is>
+      </c>
+      <c r="W306" t="n">
+        <v>48</v>
+      </c>
+      <c r="X306" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z306" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA306" t="inlineStr"/>
+      <c r="AB306" t="inlineStr"/>
+      <c r="AC306" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="AD306" t="inlineStr"/>
+      <c r="AE306" t="inlineStr"/>
+      <c r="AF306" t="inlineStr"/>
+      <c r="AG306" t="inlineStr"/>
+      <c r="AH306" t="inlineStr"/>
+      <c r="AI306" t="inlineStr"/>
+      <c r="AJ306" t="inlineStr"/>
+      <c r="AK306" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="AL306" t="n">
+        <v>185.8888888888889</v>
+      </c>
+      <c r="AM306" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN306" t="n">
+        <v>71.22222222222223</v>
+      </c>
+      <c r="AO306" t="n">
+        <v>5530555.555555556</v>
+      </c>
+      <c r="AP306" t="n">
+        <v>72.88888888888889</v>
+      </c>
+      <c r="AQ306" t="n">
+        <v>26.35714285714286</v>
+      </c>
+      <c r="AR306" t="n">
+        <v>181.7857142857143</v>
+      </c>
+      <c r="AS306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT306" t="n">
+        <v>66.14285714285714</v>
+      </c>
+      <c r="AU306" t="n">
+        <v>1019642.857142857</v>
+      </c>
+      <c r="AV306" t="n">
+        <v>71</v>
+      </c>
+      <c r="AW306" t="n">
+        <v>25.17647058823529</v>
+      </c>
+      <c r="AX306" t="n">
+        <v>181.1764705882353</v>
+      </c>
+      <c r="AY306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ306" t="n">
+        <v>68.94117647058823</v>
+      </c>
+      <c r="BA306" t="n">
+        <v>2033823.529411765</v>
+      </c>
+      <c r="BB306" t="n">
+        <v>73</v>
+      </c>
+      <c r="BC306" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD306" t="n">
+        <v>174.6666666666667</v>
+      </c>
+      <c r="BE306" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF306" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG306" t="n">
+        <v>204</v>
+      </c>
+      <c r="BH306" t="n">
+        <v>3425000</v>
+      </c>
+      <c r="BI306" t="n">
+        <v>209</v>
+      </c>
+      <c r="BJ306" t="inlineStr"/>
+      <c r="BK306" t="inlineStr"/>
+      <c r="BL306" t="inlineStr"/>
+      <c r="BM306" t="inlineStr"/>
+      <c r="BN306" t="inlineStr"/>
+      <c r="BO306" t="inlineStr"/>
+      <c r="BP306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>bBbqoCon</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="n">
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nield t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vicarage road
+  watford </t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>22200</v>
+      </c>
+      <c r="F307" t="n">
+        <v>18789</v>
+      </c>
+      <c r="G307" t="n">
+        <v>3</v>
+      </c>
+      <c r="H307" t="n">
+        <v>0</v>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
+      <c r="M307" t="n">
+        <v>53</v>
+      </c>
+      <c r="N307" t="n">
+        <v>47</v>
+      </c>
+      <c r="O307" t="n">
+        <v>26</v>
+      </c>
+      <c r="P307" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>9</v>
+      </c>
+      <c r="R307" t="n">
+        <v>3</v>
+      </c>
+      <c r="S307" t="n">
+        <v>14</v>
+      </c>
+      <c r="T307" t="n">
+        <v>16</v>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="W307" t="n">
+        <v>48</v>
+      </c>
+      <c r="X307" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z307" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA307" t="inlineStr"/>
+      <c r="AB307" t="inlineStr"/>
+      <c r="AC307" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="AD307" t="inlineStr"/>
+      <c r="AE307" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AF307" t="n">
+        <v>183.8888888888889</v>
+      </c>
+      <c r="AG307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH307" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="AI307" t="n">
+        <v>1777777.777777778</v>
+      </c>
+      <c r="AJ307" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AK307" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AL307" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AM307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN307" t="n">
+        <v>69</v>
+      </c>
+      <c r="AO307" t="n">
+        <v>2228125</v>
+      </c>
+      <c r="AP307" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AQ307" t="n">
+        <v>23.44444444444444</v>
+      </c>
+      <c r="AR307" t="n">
+        <v>181.6111111111111</v>
+      </c>
+      <c r="AS307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT307" t="n">
+        <v>68.16666666666667</v>
+      </c>
+      <c r="AU307" t="n">
+        <v>2055555.555555556</v>
+      </c>
+      <c r="AV307" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="AW307" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX307" t="n">
+        <v>180.1176470588235</v>
+      </c>
+      <c r="AY307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ307" t="n">
+        <v>66.41176470588235</v>
+      </c>
+      <c r="BA307" t="n">
+        <v>1741764.705882353</v>
+      </c>
+      <c r="BB307" t="n">
+        <v>74.41176470588235</v>
+      </c>
+      <c r="BC307" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD307" t="n">
+        <v>188</v>
+      </c>
+      <c r="BE307" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF307" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG307" t="n">
+        <v>73</v>
+      </c>
+      <c r="BH307" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="BI307" t="n">
+        <v>73</v>
+      </c>
+      <c r="BJ307" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="BK307" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="BL307" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM307" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN307" t="n">
+        <v>209</v>
+      </c>
+      <c r="BO307" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="BP307" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>8SfhEVGO</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="n">
+        <v>45521.35416666666</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pride park
+  derby </t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>33597</v>
+      </c>
+      <c r="F308" t="n">
+        <v>29443</v>
+      </c>
+      <c r="G308" t="n">
+        <v>1</v>
+      </c>
+      <c r="H308" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Iug0YO0Q</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>6F0lvLNC</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
+      <c r="M308" t="n">
+        <v>30</v>
+      </c>
+      <c r="N308" t="n">
+        <v>70</v>
+      </c>
+      <c r="O308" t="n">
+        <v>3</v>
+      </c>
+      <c r="P308" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>2</v>
+      </c>
+      <c r="R308" t="n">
+        <v>4</v>
+      </c>
+      <c r="S308" t="n">
+        <v>15</v>
+      </c>
+      <c r="T308" t="n">
+        <v>5</v>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="W308" t="n">
+        <v>48</v>
+      </c>
+      <c r="X308" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z308" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA308" t="inlineStr"/>
+      <c r="AB308" t="inlineStr"/>
+      <c r="AC308" t="inlineStr"/>
+      <c r="AD308" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="AE308" t="inlineStr"/>
+      <c r="AF308" t="inlineStr"/>
+      <c r="AG308" t="inlineStr"/>
+      <c r="AH308" t="inlineStr"/>
+      <c r="AI308" t="inlineStr"/>
+      <c r="AJ308" t="inlineStr"/>
+      <c r="AK308" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AL308" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="AM308" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN308" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AO308" t="n">
+        <v>2610000</v>
+      </c>
+      <c r="AP308" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="AQ308" t="inlineStr"/>
+      <c r="AR308" t="inlineStr"/>
+      <c r="AS308" t="inlineStr"/>
+      <c r="AT308" t="inlineStr"/>
+      <c r="AU308" t="inlineStr"/>
+      <c r="AV308" t="inlineStr"/>
+      <c r="AW308" t="n">
+        <v>21.70588235294118</v>
+      </c>
+      <c r="AX308" t="n">
+        <v>182.7647058823529</v>
+      </c>
+      <c r="AY308" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ308" t="n">
+        <v>66.58823529411765</v>
+      </c>
+      <c r="BA308" t="n">
+        <v>1988235.294117647</v>
+      </c>
+      <c r="BB308" t="n">
+        <v>76.17647058823529</v>
+      </c>
+      <c r="BC308" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD308" t="n">
+        <v>175</v>
+      </c>
+      <c r="BE308" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF308" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG308" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH308" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="BI308" t="n">
+        <v>70</v>
+      </c>
+      <c r="BJ308" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BK308" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BL308" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM308" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN308" t="n">
+        <v>139</v>
+      </c>
+      <c r="BO308" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="BP308" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>hYyIUj15</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="n">
+        <v>45521.35416666666</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busby j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fratton park
+  portsmouth </t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>21944</v>
+      </c>
+      <c r="F309" t="n">
+        <v>20293</v>
+      </c>
+      <c r="G309" t="n">
+        <v>0</v>
+      </c>
+      <c r="H309" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>zckREQFJ</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="n">
+        <v>64</v>
+      </c>
+      <c r="N309" t="n">
+        <v>36</v>
+      </c>
+      <c r="O309" t="n">
+        <v>16</v>
+      </c>
+      <c r="P309" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>7</v>
+      </c>
+      <c r="R309" t="n">
+        <v>4</v>
+      </c>
+      <c r="S309" t="n">
+        <v>12</v>
+      </c>
+      <c r="T309" t="n">
+        <v>14</v>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>djl0V3o6</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="W309" t="n">
+        <v>48</v>
+      </c>
+      <c r="X309" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y309" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z309" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA309" t="inlineStr"/>
+      <c r="AB309" t="inlineStr"/>
+      <c r="AC309" t="inlineStr"/>
+      <c r="AD309" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="AE309" t="inlineStr"/>
+      <c r="AF309" t="inlineStr"/>
+      <c r="AG309" t="inlineStr"/>
+      <c r="AH309" t="inlineStr"/>
+      <c r="AI309" t="inlineStr"/>
+      <c r="AJ309" t="inlineStr"/>
+      <c r="AK309" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AL309" t="n">
+        <v>183.0909090909091</v>
+      </c>
+      <c r="AM309" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN309" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AO309" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="AP309" t="n">
+        <v>75.18181818181819</v>
+      </c>
+      <c r="AQ309" t="inlineStr"/>
+      <c r="AR309" t="inlineStr"/>
+      <c r="AS309" t="inlineStr"/>
+      <c r="AT309" t="inlineStr"/>
+      <c r="AU309" t="inlineStr"/>
+      <c r="AV309" t="inlineStr"/>
+      <c r="AW309" t="n">
+        <v>26.55555555555556</v>
+      </c>
+      <c r="AX309" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="AY309" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ309" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="BA309" t="n">
+        <v>1947222.222222222</v>
+      </c>
+      <c r="BB309" t="n">
+        <v>72</v>
+      </c>
+      <c r="BC309" t="inlineStr"/>
+      <c r="BD309" t="inlineStr"/>
+      <c r="BE309" t="inlineStr"/>
+      <c r="BF309" t="inlineStr"/>
+      <c r="BG309" t="inlineStr"/>
+      <c r="BH309" t="inlineStr"/>
+      <c r="BI309" t="inlineStr"/>
+      <c r="BJ309" t="n">
+        <v>26.16666666666667</v>
+      </c>
+      <c r="BK309" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="BL309" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM309" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN309" t="n">
+        <v>429</v>
+      </c>
+      <c r="BO309" t="n">
+        <v>16700000</v>
+      </c>
+      <c r="BP309" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>6y2iqjGb</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="n">
+        <v>45521.35416666666</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the hawthorns
+  west bromwich </t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>26688</v>
+      </c>
+      <c r="F310" t="n">
+        <v>25329</v>
+      </c>
+      <c r="G310" t="n">
+        <v>0</v>
+      </c>
+      <c r="H310" t="n">
+        <v>0</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>CCBWpzjj</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr"/>
+      <c r="M310" t="n">
+        <v>58</v>
+      </c>
+      <c r="N310" t="n">
+        <v>42</v>
+      </c>
+      <c r="O310" t="n">
+        <v>9</v>
+      </c>
+      <c r="P310" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>2</v>
+      </c>
+      <c r="R310" t="n">
+        <v>4</v>
+      </c>
+      <c r="S310" t="n">
+        <v>15</v>
+      </c>
+      <c r="T310" t="n">
+        <v>13</v>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="W310" t="n">
+        <v>48</v>
+      </c>
+      <c r="X310" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y310" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z310" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA310" t="inlineStr"/>
+      <c r="AB310" t="inlineStr"/>
+      <c r="AC310" t="inlineStr"/>
+      <c r="AD310" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="AE310" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AF310" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="AG310" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH310" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AI310" t="n">
+        <v>2320000</v>
+      </c>
+      <c r="AJ310" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AK310" t="n">
+        <v>23.55555555555556</v>
+      </c>
+      <c r="AL310" t="n">
+        <v>185</v>
+      </c>
+      <c r="AM310" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AN310" t="n">
+        <v>74.11111111111111</v>
+      </c>
+      <c r="AO310" t="n">
+        <v>6688888.888888889</v>
+      </c>
+      <c r="AP310" t="n">
+        <v>78.88888888888889</v>
+      </c>
+      <c r="AQ310" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AR310" t="n">
+        <v>180.7333333333333</v>
+      </c>
+      <c r="AS310" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT310" t="n">
+        <v>69.86666666666666</v>
+      </c>
+      <c r="AU310" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="AV310" t="n">
+        <v>74.26666666666667</v>
+      </c>
+      <c r="AW310" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AX310" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="AY310" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ310" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="BA310" t="n">
+        <v>3480000</v>
+      </c>
+      <c r="BB310" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="BC310" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD310" t="n">
+        <v>188</v>
+      </c>
+      <c r="BE310" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF310" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG310" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH310" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="BI310" t="n">
+        <v>75</v>
+      </c>
+      <c r="BJ310" t="inlineStr"/>
+      <c r="BK310" t="inlineStr"/>
+      <c r="BL310" t="inlineStr"/>
+      <c r="BM310" t="inlineStr"/>
+      <c r="BN310" t="inlineStr"/>
+      <c r="BO310" t="inlineStr"/>
+      <c r="BP310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>nD6qGinC</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="n">
+        <v>45520.66666666666</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coventry building society arena
+  coventry </t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>32753</v>
+      </c>
+      <c r="F311" t="n">
+        <v>28051</v>
+      </c>
+      <c r="G311" t="n">
+        <v>3</v>
+      </c>
+      <c r="H311" t="n">
+        <v>2</v>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>vgOBT43c</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr"/>
+      <c r="M311" t="n">
+        <v>64</v>
+      </c>
+      <c r="N311" t="n">
+        <v>36</v>
+      </c>
+      <c r="O311" t="n">
+        <v>27</v>
+      </c>
+      <c r="P311" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>12</v>
+      </c>
+      <c r="R311" t="n">
+        <v>3</v>
+      </c>
+      <c r="S311" t="n">
+        <v>10</v>
+      </c>
+      <c r="T311" t="n">
+        <v>8</v>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
+      <c r="W311" t="n">
+        <v>48</v>
+      </c>
+      <c r="X311" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y311" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z311" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA311" t="inlineStr"/>
+      <c r="AB311" t="inlineStr"/>
+      <c r="AC311" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="AD311" t="inlineStr"/>
+      <c r="AE311" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AF311" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AG311" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH311" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AI311" t="n">
+        <v>3860000</v>
+      </c>
+      <c r="AJ311" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AK311" t="inlineStr"/>
+      <c r="AL311" t="inlineStr"/>
+      <c r="AM311" t="inlineStr"/>
+      <c r="AN311" t="inlineStr"/>
+      <c r="AO311" t="inlineStr"/>
+      <c r="AP311" t="inlineStr"/>
+      <c r="AQ311" t="n">
+        <v>24.52941176470588</v>
+      </c>
+      <c r="AR311" t="n">
+        <v>179.4117647058823</v>
+      </c>
+      <c r="AS311" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT311" t="n">
+        <v>68.88235294117646</v>
+      </c>
+      <c r="AU311" t="n">
+        <v>2101470.588235294</v>
+      </c>
+      <c r="AV311" t="n">
+        <v>73.29411764705883</v>
+      </c>
+      <c r="AW311" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AX311" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AY311" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ311" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="BA311" t="n">
+        <v>1305000</v>
+      </c>
+      <c r="BB311" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BC311" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD311" t="n">
+        <v>185</v>
+      </c>
+      <c r="BE311" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF311" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG311" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH311" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="BI311" t="n">
+        <v>80</v>
+      </c>
+      <c r="BJ311" t="inlineStr"/>
+      <c r="BK311" t="inlineStr"/>
+      <c r="BL311" t="inlineStr"/>
+      <c r="BM311" t="inlineStr"/>
+      <c r="BN311" t="inlineStr"/>
+      <c r="BO311" t="inlineStr"/>
+      <c r="BP311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>4xLQ2Sg5</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="n">
+        <v>45516.66666666666</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donohue m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kenilworth road
+  luton </t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>12300</v>
+      </c>
+      <c r="F312" t="n">
+        <v>11777</v>
+      </c>
+      <c r="G312" t="n">
+        <v>1</v>
+      </c>
+      <c r="H312" t="n">
+        <v>4</v>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
+      <c r="M312" t="n">
+        <v>60</v>
+      </c>
+      <c r="N312" t="n">
+        <v>40</v>
+      </c>
+      <c r="O312" t="n">
+        <v>10</v>
+      </c>
+      <c r="P312" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>3</v>
+      </c>
+      <c r="R312" t="n">
+        <v>7</v>
+      </c>
+      <c r="S312" t="n">
+        <v>11</v>
+      </c>
+      <c r="T312" t="n">
+        <v>19</v>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="W312" t="n">
+        <v>48</v>
+      </c>
+      <c r="X312" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z312" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA312" t="inlineStr"/>
+      <c r="AB312" t="inlineStr"/>
+      <c r="AC312" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="AD312" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="AE312" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AF312" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AG312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH312" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="AI312" t="n">
+        <v>2892500</v>
+      </c>
+      <c r="AJ312" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AK312" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AL312" t="n">
+        <v>182</v>
+      </c>
+      <c r="AM312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN312" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO312" t="n">
+        <v>4870000</v>
+      </c>
+      <c r="AP312" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="AQ312" t="n">
+        <v>29.11111111111111</v>
+      </c>
+      <c r="AR312" t="n">
+        <v>178.5555555555555</v>
+      </c>
+      <c r="AS312" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AT312" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AU312" t="n">
+        <v>2333333.333333333</v>
+      </c>
+      <c r="AV312" t="n">
+        <v>72</v>
+      </c>
+      <c r="AW312" t="n">
+        <v>23.125</v>
+      </c>
+      <c r="AX312" t="n">
+        <v>181.0625</v>
+      </c>
+      <c r="AY312" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AZ312" t="n">
+        <v>71.3125</v>
+      </c>
+      <c r="BA312" t="n">
+        <v>4387500</v>
+      </c>
+      <c r="BB312" t="n">
+        <v>78.625</v>
+      </c>
+      <c r="BC312" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="BD312" t="n">
+        <v>186</v>
+      </c>
+      <c r="BE312" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF312" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG312" t="n">
+        <v>359</v>
+      </c>
+      <c r="BH312" t="n">
+        <v>14300000</v>
+      </c>
+      <c r="BI312" t="n">
+        <v>368</v>
+      </c>
+      <c r="BJ312" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="BK312" t="n">
+        <v>181</v>
+      </c>
+      <c r="BL312" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM312" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN312" t="n">
+        <v>222</v>
+      </c>
+      <c r="BO312" t="n">
+        <v>15700000</v>
+      </c>
+      <c r="BP312" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>WOMI4lPh</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="n">
+        <v>45515.5</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hillsborough
+  sheffield </t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>39732</v>
+      </c>
+      <c r="F313" t="n">
+        <v>29535</v>
+      </c>
+      <c r="G313" t="n">
+        <v>4</v>
+      </c>
+      <c r="H313" t="n">
+        <v>0</v>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="M313" t="n">
+        <v>55</v>
+      </c>
+      <c r="N313" t="n">
+        <v>45</v>
+      </c>
+      <c r="O313" t="n">
+        <v>21</v>
+      </c>
+      <c r="P313" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>7</v>
+      </c>
+      <c r="R313" t="n">
+        <v>1</v>
+      </c>
+      <c r="S313" t="n">
+        <v>17</v>
+      </c>
+      <c r="T313" t="n">
+        <v>16</v>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>WfXv1DCa</t>
+        </is>
+      </c>
+      <c r="W313" t="n">
+        <v>48</v>
+      </c>
+      <c r="X313" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z313" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA313" t="inlineStr"/>
+      <c r="AB313" t="inlineStr"/>
+      <c r="AC313" t="inlineStr"/>
+      <c r="AD313" t="inlineStr"/>
+      <c r="AE313" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AF313" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AG313" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH313" t="n">
+        <v>68.375</v>
+      </c>
+      <c r="AI313" t="n">
+        <v>1634375</v>
+      </c>
+      <c r="AJ313" t="n">
+        <v>73.125</v>
+      </c>
+      <c r="AK313" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AL313" t="n">
+        <v>187.375</v>
+      </c>
+      <c r="AM313" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN313" t="n">
+        <v>67.375</v>
+      </c>
+      <c r="AO313" t="n">
+        <v>1903125</v>
+      </c>
+      <c r="AP313" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="AQ313" t="n">
+        <v>27.63157894736842</v>
+      </c>
+      <c r="AR313" t="n">
+        <v>182.3157894736842</v>
+      </c>
+      <c r="AS313" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT313" t="n">
+        <v>66.05263157894737</v>
+      </c>
+      <c r="AU313" t="n">
+        <v>959210.5263157894</v>
+      </c>
+      <c r="AV313" t="n">
+        <v>68.73684210526316</v>
+      </c>
+      <c r="AW313" t="n">
+        <v>24.06666666666667</v>
+      </c>
+      <c r="AX313" t="n">
+        <v>179.2666666666667</v>
+      </c>
+      <c r="AY313" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ313" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="BA313" t="n">
+        <v>2261666.666666667</v>
+      </c>
+      <c r="BB313" t="n">
+        <v>73.73333333333333</v>
+      </c>
+      <c r="BC313" t="n">
+        <v>35</v>
+      </c>
+      <c r="BD313" t="n">
+        <v>193</v>
+      </c>
+      <c r="BE313" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF313" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG313" t="n">
+        <v>69</v>
+      </c>
+      <c r="BH313" t="n">
+        <v>150000</v>
+      </c>
+      <c r="BI313" t="n">
+        <v>69</v>
+      </c>
+      <c r="BJ313" t="inlineStr"/>
+      <c r="BK313" t="inlineStr"/>
+      <c r="BL313" t="inlineStr"/>
+      <c r="BM313" t="inlineStr"/>
+      <c r="BN313" t="inlineStr"/>
+      <c r="BO313" t="inlineStr"/>
+      <c r="BP313" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/england/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP314"/>
+  <dimension ref="A1:BP332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66133,6 +66133,3668 @@
         <v>157</v>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2g67Vsyf</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="n">
+        <v>45528.5625</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="n">
+        <v>0</v>
+      </c>
+      <c r="H315" t="n">
+        <v>2</v>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="K315" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="L315" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M315" t="n">
+        <v>43</v>
+      </c>
+      <c r="N315" t="n">
+        <v>57</v>
+      </c>
+      <c r="O315" t="n">
+        <v>11</v>
+      </c>
+      <c r="P315" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>3</v>
+      </c>
+      <c r="R315" t="n">
+        <v>4</v>
+      </c>
+      <c r="S315" t="n">
+        <v>7</v>
+      </c>
+      <c r="T315" t="n">
+        <v>13</v>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="W315" t="n">
+        <v>48</v>
+      </c>
+      <c r="X315" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z315" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA315" t="inlineStr"/>
+      <c r="AB315" t="inlineStr"/>
+      <c r="AC315" t="inlineStr"/>
+      <c r="AD315" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="AE315" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AF315" t="n">
+        <v>184</v>
+      </c>
+      <c r="AG315" t="n">
+        <v>2.090909090909091</v>
+      </c>
+      <c r="AH315" t="n">
+        <v>79.72727272727273</v>
+      </c>
+      <c r="AI315" t="n">
+        <v>25054545.45454545</v>
+      </c>
+      <c r="AJ315" t="n">
+        <v>81.90909090909091</v>
+      </c>
+      <c r="AK315" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AL315" t="n">
+        <v>183.375</v>
+      </c>
+      <c r="AM315" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AN315" t="n">
+        <v>84</v>
+      </c>
+      <c r="AO315" t="n">
+        <v>67000000</v>
+      </c>
+      <c r="AP315" t="n">
+        <v>87.75</v>
+      </c>
+      <c r="AQ315" t="n">
+        <v>23.90476190476191</v>
+      </c>
+      <c r="AR315" t="n">
+        <v>181.2857142857143</v>
+      </c>
+      <c r="AS315" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="AT315" t="n">
+        <v>75.33333333333333</v>
+      </c>
+      <c r="AU315" t="n">
+        <v>12909523.80952381</v>
+      </c>
+      <c r="AV315" t="n">
+        <v>80.38095238095238</v>
+      </c>
+      <c r="AW315" t="n">
+        <v>24.21428571428572</v>
+      </c>
+      <c r="AX315" t="n">
+        <v>177.2857142857143</v>
+      </c>
+      <c r="AY315" t="n">
+        <v>1.714285714285714</v>
+      </c>
+      <c r="AZ315" t="n">
+        <v>78.85714285714286</v>
+      </c>
+      <c r="BA315" t="n">
+        <v>29892857.14285714</v>
+      </c>
+      <c r="BB315" t="n">
+        <v>83.78571428571429</v>
+      </c>
+      <c r="BC315" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BD315" t="n">
+        <v>190</v>
+      </c>
+      <c r="BE315" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF315" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG315" t="n">
+        <v>161</v>
+      </c>
+      <c r="BH315" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="BI315" t="n">
+        <v>164</v>
+      </c>
+      <c r="BJ315" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="BK315" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="BL315" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM315" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN315" t="n">
+        <v>318</v>
+      </c>
+      <c r="BO315" t="n">
+        <v>104000000</v>
+      </c>
+      <c r="BP315" t="n">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>U5cORazJ</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F316" t="n">
+        <v>22099</v>
+      </c>
+      <c r="G316" t="n">
+        <v>0</v>
+      </c>
+      <c r="H316" t="n">
+        <v>2</v>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="K316" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L316" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M316" t="n">
+        <v>59</v>
+      </c>
+      <c r="N316" t="n">
+        <v>41</v>
+      </c>
+      <c r="O316" t="n">
+        <v>14</v>
+      </c>
+      <c r="P316" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>2</v>
+      </c>
+      <c r="R316" t="n">
+        <v>3</v>
+      </c>
+      <c r="S316" t="n">
+        <v>9</v>
+      </c>
+      <c r="T316" t="n">
+        <v>17</v>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="W316" t="n">
+        <v>48</v>
+      </c>
+      <c r="X316" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z316" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA316" t="inlineStr"/>
+      <c r="AB316" t="inlineStr"/>
+      <c r="AC316" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="AD316" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="AE316" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AF316" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="AG316" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH316" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="AI316" t="n">
+        <v>13900000</v>
+      </c>
+      <c r="AJ316" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="AK316" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL316" t="n">
+        <v>183.2222222222222</v>
+      </c>
+      <c r="AM316" t="n">
+        <v>2.111111111111111</v>
+      </c>
+      <c r="AN316" t="n">
+        <v>79.22222222222223</v>
+      </c>
+      <c r="AO316" t="n">
+        <v>20333333.33333333</v>
+      </c>
+      <c r="AP316" t="n">
+        <v>80.88888888888889</v>
+      </c>
+      <c r="AQ316" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AR316" t="n">
+        <v>183</v>
+      </c>
+      <c r="AS316" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AT316" t="n">
+        <v>74.58333333333333</v>
+      </c>
+      <c r="AU316" t="n">
+        <v>6875000</v>
+      </c>
+      <c r="AV316" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="AW316" t="n">
+        <v>27.94444444444444</v>
+      </c>
+      <c r="AX316" t="n">
+        <v>180.8333333333333</v>
+      </c>
+      <c r="AY316" t="n">
+        <v>2.111111111111111</v>
+      </c>
+      <c r="AZ316" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="BA316" t="n">
+        <v>16950000</v>
+      </c>
+      <c r="BB316" t="n">
+        <v>80.22222222222223</v>
+      </c>
+      <c r="BC316" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD316" t="n">
+        <v>185</v>
+      </c>
+      <c r="BE316" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF316" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG316" t="n">
+        <v>74</v>
+      </c>
+      <c r="BH316" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="BI316" t="n">
+        <v>74</v>
+      </c>
+      <c r="BJ316" t="inlineStr"/>
+      <c r="BK316" t="inlineStr"/>
+      <c r="BL316" t="inlineStr"/>
+      <c r="BM316" t="inlineStr"/>
+      <c r="BN316" t="inlineStr"/>
+      <c r="BO316" t="inlineStr"/>
+      <c r="BP316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>dCkAk3SP</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>26600</v>
+      </c>
+      <c r="F317" t="n">
+        <v>25401</v>
+      </c>
+      <c r="G317" t="n">
+        <v>2</v>
+      </c>
+      <c r="H317" t="n">
+        <v>1</v>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="K317" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L317" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M317" t="n">
+        <v>55</v>
+      </c>
+      <c r="N317" t="n">
+        <v>45</v>
+      </c>
+      <c r="O317" t="n">
+        <v>18</v>
+      </c>
+      <c r="P317" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>6</v>
+      </c>
+      <c r="R317" t="n">
+        <v>4</v>
+      </c>
+      <c r="S317" t="n">
+        <v>14</v>
+      </c>
+      <c r="T317" t="n">
+        <v>13</v>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="W317" t="n">
+        <v>48</v>
+      </c>
+      <c r="X317" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA317" t="inlineStr"/>
+      <c r="AB317" t="inlineStr"/>
+      <c r="AC317" t="inlineStr"/>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="AE317" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AF317" t="n">
+        <v>184</v>
+      </c>
+      <c r="AG317" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH317" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AI317" t="n">
+        <v>11410000</v>
+      </c>
+      <c r="AJ317" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AK317" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="AL317" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="AM317" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN317" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO317" t="n">
+        <v>7580000</v>
+      </c>
+      <c r="AP317" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AQ317" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="AR317" t="n">
+        <v>181.55</v>
+      </c>
+      <c r="AS317" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT317" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AU317" t="n">
+        <v>6090000</v>
+      </c>
+      <c r="AV317" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AW317" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="AX317" t="n">
+        <v>178.65</v>
+      </c>
+      <c r="AY317" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ317" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="BA317" t="n">
+        <v>7018750</v>
+      </c>
+      <c r="BB317" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="BC317" t="inlineStr"/>
+      <c r="BD317" t="inlineStr"/>
+      <c r="BE317" t="inlineStr"/>
+      <c r="BF317" t="inlineStr"/>
+      <c r="BG317" t="inlineStr"/>
+      <c r="BH317" t="inlineStr"/>
+      <c r="BI317" t="inlineStr"/>
+      <c r="BJ317" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="BK317" t="n">
+        <v>184.6666666666667</v>
+      </c>
+      <c r="BL317" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM317" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN317" t="n">
+        <v>211</v>
+      </c>
+      <c r="BO317" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="BP317" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>lAUlrLKa</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="n">
+        <v>4</v>
+      </c>
+      <c r="H318" t="n">
+        <v>1</v>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="K318" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L318" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M318" t="n">
+        <v>76</v>
+      </c>
+      <c r="N318" t="n">
+        <v>24</v>
+      </c>
+      <c r="O318" t="n">
+        <v>14</v>
+      </c>
+      <c r="P318" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>5</v>
+      </c>
+      <c r="R318" t="n">
+        <v>2</v>
+      </c>
+      <c r="S318" t="n">
+        <v>4</v>
+      </c>
+      <c r="T318" t="n">
+        <v>15</v>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="W318" t="n">
+        <v>48</v>
+      </c>
+      <c r="X318" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA318" t="inlineStr"/>
+      <c r="AB318" t="inlineStr"/>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="AE318" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AF318" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AG318" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH318" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="AI318" t="n">
+        <v>71150000</v>
+      </c>
+      <c r="AJ318" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="AK318" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AL318" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AM318" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN318" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AO318" t="n">
+        <v>4160000</v>
+      </c>
+      <c r="AP318" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="AQ318" t="n">
+        <v>25.73684210526316</v>
+      </c>
+      <c r="AR318" t="n">
+        <v>182.4736842105263</v>
+      </c>
+      <c r="AS318" t="n">
+        <v>2.210526315789474</v>
+      </c>
+      <c r="AT318" t="n">
+        <v>80.84210526315789</v>
+      </c>
+      <c r="AU318" t="n">
+        <v>42526315.78947368</v>
+      </c>
+      <c r="AV318" t="n">
+        <v>84.47368421052632</v>
+      </c>
+      <c r="AW318" t="n">
+        <v>25.08695652173913</v>
+      </c>
+      <c r="AX318" t="n">
+        <v>182.4782608695652</v>
+      </c>
+      <c r="AY318" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ318" t="n">
+        <v>69.1304347826087</v>
+      </c>
+      <c r="BA318" t="n">
+        <v>2365217.391304348</v>
+      </c>
+      <c r="BB318" t="n">
+        <v>73.04347826086956</v>
+      </c>
+      <c r="BC318" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD318" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BE318" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BF318" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG318" t="n">
+        <v>158</v>
+      </c>
+      <c r="BH318" t="n">
+        <v>132400000</v>
+      </c>
+      <c r="BI318" t="n">
+        <v>174</v>
+      </c>
+      <c r="BJ318" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="BK318" t="n">
+        <v>181.1666666666667</v>
+      </c>
+      <c r="BL318" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="BM318" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN318" t="n">
+        <v>426</v>
+      </c>
+      <c r="BO318" t="n">
+        <v>21800000</v>
+      </c>
+      <c r="BP318" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>fNaktakC</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>32384</v>
+      </c>
+      <c r="F319" t="n">
+        <v>31150</v>
+      </c>
+      <c r="G319" t="n">
+        <v>0</v>
+      </c>
+      <c r="H319" t="n">
+        <v>1</v>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="K319" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L319" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M319" t="n">
+        <v>65</v>
+      </c>
+      <c r="N319" t="n">
+        <v>35</v>
+      </c>
+      <c r="O319" t="n">
+        <v>5</v>
+      </c>
+      <c r="P319" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>1</v>
+      </c>
+      <c r="R319" t="n">
+        <v>8</v>
+      </c>
+      <c r="S319" t="n">
+        <v>14</v>
+      </c>
+      <c r="T319" t="n">
+        <v>13</v>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="W319" t="n">
+        <v>48</v>
+      </c>
+      <c r="X319" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y319" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z319" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA319" t="inlineStr"/>
+      <c r="AB319" t="inlineStr"/>
+      <c r="AC319" t="inlineStr"/>
+      <c r="AD319" t="inlineStr"/>
+      <c r="AE319" t="n">
+        <v>25.55555555555556</v>
+      </c>
+      <c r="AF319" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="AG319" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH319" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AI319" t="n">
+        <v>4811111.111111111</v>
+      </c>
+      <c r="AJ319" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="AK319" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AL319" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="AM319" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN319" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO319" t="n">
+        <v>10210000</v>
+      </c>
+      <c r="AP319" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="AQ319" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AR319" t="n">
+        <v>179.0555555555555</v>
+      </c>
+      <c r="AS319" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT319" t="n">
+        <v>68.05555555555556</v>
+      </c>
+      <c r="AU319" t="n">
+        <v>2797222.222222222</v>
+      </c>
+      <c r="AV319" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AW319" t="n">
+        <v>25.78947368421053</v>
+      </c>
+      <c r="AX319" t="n">
+        <v>187</v>
+      </c>
+      <c r="AY319" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="AZ319" t="n">
+        <v>75.84210526315789</v>
+      </c>
+      <c r="BA319" t="n">
+        <v>10510526.31578947</v>
+      </c>
+      <c r="BB319" t="n">
+        <v>79.31578947368421</v>
+      </c>
+      <c r="BC319" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="BD319" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="BE319" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BF319" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG319" t="n">
+        <v>280</v>
+      </c>
+      <c r="BH319" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="BI319" t="n">
+        <v>308</v>
+      </c>
+      <c r="BJ319" t="inlineStr"/>
+      <c r="BK319" t="inlineStr"/>
+      <c r="BL319" t="inlineStr"/>
+      <c r="BM319" t="inlineStr"/>
+      <c r="BN319" t="inlineStr"/>
+      <c r="BO319" t="inlineStr"/>
+      <c r="BP319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2m3cvwKO</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>62850</v>
+      </c>
+      <c r="F320" t="n">
+        <v>61357</v>
+      </c>
+      <c r="G320" t="n">
+        <v>4</v>
+      </c>
+      <c r="H320" t="n">
+        <v>0</v>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="K320" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L320" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M320" t="n">
+        <v>71</v>
+      </c>
+      <c r="N320" t="n">
+        <v>29</v>
+      </c>
+      <c r="O320" t="n">
+        <v>13</v>
+      </c>
+      <c r="P320" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>7</v>
+      </c>
+      <c r="R320" t="n">
+        <v>1</v>
+      </c>
+      <c r="S320" t="n">
+        <v>11</v>
+      </c>
+      <c r="T320" t="n">
+        <v>15</v>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="W320" t="n">
+        <v>48</v>
+      </c>
+      <c r="X320" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y320" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z320" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA320" t="inlineStr"/>
+      <c r="AB320" t="inlineStr"/>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="AE320" t="n">
+        <v>24.22222222222222</v>
+      </c>
+      <c r="AF320" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="AG320" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH320" t="n">
+        <v>80.66666666666667</v>
+      </c>
+      <c r="AI320" t="n">
+        <v>38644444.44444445</v>
+      </c>
+      <c r="AJ320" t="n">
+        <v>85.11111111111111</v>
+      </c>
+      <c r="AK320" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AL320" t="n">
+        <v>183</v>
+      </c>
+      <c r="AM320" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN320" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="AO320" t="n">
+        <v>10260000</v>
+      </c>
+      <c r="AP320" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="AQ320" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AR320" t="n">
+        <v>184.2777777777778</v>
+      </c>
+      <c r="AS320" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AT320" t="n">
+        <v>76.72222222222223</v>
+      </c>
+      <c r="AU320" t="n">
+        <v>19348611.11111111</v>
+      </c>
+      <c r="AV320" t="n">
+        <v>83.05555555555556</v>
+      </c>
+      <c r="AW320" t="n">
+        <v>25.41666666666667</v>
+      </c>
+      <c r="AX320" t="n">
+        <v>185.9166666666667</v>
+      </c>
+      <c r="AY320" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ320" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="BA320" t="n">
+        <v>8970833.333333334</v>
+      </c>
+      <c r="BB320" t="n">
+        <v>76.16666666666667</v>
+      </c>
+      <c r="BC320" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BD320" t="n">
+        <v>187</v>
+      </c>
+      <c r="BE320" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF320" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG320" t="n">
+        <v>159</v>
+      </c>
+      <c r="BH320" t="n">
+        <v>53000000</v>
+      </c>
+      <c r="BI320" t="n">
+        <v>164</v>
+      </c>
+      <c r="BJ320" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BK320" t="n">
+        <v>184</v>
+      </c>
+      <c r="BL320" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BM320" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN320" t="n">
+        <v>443</v>
+      </c>
+      <c r="BO320" t="n">
+        <v>40625000</v>
+      </c>
+      <c r="BP320" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>8j9FTL56</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="n">
+        <v>45528.35416666666</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F321" t="n">
+        <v>31537</v>
+      </c>
+      <c r="G321" t="n">
+        <v>2</v>
+      </c>
+      <c r="H321" t="n">
+        <v>1</v>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="K321" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="L321" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M321" t="n">
+        <v>48</v>
+      </c>
+      <c r="N321" t="n">
+        <v>52</v>
+      </c>
+      <c r="O321" t="n">
+        <v>14</v>
+      </c>
+      <c r="P321" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>5</v>
+      </c>
+      <c r="R321" t="n">
+        <v>4</v>
+      </c>
+      <c r="S321" t="n">
+        <v>9</v>
+      </c>
+      <c r="T321" t="n">
+        <v>13</v>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="W321" t="n">
+        <v>48</v>
+      </c>
+      <c r="X321" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y321" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z321" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA321" t="inlineStr"/>
+      <c r="AB321" t="inlineStr"/>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="AE321" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF321" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AG321" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AH321" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="AI321" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="AJ321" t="n">
+        <v>78.77777777777777</v>
+      </c>
+      <c r="AK321" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AL321" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AM321" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AN321" t="n">
+        <v>82</v>
+      </c>
+      <c r="AO321" t="n">
+        <v>39625000</v>
+      </c>
+      <c r="AP321" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="AQ321" t="n">
+        <v>22.04545454545455</v>
+      </c>
+      <c r="AR321" t="n">
+        <v>177.0909090909091</v>
+      </c>
+      <c r="AS321" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AT321" t="n">
+        <v>71.95454545454545</v>
+      </c>
+      <c r="AU321" t="n">
+        <v>7793181.818181818</v>
+      </c>
+      <c r="AV321" t="n">
+        <v>81</v>
+      </c>
+      <c r="AW321" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="AX321" t="n">
+        <v>184.5833333333333</v>
+      </c>
+      <c r="AY321" t="n">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="AZ321" t="n">
+        <v>77.16666666666667</v>
+      </c>
+      <c r="BA321" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="BB321" t="n">
+        <v>81.58333333333333</v>
+      </c>
+      <c r="BC321" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD321" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="BE321" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF321" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG321" t="n">
+        <v>230</v>
+      </c>
+      <c r="BH321" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="BI321" t="n">
+        <v>254</v>
+      </c>
+      <c r="BJ321" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BK321" t="n">
+        <v>182</v>
+      </c>
+      <c r="BL321" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM321" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN321" t="n">
+        <v>316</v>
+      </c>
+      <c r="BO321" t="n">
+        <v>92000000</v>
+      </c>
+      <c r="BP321" t="n">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>23e0sUpB</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ewood park
+  blackburn </t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>31367</v>
+      </c>
+      <c r="F322" t="n">
+        <v>14769</v>
+      </c>
+      <c r="G322" t="n">
+        <v>2</v>
+      </c>
+      <c r="H322" t="n">
+        <v>1</v>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>vgOBT43c</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="n">
+        <v>50</v>
+      </c>
+      <c r="N322" t="n">
+        <v>50</v>
+      </c>
+      <c r="O322" t="n">
+        <v>21</v>
+      </c>
+      <c r="P322" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>4</v>
+      </c>
+      <c r="R322" t="n">
+        <v>3</v>
+      </c>
+      <c r="S322" t="n">
+        <v>16</v>
+      </c>
+      <c r="T322" t="n">
+        <v>8</v>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
+      <c r="W322" t="n">
+        <v>48</v>
+      </c>
+      <c r="X322" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y322" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z322" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA322" t="inlineStr"/>
+      <c r="AB322" t="inlineStr"/>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="AD322" t="inlineStr"/>
+      <c r="AE322" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AF322" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="AG322" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH322" t="n">
+        <v>70</v>
+      </c>
+      <c r="AI322" t="n">
+        <v>2040000</v>
+      </c>
+      <c r="AJ322" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AK322" t="inlineStr"/>
+      <c r="AL322" t="inlineStr"/>
+      <c r="AM322" t="inlineStr"/>
+      <c r="AN322" t="inlineStr"/>
+      <c r="AO322" t="inlineStr"/>
+      <c r="AP322" t="inlineStr"/>
+      <c r="AQ322" t="n">
+        <v>26.57142857142857</v>
+      </c>
+      <c r="AR322" t="n">
+        <v>182.4285714285714</v>
+      </c>
+      <c r="AS322" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT322" t="n">
+        <v>68.21428571428571</v>
+      </c>
+      <c r="AU322" t="n">
+        <v>1603571.428571429</v>
+      </c>
+      <c r="AV322" t="n">
+        <v>72</v>
+      </c>
+      <c r="AW322" t="n">
+        <v>26.14285714285714</v>
+      </c>
+      <c r="AX322" t="n">
+        <v>183</v>
+      </c>
+      <c r="AY322" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ322" t="n">
+        <v>65.71428571428571</v>
+      </c>
+      <c r="BA322" t="n">
+        <v>1014285.714285714</v>
+      </c>
+      <c r="BB322" t="n">
+        <v>69.57142857142857</v>
+      </c>
+      <c r="BC322" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD322" t="n">
+        <v>183</v>
+      </c>
+      <c r="BE322" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF322" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG322" t="n">
+        <v>134</v>
+      </c>
+      <c r="BH322" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="BI322" t="n">
+        <v>148</v>
+      </c>
+      <c r="BJ322" t="inlineStr"/>
+      <c r="BK322" t="inlineStr"/>
+      <c r="BL322" t="inlineStr"/>
+      <c r="BM322" t="inlineStr"/>
+      <c r="BN322" t="inlineStr"/>
+      <c r="BO322" t="inlineStr"/>
+      <c r="BP322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>prkJckVi</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donohue m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riverside stadium
+  middlesbrough </t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>34742</v>
+      </c>
+      <c r="F323" t="n">
+        <v>26270</v>
+      </c>
+      <c r="G323" t="n">
+        <v>2</v>
+      </c>
+      <c r="H323" t="n">
+        <v>2</v>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>6F0lvLNC</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>zckREQFJ</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="n">
+        <v>67</v>
+      </c>
+      <c r="N323" t="n">
+        <v>33</v>
+      </c>
+      <c r="O323" t="n">
+        <v>31</v>
+      </c>
+      <c r="P323" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>8</v>
+      </c>
+      <c r="R323" t="n">
+        <v>3</v>
+      </c>
+      <c r="S323" t="n">
+        <v>10</v>
+      </c>
+      <c r="T323" t="n">
+        <v>15</v>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>djl0V3o6</t>
+        </is>
+      </c>
+      <c r="W323" t="n">
+        <v>48</v>
+      </c>
+      <c r="X323" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y323" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z323" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA323" t="inlineStr"/>
+      <c r="AB323" t="inlineStr"/>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="AD323" t="inlineStr"/>
+      <c r="AE323" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF323" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="AG323" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH323" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AI323" t="n">
+        <v>2520000</v>
+      </c>
+      <c r="AJ323" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="AK323" t="inlineStr"/>
+      <c r="AL323" t="inlineStr"/>
+      <c r="AM323" t="inlineStr"/>
+      <c r="AN323" t="inlineStr"/>
+      <c r="AO323" t="inlineStr"/>
+      <c r="AP323" t="inlineStr"/>
+      <c r="AQ323" t="n">
+        <v>21.35714285714286</v>
+      </c>
+      <c r="AR323" t="n">
+        <v>181.5714285714286</v>
+      </c>
+      <c r="AS323" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT323" t="n">
+        <v>64.85714285714286</v>
+      </c>
+      <c r="AU323" t="n">
+        <v>1605714.285714286</v>
+      </c>
+      <c r="AV323" t="n">
+        <v>75.64285714285714</v>
+      </c>
+      <c r="AW323" t="inlineStr"/>
+      <c r="AX323" t="inlineStr"/>
+      <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr"/>
+      <c r="BA323" t="inlineStr"/>
+      <c r="BB323" t="inlineStr"/>
+      <c r="BC323" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BD323" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BE323" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF323" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG323" t="n">
+        <v>139</v>
+      </c>
+      <c r="BH323" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="BI323" t="n">
+        <v>150</v>
+      </c>
+      <c r="BJ323" t="inlineStr"/>
+      <c r="BK323" t="inlineStr"/>
+      <c r="BL323" t="inlineStr"/>
+      <c r="BM323" t="inlineStr"/>
+      <c r="BN323" t="inlineStr"/>
+      <c r="BO323" t="inlineStr"/>
+      <c r="BP323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>6cwSeTa4</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carrow road
+  norwich </t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>27137</v>
+      </c>
+      <c r="F324" t="n">
+        <v>26373</v>
+      </c>
+      <c r="G324" t="n">
+        <v>1</v>
+      </c>
+      <c r="H324" t="n">
+        <v>1</v>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="n">
+        <v>53</v>
+      </c>
+      <c r="N324" t="n">
+        <v>47</v>
+      </c>
+      <c r="O324" t="n">
+        <v>7</v>
+      </c>
+      <c r="P324" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>5</v>
+      </c>
+      <c r="R324" t="n">
+        <v>4</v>
+      </c>
+      <c r="S324" t="n">
+        <v>15</v>
+      </c>
+      <c r="T324" t="n">
+        <v>7</v>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="W324" t="n">
+        <v>48</v>
+      </c>
+      <c r="X324" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA324" t="inlineStr"/>
+      <c r="AB324" t="inlineStr"/>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr"/>
+      <c r="AE324" t="inlineStr"/>
+      <c r="AF324" t="inlineStr"/>
+      <c r="AG324" t="inlineStr"/>
+      <c r="AH324" t="inlineStr"/>
+      <c r="AI324" t="inlineStr"/>
+      <c r="AJ324" t="inlineStr"/>
+      <c r="AK324" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="AL324" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AM324" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN324" t="n">
+        <v>69.11111111111111</v>
+      </c>
+      <c r="AO324" t="n">
+        <v>3191666.666666667</v>
+      </c>
+      <c r="AP324" t="n">
+        <v>76.88888888888889</v>
+      </c>
+      <c r="AQ324" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AR324" t="n">
+        <v>178.8888888888889</v>
+      </c>
+      <c r="AS324" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT324" t="n">
+        <v>67.77777777777777</v>
+      </c>
+      <c r="AU324" t="n">
+        <v>1613888.888888889</v>
+      </c>
+      <c r="AV324" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AW324" t="n">
+        <v>20.92307692307692</v>
+      </c>
+      <c r="AX324" t="n">
+        <v>179.4615384615385</v>
+      </c>
+      <c r="AY324" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ324" t="n">
+        <v>65.46153846153847</v>
+      </c>
+      <c r="BA324" t="n">
+        <v>2605769.230769231</v>
+      </c>
+      <c r="BB324" t="n">
+        <v>75.84615384615384</v>
+      </c>
+      <c r="BC324" t="n">
+        <v>33</v>
+      </c>
+      <c r="BD324" t="n">
+        <v>186</v>
+      </c>
+      <c r="BE324" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF324" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG324" t="n">
+        <v>71</v>
+      </c>
+      <c r="BH324" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="BI324" t="n">
+        <v>71</v>
+      </c>
+      <c r="BJ324" t="n">
+        <v>22</v>
+      </c>
+      <c r="BK324" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="BL324" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM324" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN324" t="n">
+        <v>130</v>
+      </c>
+      <c r="BO324" t="n">
+        <v>2625000</v>
+      </c>
+      <c r="BP324" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>ENtzf7UG</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whitestone d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deepdale
+  preston </t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>23408</v>
+      </c>
+      <c r="F325" t="n">
+        <v>15245</v>
+      </c>
+      <c r="G325" t="n">
+        <v>1</v>
+      </c>
+      <c r="H325" t="n">
+        <v>0</v>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>x8IDVcbi</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="n">
+        <v>43</v>
+      </c>
+      <c r="N325" t="n">
+        <v>57</v>
+      </c>
+      <c r="O325" t="n">
+        <v>7</v>
+      </c>
+      <c r="P325" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>3</v>
+      </c>
+      <c r="R325" t="n">
+        <v>4</v>
+      </c>
+      <c r="S325" t="n">
+        <v>18</v>
+      </c>
+      <c r="T325" t="n">
+        <v>12</v>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>lGE8iEO1</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="W325" t="n">
+        <v>48</v>
+      </c>
+      <c r="X325" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y325" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z325" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA325" t="inlineStr"/>
+      <c r="AB325" t="inlineStr"/>
+      <c r="AC325" t="inlineStr"/>
+      <c r="AD325" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="AE325" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AF325" t="n">
+        <v>186.375</v>
+      </c>
+      <c r="AG325" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AH325" t="n">
+        <v>71.375</v>
+      </c>
+      <c r="AI325" t="n">
+        <v>6175000</v>
+      </c>
+      <c r="AJ325" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AK325" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL325" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AM325" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN325" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO325" t="n">
+        <v>2920000</v>
+      </c>
+      <c r="AP325" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AQ325" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AR325" t="n">
+        <v>180</v>
+      </c>
+      <c r="AS325" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT325" t="n">
+        <v>68.06666666666666</v>
+      </c>
+      <c r="AU325" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AV325" t="n">
+        <v>72.73333333333333</v>
+      </c>
+      <c r="AW325" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="AX325" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="AY325" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ325" t="n">
+        <v>66.55</v>
+      </c>
+      <c r="BA325" t="n">
+        <v>1503750</v>
+      </c>
+      <c r="BB325" t="n">
+        <v>72.95</v>
+      </c>
+      <c r="BC325" t="inlineStr"/>
+      <c r="BD325" t="inlineStr"/>
+      <c r="BE325" t="inlineStr"/>
+      <c r="BF325" t="inlineStr"/>
+      <c r="BG325" t="inlineStr"/>
+      <c r="BH325" t="inlineStr"/>
+      <c r="BI325" t="inlineStr"/>
+      <c r="BJ325" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="BK325" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="BL325" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM325" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN325" t="n">
+        <v>363</v>
+      </c>
+      <c r="BO325" t="n">
+        <v>16400000</v>
+      </c>
+      <c r="BP325" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>6BI0ASEc</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bet365 stadium
+  stoke on trent </t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>30089</v>
+      </c>
+      <c r="F326" t="n">
+        <v>24371</v>
+      </c>
+      <c r="G326" t="n">
+        <v>1</v>
+      </c>
+      <c r="H326" t="n">
+        <v>2</v>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>CCBWpzjj</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr"/>
+      <c r="M326" t="n">
+        <v>51</v>
+      </c>
+      <c r="N326" t="n">
+        <v>49</v>
+      </c>
+      <c r="O326" t="n">
+        <v>10</v>
+      </c>
+      <c r="P326" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>2</v>
+      </c>
+      <c r="R326" t="n">
+        <v>5</v>
+      </c>
+      <c r="S326" t="n">
+        <v>12</v>
+      </c>
+      <c r="T326" t="n">
+        <v>10</v>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="W326" t="n">
+        <v>48</v>
+      </c>
+      <c r="X326" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y326" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA326" t="inlineStr"/>
+      <c r="AB326" t="inlineStr"/>
+      <c r="AC326" t="inlineStr"/>
+      <c r="AD326" t="inlineStr"/>
+      <c r="AE326" t="n">
+        <v>23.125</v>
+      </c>
+      <c r="AF326" t="n">
+        <v>181.375</v>
+      </c>
+      <c r="AG326" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH326" t="n">
+        <v>67.625</v>
+      </c>
+      <c r="AI326" t="n">
+        <v>1893750</v>
+      </c>
+      <c r="AJ326" t="n">
+        <v>73.625</v>
+      </c>
+      <c r="AK326" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AL326" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="AM326" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN326" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AO326" t="n">
+        <v>2320000</v>
+      </c>
+      <c r="AP326" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AQ326" t="n">
+        <v>23.95238095238095</v>
+      </c>
+      <c r="AR326" t="n">
+        <v>182</v>
+      </c>
+      <c r="AS326" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT326" t="n">
+        <v>68.47619047619048</v>
+      </c>
+      <c r="AU326" t="n">
+        <v>2058809.523809524</v>
+      </c>
+      <c r="AV326" t="n">
+        <v>73.85714285714286</v>
+      </c>
+      <c r="AW326" t="n">
+        <v>24.4375</v>
+      </c>
+      <c r="AX326" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AY326" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ326" t="n">
+        <v>69.375</v>
+      </c>
+      <c r="BA326" t="n">
+        <v>2375000</v>
+      </c>
+      <c r="BB326" t="n">
+        <v>74</v>
+      </c>
+      <c r="BC326" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="BD326" t="n">
+        <v>185</v>
+      </c>
+      <c r="BE326" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF326" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG326" t="n">
+        <v>278</v>
+      </c>
+      <c r="BH326" t="n">
+        <v>5475000</v>
+      </c>
+      <c r="BI326" t="n">
+        <v>279</v>
+      </c>
+      <c r="BJ326" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK326" t="n">
+        <v>188</v>
+      </c>
+      <c r="BL326" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM326" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN326" t="n">
+        <v>70</v>
+      </c>
+      <c r="BO326" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="BP326" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>EyM886qA</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">martin s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium of light
+  sunderland </t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>48707</v>
+      </c>
+      <c r="F327" t="n">
+        <v>40096</v>
+      </c>
+      <c r="G327" t="n">
+        <v>1</v>
+      </c>
+      <c r="H327" t="n">
+        <v>0</v>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="n">
+        <v>39</v>
+      </c>
+      <c r="N327" t="n">
+        <v>61</v>
+      </c>
+      <c r="O327" t="n">
+        <v>15</v>
+      </c>
+      <c r="P327" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>3</v>
+      </c>
+      <c r="R327" t="n">
+        <v>1</v>
+      </c>
+      <c r="S327" t="n">
+        <v>15</v>
+      </c>
+      <c r="T327" t="n">
+        <v>19</v>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>pYaUUJs1</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="W327" t="n">
+        <v>48</v>
+      </c>
+      <c r="X327" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y327" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA327" t="inlineStr"/>
+      <c r="AB327" t="inlineStr"/>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="AE327" t="n">
+        <v>21.77777777777778</v>
+      </c>
+      <c r="AF327" t="n">
+        <v>181.4444444444445</v>
+      </c>
+      <c r="AG327" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH327" t="n">
+        <v>67.77777777777777</v>
+      </c>
+      <c r="AI327" t="n">
+        <v>2413888.888888889</v>
+      </c>
+      <c r="AJ327" t="n">
+        <v>76.66666666666667</v>
+      </c>
+      <c r="AK327" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AL327" t="n">
+        <v>182.5555555555555</v>
+      </c>
+      <c r="AM327" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN327" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="AO327" t="n">
+        <v>4444444.444444444</v>
+      </c>
+      <c r="AP327" t="n">
+        <v>78.44444444444444</v>
+      </c>
+      <c r="AQ327" t="n">
+        <v>23.42105263157895</v>
+      </c>
+      <c r="AR327" t="n">
+        <v>182.2105263157895</v>
+      </c>
+      <c r="AS327" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT327" t="n">
+        <v>68</v>
+      </c>
+      <c r="AU327" t="n">
+        <v>2328947.368421053</v>
+      </c>
+      <c r="AV327" t="n">
+        <v>74.78947368421052</v>
+      </c>
+      <c r="AW327" t="n">
+        <v>23.57142857142857</v>
+      </c>
+      <c r="AX327" t="n">
+        <v>186.8571428571429</v>
+      </c>
+      <c r="AY327" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ327" t="n">
+        <v>69.85714285714286</v>
+      </c>
+      <c r="BA327" t="n">
+        <v>2914285.714285714</v>
+      </c>
+      <c r="BB327" t="n">
+        <v>77.28571428571429</v>
+      </c>
+      <c r="BC327" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD327" t="n">
+        <v>183</v>
+      </c>
+      <c r="BE327" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF327" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG327" t="n">
+        <v>130</v>
+      </c>
+      <c r="BH327" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BI327" t="n">
+        <v>155</v>
+      </c>
+      <c r="BJ327" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BK327" t="n">
+        <v>181</v>
+      </c>
+      <c r="BL327" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM327" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN327" t="n">
+        <v>445</v>
+      </c>
+      <c r="BO327" t="n">
+        <v>43100000</v>
+      </c>
+      <c r="BP327" t="n">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>YPYtjbTr</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vicarage road
+  watford </t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>22200</v>
+      </c>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="n">
+        <v>2</v>
+      </c>
+      <c r="H328" t="n">
+        <v>1</v>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>Iug0YO0Q</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="n">
+        <v>68</v>
+      </c>
+      <c r="N328" t="n">
+        <v>32</v>
+      </c>
+      <c r="O328" t="n">
+        <v>12</v>
+      </c>
+      <c r="P328" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>3</v>
+      </c>
+      <c r="R328" t="n">
+        <v>3</v>
+      </c>
+      <c r="S328" t="n">
+        <v>10</v>
+      </c>
+      <c r="T328" t="n">
+        <v>11</v>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
+      <c r="W328" t="n">
+        <v>48</v>
+      </c>
+      <c r="X328" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y328" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA328" t="inlineStr"/>
+      <c r="AB328" t="inlineStr"/>
+      <c r="AC328" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="AD328" t="inlineStr"/>
+      <c r="AE328" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AF328" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="AG328" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH328" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="AI328" t="n">
+        <v>1788888.888888889</v>
+      </c>
+      <c r="AJ328" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="AK328" t="inlineStr"/>
+      <c r="AL328" t="inlineStr"/>
+      <c r="AM328" t="inlineStr"/>
+      <c r="AN328" t="inlineStr"/>
+      <c r="AO328" t="inlineStr"/>
+      <c r="AP328" t="inlineStr"/>
+      <c r="AQ328" t="n">
+        <v>24.27777777777778</v>
+      </c>
+      <c r="AR328" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="AS328" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT328" t="n">
+        <v>67.77777777777777</v>
+      </c>
+      <c r="AU328" t="n">
+        <v>1738888.888888889</v>
+      </c>
+      <c r="AV328" t="n">
+        <v>72.77777777777777</v>
+      </c>
+      <c r="AW328" t="inlineStr"/>
+      <c r="AX328" t="inlineStr"/>
+      <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr"/>
+      <c r="BA328" t="inlineStr"/>
+      <c r="BB328" t="inlineStr"/>
+      <c r="BC328" t="inlineStr"/>
+      <c r="BD328" t="inlineStr"/>
+      <c r="BE328" t="inlineStr"/>
+      <c r="BF328" t="inlineStr"/>
+      <c r="BG328" t="inlineStr"/>
+      <c r="BH328" t="inlineStr"/>
+      <c r="BI328" t="inlineStr"/>
+      <c r="BJ328" t="inlineStr"/>
+      <c r="BK328" t="inlineStr"/>
+      <c r="BL328" t="inlineStr"/>
+      <c r="BM328" t="inlineStr"/>
+      <c r="BN328" t="inlineStr"/>
+      <c r="BO328" t="inlineStr"/>
+      <c r="BP328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>zHg8u8FN</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="n">
+        <v>45528.35416666666</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kitchen a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ashton gate stadium
+  bristol </t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F329" t="n">
+        <v>21454</v>
+      </c>
+      <c r="G329" t="n">
+        <v>1</v>
+      </c>
+      <c r="H329" t="n">
+        <v>1</v>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>MahqU27I</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
+      <c r="M329" t="n">
+        <v>51</v>
+      </c>
+      <c r="N329" t="n">
+        <v>49</v>
+      </c>
+      <c r="O329" t="n">
+        <v>13</v>
+      </c>
+      <c r="P329" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>8</v>
+      </c>
+      <c r="R329" t="n">
+        <v>1</v>
+      </c>
+      <c r="S329" t="n">
+        <v>8</v>
+      </c>
+      <c r="T329" t="n">
+        <v>18</v>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
+      <c r="W329" t="n">
+        <v>48</v>
+      </c>
+      <c r="X329" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA329" t="inlineStr"/>
+      <c r="AB329" t="inlineStr"/>
+      <c r="AC329" t="inlineStr"/>
+      <c r="AD329" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="AE329" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AF329" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="AG329" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH329" t="n">
+        <v>68.875</v>
+      </c>
+      <c r="AI329" t="n">
+        <v>2087500</v>
+      </c>
+      <c r="AJ329" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AK329" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AL329" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AM329" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN329" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AO329" t="n">
+        <v>3860000</v>
+      </c>
+      <c r="AP329" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AQ329" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR329" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="AS329" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT329" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AU329" t="n">
+        <v>1484722.222222222</v>
+      </c>
+      <c r="AV329" t="n">
+        <v>73.27777777777777</v>
+      </c>
+      <c r="AW329" t="n">
+        <v>25.0625</v>
+      </c>
+      <c r="AX329" t="n">
+        <v>179</v>
+      </c>
+      <c r="AY329" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ329" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="BA329" t="n">
+        <v>2212500</v>
+      </c>
+      <c r="BB329" t="n">
+        <v>73.4375</v>
+      </c>
+      <c r="BC329" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD329" t="n">
+        <v>187</v>
+      </c>
+      <c r="BE329" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF329" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG329" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH329" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="BI329" t="n">
+        <v>73</v>
+      </c>
+      <c r="BJ329" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK329" t="n">
+        <v>185</v>
+      </c>
+      <c r="BL329" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM329" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN329" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO329" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="BP329" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>IycXZowo</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="n">
+        <v>45528.35416666666</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webb d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mkm stadium
+  hull </t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>25586</v>
+      </c>
+      <c r="F330" t="n">
+        <v>20009</v>
+      </c>
+      <c r="G330" t="n">
+        <v>0</v>
+      </c>
+      <c r="H330" t="n">
+        <v>0</v>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>S66R0t75</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
+      <c r="M330" t="n">
+        <v>71</v>
+      </c>
+      <c r="N330" t="n">
+        <v>29</v>
+      </c>
+      <c r="O330" t="n">
+        <v>14</v>
+      </c>
+      <c r="P330" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>4</v>
+      </c>
+      <c r="R330" t="n">
+        <v>5</v>
+      </c>
+      <c r="S330" t="n">
+        <v>12</v>
+      </c>
+      <c r="T330" t="n">
+        <v>16</v>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="W330" t="n">
+        <v>48</v>
+      </c>
+      <c r="X330" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA330" t="inlineStr"/>
+      <c r="AB330" t="inlineStr"/>
+      <c r="AC330" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="AD330" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="AE330" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AF330" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AG330" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH330" t="n">
+        <v>69.625</v>
+      </c>
+      <c r="AI330" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="AJ330" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AK330" t="n">
+        <v>27.22222222222222</v>
+      </c>
+      <c r="AL330" t="n">
+        <v>177.8888888888889</v>
+      </c>
+      <c r="AM330" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN330" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="AO330" t="n">
+        <v>2025000</v>
+      </c>
+      <c r="AP330" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AQ330" t="n">
+        <v>20.57142857142857</v>
+      </c>
+      <c r="AR330" t="n">
+        <v>179.9285714285714</v>
+      </c>
+      <c r="AS330" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT330" t="n">
+        <v>63.92857142857143</v>
+      </c>
+      <c r="AU330" t="n">
+        <v>2096071.428571429</v>
+      </c>
+      <c r="AV330" t="n">
+        <v>74.85714285714286</v>
+      </c>
+      <c r="AW330" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="AX330" t="n">
+        <v>180.5714285714286</v>
+      </c>
+      <c r="AY330" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ330" t="n">
+        <v>68</v>
+      </c>
+      <c r="BA330" t="n">
+        <v>1335714.285714286</v>
+      </c>
+      <c r="BB330" t="n">
+        <v>71.14285714285714</v>
+      </c>
+      <c r="BC330" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD330" t="n">
+        <v>181</v>
+      </c>
+      <c r="BE330" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF330" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG330" t="n">
+        <v>198</v>
+      </c>
+      <c r="BH330" t="n">
+        <v>5125000</v>
+      </c>
+      <c r="BI330" t="n">
+        <v>227</v>
+      </c>
+      <c r="BJ330" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK330" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BL330" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM330" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN330" t="n">
+        <v>143</v>
+      </c>
+      <c r="BO330" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="BP330" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>fXlrhoaT</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="n">
+        <v>45528.35416666666</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">loftus road
+  london </t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>18439</v>
+      </c>
+      <c r="F331" t="n">
+        <v>15285</v>
+      </c>
+      <c r="G331" t="n">
+        <v>1</v>
+      </c>
+      <c r="H331" t="n">
+        <v>1</v>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="n">
+        <v>55</v>
+      </c>
+      <c r="N331" t="n">
+        <v>45</v>
+      </c>
+      <c r="O331" t="n">
+        <v>31</v>
+      </c>
+      <c r="P331" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>10</v>
+      </c>
+      <c r="R331" t="n">
+        <v>1</v>
+      </c>
+      <c r="S331" t="n">
+        <v>11</v>
+      </c>
+      <c r="T331" t="n">
+        <v>14</v>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>WfXv1DCa</t>
+        </is>
+      </c>
+      <c r="W331" t="n">
+        <v>48</v>
+      </c>
+      <c r="X331" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA331" t="inlineStr"/>
+      <c r="AB331" t="inlineStr"/>
+      <c r="AC331" t="inlineStr"/>
+      <c r="AD331" t="inlineStr"/>
+      <c r="AE331" t="inlineStr"/>
+      <c r="AF331" t="inlineStr"/>
+      <c r="AG331" t="inlineStr"/>
+      <c r="AH331" t="inlineStr"/>
+      <c r="AI331" t="inlineStr"/>
+      <c r="AJ331" t="inlineStr"/>
+      <c r="AK331" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AL331" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="AM331" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN331" t="n">
+        <v>68</v>
+      </c>
+      <c r="AO331" t="n">
+        <v>2095000</v>
+      </c>
+      <c r="AP331" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AQ331" t="n">
+        <v>20.83333333333333</v>
+      </c>
+      <c r="AR331" t="n">
+        <v>182.1666666666667</v>
+      </c>
+      <c r="AS331" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT331" t="n">
+        <v>59.33333333333334</v>
+      </c>
+      <c r="AU331" t="n">
+        <v>712500</v>
+      </c>
+      <c r="AV331" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AW331" t="n">
+        <v>23.8125</v>
+      </c>
+      <c r="AX331" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AY331" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ331" t="n">
+        <v>67.1875</v>
+      </c>
+      <c r="BA331" t="n">
+        <v>1810937.5</v>
+      </c>
+      <c r="BB331" t="n">
+        <v>72.375</v>
+      </c>
+      <c r="BC331" t="n">
+        <v>28.66666666666667</v>
+      </c>
+      <c r="BD331" t="n">
+        <v>177.6666666666667</v>
+      </c>
+      <c r="BE331" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF331" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG331" t="n">
+        <v>212</v>
+      </c>
+      <c r="BH331" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="BI331" t="n">
+        <v>213</v>
+      </c>
+      <c r="BJ331" t="inlineStr"/>
+      <c r="BK331" t="inlineStr"/>
+      <c r="BL331" t="inlineStr"/>
+      <c r="BM331" t="inlineStr"/>
+      <c r="BN331" t="inlineStr"/>
+      <c r="BO331" t="inlineStr"/>
+      <c r="BP331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>j3zEnPMj</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="n">
+        <v>45527.66666666666</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hillsborough
+  sheffield </t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>39732</v>
+      </c>
+      <c r="F332" t="n">
+        <v>28800</v>
+      </c>
+      <c r="G332" t="n">
+        <v>0</v>
+      </c>
+      <c r="H332" t="n">
+        <v>2</v>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr"/>
+      <c r="L332" t="inlineStr"/>
+      <c r="M332" t="n">
+        <v>30</v>
+      </c>
+      <c r="N332" t="n">
+        <v>70</v>
+      </c>
+      <c r="O332" t="n">
+        <v>8</v>
+      </c>
+      <c r="P332" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>2</v>
+      </c>
+      <c r="R332" t="n">
+        <v>5</v>
+      </c>
+      <c r="S332" t="n">
+        <v>15</v>
+      </c>
+      <c r="T332" t="n">
+        <v>10</v>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="W332" t="n">
+        <v>48</v>
+      </c>
+      <c r="X332" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z332" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA332" t="inlineStr"/>
+      <c r="AB332" t="inlineStr"/>
+      <c r="AC332" t="inlineStr"/>
+      <c r="AD332" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="AE332" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AF332" t="n">
+        <v>181.625</v>
+      </c>
+      <c r="AG332" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH332" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AI332" t="n">
+        <v>1556250</v>
+      </c>
+      <c r="AJ332" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="AK332" t="n">
+        <v>23.625</v>
+      </c>
+      <c r="AL332" t="n">
+        <v>185</v>
+      </c>
+      <c r="AM332" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN332" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="AO332" t="n">
+        <v>6462500</v>
+      </c>
+      <c r="AP332" t="n">
+        <v>78.625</v>
+      </c>
+      <c r="AQ332" t="n">
+        <v>26.59090909090909</v>
+      </c>
+      <c r="AR332" t="n">
+        <v>182.2727272727273</v>
+      </c>
+      <c r="AS332" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT332" t="n">
+        <v>66.27272727272727</v>
+      </c>
+      <c r="AU332" t="n">
+        <v>1181818.181818182</v>
+      </c>
+      <c r="AV332" t="n">
+        <v>70.40909090909091</v>
+      </c>
+      <c r="AW332" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AX332" t="n">
+        <v>182</v>
+      </c>
+      <c r="AY332" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ332" t="n">
+        <v>72.09090909090909</v>
+      </c>
+      <c r="BA332" t="n">
+        <v>4545454.545454546</v>
+      </c>
+      <c r="BB332" t="n">
+        <v>76.54545454545455</v>
+      </c>
+      <c r="BC332" t="n">
+        <v>35</v>
+      </c>
+      <c r="BD332" t="n">
+        <v>193</v>
+      </c>
+      <c r="BE332" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF332" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG332" t="n">
+        <v>69</v>
+      </c>
+      <c r="BH332" t="n">
+        <v>150000</v>
+      </c>
+      <c r="BI332" t="n">
+        <v>69</v>
+      </c>
+      <c r="BJ332" t="inlineStr"/>
+      <c r="BK332" t="inlineStr"/>
+      <c r="BL332" t="inlineStr"/>
+      <c r="BM332" t="inlineStr"/>
+      <c r="BN332" t="inlineStr"/>
+      <c r="BO332" t="inlineStr"/>
+      <c r="BP332" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/england/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP332"/>
+  <dimension ref="A1:BP336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69795,6 +69795,840 @@
       <c r="BO332" t="inlineStr"/>
       <c r="BP332" t="inlineStr"/>
     </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="n">
+        <v>45529.52083333334</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>61276</v>
+      </c>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="n">
+        <v>2</v>
+      </c>
+      <c r="H333" t="n">
+        <v>0</v>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="K333" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L333" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M333" t="n">
+        <v>62</v>
+      </c>
+      <c r="N333" t="n">
+        <v>38</v>
+      </c>
+      <c r="O333" t="n">
+        <v>19</v>
+      </c>
+      <c r="P333" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>8</v>
+      </c>
+      <c r="R333" t="n">
+        <v>2</v>
+      </c>
+      <c r="S333" t="n">
+        <v>10</v>
+      </c>
+      <c r="T333" t="n">
+        <v>7</v>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="W333" t="n">
+        <v>48</v>
+      </c>
+      <c r="X333" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y333" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z333" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA333" t="inlineStr"/>
+      <c r="AB333" t="inlineStr"/>
+      <c r="AC333" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="AD333" t="inlineStr"/>
+      <c r="AE333" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AF333" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AG333" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH333" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="AI333" t="n">
+        <v>59500000</v>
+      </c>
+      <c r="AJ333" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="AK333" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AL333" t="n">
+        <v>184.5454545454545</v>
+      </c>
+      <c r="AM333" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN333" t="n">
+        <v>76.27272727272727</v>
+      </c>
+      <c r="AO333" t="n">
+        <v>10918181.81818182</v>
+      </c>
+      <c r="AP333" t="n">
+        <v>79.09090909090909</v>
+      </c>
+      <c r="AQ333" t="n">
+        <v>23.91304347826087</v>
+      </c>
+      <c r="AR333" t="n">
+        <v>181.695652173913</v>
+      </c>
+      <c r="AS333" t="n">
+        <v>1.869565217391304</v>
+      </c>
+      <c r="AT333" t="n">
+        <v>79.56521739130434</v>
+      </c>
+      <c r="AU333" t="n">
+        <v>31817391.30434782</v>
+      </c>
+      <c r="AV333" t="n">
+        <v>84.17391304347827</v>
+      </c>
+      <c r="AW333" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="AX333" t="n">
+        <v>178.5333333333333</v>
+      </c>
+      <c r="AY333" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="AZ333" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="BA333" t="n">
+        <v>8285000</v>
+      </c>
+      <c r="BB333" t="n">
+        <v>80.53333333333333</v>
+      </c>
+      <c r="BC333" t="inlineStr"/>
+      <c r="BD333" t="inlineStr"/>
+      <c r="BE333" t="inlineStr"/>
+      <c r="BF333" t="inlineStr"/>
+      <c r="BG333" t="inlineStr"/>
+      <c r="BH333" t="inlineStr"/>
+      <c r="BI333" t="inlineStr"/>
+      <c r="BJ333" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK333" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="BL333" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM333" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN333" t="n">
+        <v>153</v>
+      </c>
+      <c r="BO333" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="BP333" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>6RCbX36s</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="n">
+        <v>45529.41666666666</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>11307</v>
+      </c>
+      <c r="F334" t="n">
+        <v>11161</v>
+      </c>
+      <c r="G334" t="n">
+        <v>1</v>
+      </c>
+      <c r="H334" t="n">
+        <v>1</v>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="K334" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L334" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M334" t="n">
+        <v>39</v>
+      </c>
+      <c r="N334" t="n">
+        <v>61</v>
+      </c>
+      <c r="O334" t="n">
+        <v>16</v>
+      </c>
+      <c r="P334" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>4</v>
+      </c>
+      <c r="R334" t="n">
+        <v>5</v>
+      </c>
+      <c r="S334" t="n">
+        <v>19</v>
+      </c>
+      <c r="T334" t="n">
+        <v>8</v>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="W334" t="n">
+        <v>48</v>
+      </c>
+      <c r="X334" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z334" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA334" t="inlineStr"/>
+      <c r="AB334" t="inlineStr"/>
+      <c r="AC334" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="AD334" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="AE334" t="n">
+        <v>24.77777777777778</v>
+      </c>
+      <c r="AF334" t="n">
+        <v>179.8888888888889</v>
+      </c>
+      <c r="AG334" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AH334" t="n">
+        <v>75.33333333333333</v>
+      </c>
+      <c r="AI334" t="n">
+        <v>8233333.333333333</v>
+      </c>
+      <c r="AJ334" t="n">
+        <v>78.88888888888889</v>
+      </c>
+      <c r="AK334" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AL334" t="n">
+        <v>187.3</v>
+      </c>
+      <c r="AM334" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN334" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AO334" t="n">
+        <v>22330000</v>
+      </c>
+      <c r="AP334" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="AQ334" t="n">
+        <v>21.83333333333333</v>
+      </c>
+      <c r="AR334" t="n">
+        <v>180.0555555555555</v>
+      </c>
+      <c r="AS334" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT334" t="n">
+        <v>72.55555555555556</v>
+      </c>
+      <c r="AU334" t="n">
+        <v>7788888.888888889</v>
+      </c>
+      <c r="AV334" t="n">
+        <v>80.33333333333333</v>
+      </c>
+      <c r="AW334" t="n">
+        <v>25.94736842105263</v>
+      </c>
+      <c r="AX334" t="n">
+        <v>180.4736842105263</v>
+      </c>
+      <c r="AY334" t="n">
+        <v>1.473684210526316</v>
+      </c>
+      <c r="AZ334" t="n">
+        <v>76.31578947368421</v>
+      </c>
+      <c r="BA334" t="n">
+        <v>16646315.78947368</v>
+      </c>
+      <c r="BB334" t="n">
+        <v>80.36842105263158</v>
+      </c>
+      <c r="BC334" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD334" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="BE334" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF334" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG334" t="n">
+        <v>232</v>
+      </c>
+      <c r="BH334" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="BI334" t="n">
+        <v>237</v>
+      </c>
+      <c r="BJ334" t="n">
+        <v>24.85714285714286</v>
+      </c>
+      <c r="BK334" t="n">
+        <v>186.4285714285714</v>
+      </c>
+      <c r="BL334" t="n">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="BM334" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN334" t="n">
+        <v>540</v>
+      </c>
+      <c r="BO334" t="n">
+        <v>188375000</v>
+      </c>
+      <c r="BP334" t="n">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>61T7bt5t</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="n">
+        <v>45529.41666666666</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>31750</v>
+      </c>
+      <c r="F335" t="n">
+        <v>31235</v>
+      </c>
+      <c r="G335" t="n">
+        <v>2</v>
+      </c>
+      <c r="H335" t="n">
+        <v>6</v>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="K335" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L335" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M335" t="n">
+        <v>38</v>
+      </c>
+      <c r="N335" t="n">
+        <v>62</v>
+      </c>
+      <c r="O335" t="n">
+        <v>12</v>
+      </c>
+      <c r="P335" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>4</v>
+      </c>
+      <c r="R335" t="n">
+        <v>8</v>
+      </c>
+      <c r="S335" t="n">
+        <v>13</v>
+      </c>
+      <c r="T335" t="n">
+        <v>13</v>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="W335" t="n">
+        <v>48</v>
+      </c>
+      <c r="X335" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z335" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA335" t="inlineStr"/>
+      <c r="AB335" t="inlineStr"/>
+      <c r="AC335" t="inlineStr"/>
+      <c r="AD335" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="AE335" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AF335" t="n">
+        <v>182.125</v>
+      </c>
+      <c r="AG335" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH335" t="n">
+        <v>77.125</v>
+      </c>
+      <c r="AI335" t="n">
+        <v>13137500</v>
+      </c>
+      <c r="AJ335" t="n">
+        <v>79.625</v>
+      </c>
+      <c r="AK335" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AL335" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="AM335" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN335" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AO335" t="n">
+        <v>24050000</v>
+      </c>
+      <c r="AP335" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="AQ335" t="n">
+        <v>27.88235294117647</v>
+      </c>
+      <c r="AR335" t="n">
+        <v>178.7058823529412</v>
+      </c>
+      <c r="AS335" t="n">
+        <v>1.529411764705882</v>
+      </c>
+      <c r="AT335" t="n">
+        <v>76.29411764705883</v>
+      </c>
+      <c r="AU335" t="n">
+        <v>9617647.05882353</v>
+      </c>
+      <c r="AV335" t="n">
+        <v>78</v>
+      </c>
+      <c r="AW335" t="n">
+        <v>23.3125</v>
+      </c>
+      <c r="AX335" t="n">
+        <v>180</v>
+      </c>
+      <c r="AY335" t="n">
+        <v>1.5625</v>
+      </c>
+      <c r="AZ335" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="BA335" t="n">
+        <v>29906250</v>
+      </c>
+      <c r="BB335" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="BC335" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD335" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="BE335" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF335" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG335" t="n">
+        <v>156</v>
+      </c>
+      <c r="BH335" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="BI335" t="n">
+        <v>158</v>
+      </c>
+      <c r="BJ335" t="inlineStr"/>
+      <c r="BK335" t="inlineStr"/>
+      <c r="BL335" t="inlineStr"/>
+      <c r="BM335" t="inlineStr"/>
+      <c r="BN335" t="inlineStr"/>
+      <c r="BO335" t="inlineStr"/>
+      <c r="BP335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>pKIPNiIj</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="n">
+        <v>45529.45833333334</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langford o 
+  eng </t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>21088</v>
+      </c>
+      <c r="F336" t="n">
+        <v>20174</v>
+      </c>
+      <c r="G336" t="n">
+        <v>1</v>
+      </c>
+      <c r="H336" t="n">
+        <v>1</v>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr"/>
+      <c r="L336" t="inlineStr"/>
+      <c r="M336" t="n">
+        <v>58</v>
+      </c>
+      <c r="N336" t="n">
+        <v>42</v>
+      </c>
+      <c r="O336" t="n">
+        <v>9</v>
+      </c>
+      <c r="P336" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>4</v>
+      </c>
+      <c r="R336" t="n">
+        <v>3</v>
+      </c>
+      <c r="S336" t="n">
+        <v>15</v>
+      </c>
+      <c r="T336" t="n">
+        <v>14</v>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
+      <c r="W336" t="n">
+        <v>48</v>
+      </c>
+      <c r="X336" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y336" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z336" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA336" t="inlineStr"/>
+      <c r="AB336" t="inlineStr"/>
+      <c r="AC336" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="AD336" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="AE336" t="inlineStr"/>
+      <c r="AF336" t="inlineStr"/>
+      <c r="AG336" t="inlineStr"/>
+      <c r="AH336" t="inlineStr"/>
+      <c r="AI336" t="inlineStr"/>
+      <c r="AJ336" t="inlineStr"/>
+      <c r="AK336" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AL336" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AM336" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AN336" t="n">
+        <v>71.625</v>
+      </c>
+      <c r="AO336" t="n">
+        <v>2575000</v>
+      </c>
+      <c r="AP336" t="n">
+        <v>73.625</v>
+      </c>
+      <c r="AQ336" t="n">
+        <v>27.47058823529412</v>
+      </c>
+      <c r="AR336" t="n">
+        <v>179</v>
+      </c>
+      <c r="AS336" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT336" t="n">
+        <v>66.47058823529412</v>
+      </c>
+      <c r="AU336" t="n">
+        <v>963235.2941176471</v>
+      </c>
+      <c r="AV336" t="n">
+        <v>70.58823529411765</v>
+      </c>
+      <c r="AW336" t="n">
+        <v>24.84615384615385</v>
+      </c>
+      <c r="AX336" t="n">
+        <v>184.2307692307692</v>
+      </c>
+      <c r="AY336" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ336" t="n">
+        <v>67</v>
+      </c>
+      <c r="BA336" t="n">
+        <v>1432692.307692308</v>
+      </c>
+      <c r="BB336" t="n">
+        <v>70.84615384615384</v>
+      </c>
+      <c r="BC336" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BD336" t="n">
+        <v>178</v>
+      </c>
+      <c r="BE336" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF336" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG336" t="n">
+        <v>136</v>
+      </c>
+      <c r="BH336" t="n">
+        <v>2825000</v>
+      </c>
+      <c r="BI336" t="n">
+        <v>141</v>
+      </c>
+      <c r="BJ336" t="n">
+        <v>26</v>
+      </c>
+      <c r="BK336" t="n">
+        <v>186.3333333333333</v>
+      </c>
+      <c r="BL336" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM336" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN336" t="n">
+        <v>204</v>
+      </c>
+      <c r="BO336" t="n">
+        <v>4100000</v>
+      </c>
+      <c r="BP336" t="n">
+        <v>210</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/england/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP336"/>
+  <dimension ref="A1:BP363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70629,6 +70629,4404 @@
         <v>210</v>
       </c>
     </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>vDEpovX1</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="n">
+        <v>45534.65625</v>
+      </c>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="n">
+        <v>3</v>
+      </c>
+      <c r="H337" t="n">
+        <v>3</v>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>42DzSumJ</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>fBo5RVhP</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr"/>
+      <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr"/>
+      <c r="O337" t="inlineStr"/>
+      <c r="P337" t="inlineStr"/>
+      <c r="Q337" t="inlineStr"/>
+      <c r="R337" t="inlineStr"/>
+      <c r="S337" t="inlineStr"/>
+      <c r="T337" t="inlineStr"/>
+      <c r="U337" t="inlineStr"/>
+      <c r="V337" t="inlineStr"/>
+      <c r="W337" t="n">
+        <v>48</v>
+      </c>
+      <c r="X337" t="n">
+        <v>483</v>
+      </c>
+      <c r="Y337" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z337" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA337" t="inlineStr"/>
+      <c r="AB337" t="inlineStr"/>
+      <c r="AC337" t="inlineStr"/>
+      <c r="AD337" t="inlineStr"/>
+      <c r="AE337" t="inlineStr"/>
+      <c r="AF337" t="inlineStr"/>
+      <c r="AG337" t="inlineStr"/>
+      <c r="AH337" t="inlineStr"/>
+      <c r="AI337" t="inlineStr"/>
+      <c r="AJ337" t="inlineStr"/>
+      <c r="AK337" t="inlineStr"/>
+      <c r="AL337" t="inlineStr"/>
+      <c r="AM337" t="inlineStr"/>
+      <c r="AN337" t="inlineStr"/>
+      <c r="AO337" t="inlineStr"/>
+      <c r="AP337" t="inlineStr"/>
+      <c r="AQ337" t="inlineStr"/>
+      <c r="AR337" t="inlineStr"/>
+      <c r="AS337" t="inlineStr"/>
+      <c r="AT337" t="inlineStr"/>
+      <c r="AU337" t="inlineStr"/>
+      <c r="AV337" t="inlineStr"/>
+      <c r="AW337" t="inlineStr"/>
+      <c r="AX337" t="inlineStr"/>
+      <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr"/>
+      <c r="BA337" t="inlineStr"/>
+      <c r="BB337" t="inlineStr"/>
+      <c r="BC337" t="inlineStr"/>
+      <c r="BD337" t="inlineStr"/>
+      <c r="BE337" t="inlineStr"/>
+      <c r="BF337" t="inlineStr"/>
+      <c r="BG337" t="inlineStr"/>
+      <c r="BH337" t="inlineStr"/>
+      <c r="BI337" t="inlineStr"/>
+      <c r="BJ337" t="inlineStr"/>
+      <c r="BK337" t="inlineStr"/>
+      <c r="BL337" t="inlineStr"/>
+      <c r="BM337" t="inlineStr"/>
+      <c r="BN337" t="inlineStr"/>
+      <c r="BO337" t="inlineStr"/>
+      <c r="BP337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>hxlYyYo4</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="n">
+        <v>45532.66666666666</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city ground
+  nottingham </t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>30404</v>
+      </c>
+      <c r="F338" t="n">
+        <v>23083</v>
+      </c>
+      <c r="G338" t="n">
+        <v>1</v>
+      </c>
+      <c r="H338" t="n">
+        <v>2</v>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="n">
+        <v>40</v>
+      </c>
+      <c r="N338" t="n">
+        <v>60</v>
+      </c>
+      <c r="O338" t="n">
+        <v>13</v>
+      </c>
+      <c r="P338" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>3</v>
+      </c>
+      <c r="R338" t="n">
+        <v>7</v>
+      </c>
+      <c r="S338" t="n">
+        <v>13</v>
+      </c>
+      <c r="T338" t="n">
+        <v>6</v>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="W338" t="n">
+        <v>48</v>
+      </c>
+      <c r="X338" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y338" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z338" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA338" t="inlineStr"/>
+      <c r="AB338" t="inlineStr"/>
+      <c r="AC338" t="inlineStr"/>
+      <c r="AD338" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="AE338" t="inlineStr"/>
+      <c r="AF338" t="inlineStr"/>
+      <c r="AG338" t="inlineStr"/>
+      <c r="AH338" t="inlineStr"/>
+      <c r="AI338" t="inlineStr"/>
+      <c r="AJ338" t="inlineStr"/>
+      <c r="AK338" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AL338" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="AM338" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN338" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="AO338" t="n">
+        <v>28360000</v>
+      </c>
+      <c r="AP338" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="AQ338" t="n">
+        <v>23.5625</v>
+      </c>
+      <c r="AR338" t="n">
+        <v>184.0625</v>
+      </c>
+      <c r="AS338" t="n">
+        <v>1.5625</v>
+      </c>
+      <c r="AT338" t="n">
+        <v>75.5625</v>
+      </c>
+      <c r="AU338" t="n">
+        <v>11762500</v>
+      </c>
+      <c r="AV338" t="n">
+        <v>80.5625</v>
+      </c>
+      <c r="AW338" t="n">
+        <v>25.9375</v>
+      </c>
+      <c r="AX338" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AY338" t="n">
+        <v>1.4375</v>
+      </c>
+      <c r="AZ338" t="n">
+        <v>79.125</v>
+      </c>
+      <c r="BA338" t="n">
+        <v>28105000</v>
+      </c>
+      <c r="BB338" t="n">
+        <v>81.5625</v>
+      </c>
+      <c r="BC338" t="inlineStr"/>
+      <c r="BD338" t="inlineStr"/>
+      <c r="BE338" t="inlineStr"/>
+      <c r="BF338" t="inlineStr"/>
+      <c r="BG338" t="inlineStr"/>
+      <c r="BH338" t="inlineStr"/>
+      <c r="BI338" t="inlineStr"/>
+      <c r="BJ338" t="inlineStr"/>
+      <c r="BK338" t="inlineStr"/>
+      <c r="BL338" t="inlineStr"/>
+      <c r="BM338" t="inlineStr"/>
+      <c r="BN338" t="inlineStr"/>
+      <c r="BO338" t="inlineStr"/>
+      <c r="BP338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>U32wGjPp</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="n">
+        <v>45532.65625</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">linington j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the cherry red records stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>9215</v>
+      </c>
+      <c r="F339" t="n">
+        <v>7934</v>
+      </c>
+      <c r="G339" t="n">
+        <v>3</v>
+      </c>
+      <c r="H339" t="n">
+        <v>2</v>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>4KREuF43</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="n">
+        <v>21</v>
+      </c>
+      <c r="N339" t="n">
+        <v>79</v>
+      </c>
+      <c r="O339" t="n">
+        <v>2</v>
+      </c>
+      <c r="P339" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>2</v>
+      </c>
+      <c r="R339" t="n">
+        <v>5</v>
+      </c>
+      <c r="S339" t="n">
+        <v>13</v>
+      </c>
+      <c r="T339" t="n">
+        <v>10</v>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>zHJOSLsG</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="W339" t="n">
+        <v>48</v>
+      </c>
+      <c r="X339" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y339" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z339" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA339" t="inlineStr"/>
+      <c r="AB339" t="inlineStr"/>
+      <c r="AC339" t="inlineStr"/>
+      <c r="AD339" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="AE339" t="inlineStr"/>
+      <c r="AF339" t="inlineStr"/>
+      <c r="AG339" t="inlineStr"/>
+      <c r="AH339" t="inlineStr"/>
+      <c r="AI339" t="inlineStr"/>
+      <c r="AJ339" t="inlineStr"/>
+      <c r="AK339" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL339" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="AM339" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AN339" t="n">
+        <v>71</v>
+      </c>
+      <c r="AO339" t="n">
+        <v>3537500</v>
+      </c>
+      <c r="AP339" t="n">
+        <v>73.625</v>
+      </c>
+      <c r="AQ339" t="inlineStr"/>
+      <c r="AR339" t="inlineStr"/>
+      <c r="AS339" t="inlineStr"/>
+      <c r="AT339" t="inlineStr"/>
+      <c r="AU339" t="inlineStr"/>
+      <c r="AV339" t="inlineStr"/>
+      <c r="AW339" t="n">
+        <v>24.04545454545455</v>
+      </c>
+      <c r="AX339" t="n">
+        <v>181.8636363636364</v>
+      </c>
+      <c r="AY339" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AZ339" t="n">
+        <v>69.22727272727273</v>
+      </c>
+      <c r="BA339" t="n">
+        <v>2796590.909090909</v>
+      </c>
+      <c r="BB339" t="n">
+        <v>75.22727272727273</v>
+      </c>
+      <c r="BC339" t="inlineStr"/>
+      <c r="BD339" t="inlineStr"/>
+      <c r="BE339" t="inlineStr"/>
+      <c r="BF339" t="inlineStr"/>
+      <c r="BG339" t="inlineStr"/>
+      <c r="BH339" t="inlineStr"/>
+      <c r="BI339" t="inlineStr"/>
+      <c r="BJ339" t="inlineStr"/>
+      <c r="BK339" t="inlineStr"/>
+      <c r="BL339" t="inlineStr"/>
+      <c r="BM339" t="inlineStr"/>
+      <c r="BN339" t="inlineStr"/>
+      <c r="BO339" t="inlineStr"/>
+      <c r="BP339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>hGzqjO6E</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="n">
+        <v>45532.65625</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nield t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>33280</v>
+      </c>
+      <c r="F340" t="n">
+        <v>7225</v>
+      </c>
+      <c r="G340" t="n">
+        <v>3</v>
+      </c>
+      <c r="H340" t="n">
+        <v>5</v>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr"/>
+      <c r="L340" t="inlineStr"/>
+      <c r="M340" t="n">
+        <v>27</v>
+      </c>
+      <c r="N340" t="n">
+        <v>73</v>
+      </c>
+      <c r="O340" t="n">
+        <v>10</v>
+      </c>
+      <c r="P340" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>4</v>
+      </c>
+      <c r="R340" t="n">
+        <v>8</v>
+      </c>
+      <c r="S340" t="n">
+        <v>12</v>
+      </c>
+      <c r="T340" t="n">
+        <v>4</v>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="W340" t="n">
+        <v>48</v>
+      </c>
+      <c r="X340" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y340" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z340" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA340" t="inlineStr"/>
+      <c r="AB340" t="inlineStr"/>
+      <c r="AC340" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="AD340" t="inlineStr"/>
+      <c r="AE340" t="inlineStr"/>
+      <c r="AF340" t="inlineStr"/>
+      <c r="AG340" t="inlineStr"/>
+      <c r="AH340" t="inlineStr"/>
+      <c r="AI340" t="inlineStr"/>
+      <c r="AJ340" t="inlineStr"/>
+      <c r="AK340" t="inlineStr"/>
+      <c r="AL340" t="inlineStr"/>
+      <c r="AM340" t="inlineStr"/>
+      <c r="AN340" t="inlineStr"/>
+      <c r="AO340" t="inlineStr"/>
+      <c r="AP340" t="inlineStr"/>
+      <c r="AQ340" t="inlineStr"/>
+      <c r="AR340" t="inlineStr"/>
+      <c r="AS340" t="inlineStr"/>
+      <c r="AT340" t="inlineStr"/>
+      <c r="AU340" t="inlineStr"/>
+      <c r="AV340" t="inlineStr"/>
+      <c r="AW340" t="n">
+        <v>24.46153846153846</v>
+      </c>
+      <c r="AX340" t="n">
+        <v>178.7692307692308</v>
+      </c>
+      <c r="AY340" t="n">
+        <v>1.230769230769231</v>
+      </c>
+      <c r="AZ340" t="n">
+        <v>68.46153846153847</v>
+      </c>
+      <c r="BA340" t="n">
+        <v>3392307.692307692</v>
+      </c>
+      <c r="BB340" t="n">
+        <v>77.30769230769231</v>
+      </c>
+      <c r="BC340" t="inlineStr"/>
+      <c r="BD340" t="inlineStr"/>
+      <c r="BE340" t="inlineStr"/>
+      <c r="BF340" t="inlineStr"/>
+      <c r="BG340" t="inlineStr"/>
+      <c r="BH340" t="inlineStr"/>
+      <c r="BI340" t="inlineStr"/>
+      <c r="BJ340" t="inlineStr"/>
+      <c r="BK340" t="inlineStr"/>
+      <c r="BL340" t="inlineStr"/>
+      <c r="BM340" t="inlineStr"/>
+      <c r="BN340" t="inlineStr"/>
+      <c r="BO340" t="inlineStr"/>
+      <c r="BP340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>OrHrRGXo</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="n">
+        <v>45532.65625</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">howard p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colchester community stadium
+  colchester </t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>10105</v>
+      </c>
+      <c r="F341" t="n">
+        <v>6716</v>
+      </c>
+      <c r="G341" t="n">
+        <v>0</v>
+      </c>
+      <c r="H341" t="n">
+        <v>1</v>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>xYu73rNn</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr"/>
+      <c r="M341" t="n">
+        <v>27</v>
+      </c>
+      <c r="N341" t="n">
+        <v>73</v>
+      </c>
+      <c r="O341" t="n">
+        <v>5</v>
+      </c>
+      <c r="P341" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>3</v>
+      </c>
+      <c r="R341" t="n">
+        <v>3</v>
+      </c>
+      <c r="S341" t="n">
+        <v>13</v>
+      </c>
+      <c r="T341" t="n">
+        <v>9</v>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>MiVxbVgA</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="W341" t="n">
+        <v>48</v>
+      </c>
+      <c r="X341" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y341" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z341" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA341" t="inlineStr"/>
+      <c r="AB341" t="inlineStr"/>
+      <c r="AC341" t="inlineStr"/>
+      <c r="AD341" t="inlineStr"/>
+      <c r="AE341" t="inlineStr"/>
+      <c r="AF341" t="inlineStr"/>
+      <c r="AG341" t="inlineStr"/>
+      <c r="AH341" t="inlineStr"/>
+      <c r="AI341" t="inlineStr"/>
+      <c r="AJ341" t="inlineStr"/>
+      <c r="AK341" t="inlineStr"/>
+      <c r="AL341" t="inlineStr"/>
+      <c r="AM341" t="inlineStr"/>
+      <c r="AN341" t="inlineStr"/>
+      <c r="AO341" t="inlineStr"/>
+      <c r="AP341" t="inlineStr"/>
+      <c r="AQ341" t="inlineStr"/>
+      <c r="AR341" t="inlineStr"/>
+      <c r="AS341" t="inlineStr"/>
+      <c r="AT341" t="inlineStr"/>
+      <c r="AU341" t="inlineStr"/>
+      <c r="AV341" t="inlineStr"/>
+      <c r="AW341" t="n">
+        <v>23.05555555555556</v>
+      </c>
+      <c r="AX341" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AY341" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AZ341" t="n">
+        <v>72.61111111111111</v>
+      </c>
+      <c r="BA341" t="n">
+        <v>7887500</v>
+      </c>
+      <c r="BB341" t="n">
+        <v>77.77777777777777</v>
+      </c>
+      <c r="BC341" t="inlineStr"/>
+      <c r="BD341" t="inlineStr"/>
+      <c r="BE341" t="inlineStr"/>
+      <c r="BF341" t="inlineStr"/>
+      <c r="BG341" t="inlineStr"/>
+      <c r="BH341" t="inlineStr"/>
+      <c r="BI341" t="inlineStr"/>
+      <c r="BJ341" t="inlineStr"/>
+      <c r="BK341" t="inlineStr"/>
+      <c r="BL341" t="inlineStr"/>
+      <c r="BM341" t="inlineStr"/>
+      <c r="BN341" t="inlineStr"/>
+      <c r="BO341" t="inlineStr"/>
+      <c r="BP341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>WQF2UUMt</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="n">
+        <v>45532.65625</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toner b 
+  eng </t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>21088</v>
+      </c>
+      <c r="F342" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G342" t="n">
+        <v>0</v>
+      </c>
+      <c r="H342" t="n">
+        <v>1</v>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>hl2V5JIl</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr"/>
+      <c r="L342" t="inlineStr"/>
+      <c r="M342" t="n">
+        <v>73</v>
+      </c>
+      <c r="N342" t="n">
+        <v>27</v>
+      </c>
+      <c r="O342" t="n">
+        <v>6</v>
+      </c>
+      <c r="P342" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>0</v>
+      </c>
+      <c r="R342" t="n">
+        <v>2</v>
+      </c>
+      <c r="S342" t="n">
+        <v>12</v>
+      </c>
+      <c r="T342" t="n">
+        <v>9</v>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>65pf39vc</t>
+        </is>
+      </c>
+      <c r="W342" t="n">
+        <v>48</v>
+      </c>
+      <c r="X342" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y342" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z342" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA342" t="inlineStr"/>
+      <c r="AB342" t="inlineStr"/>
+      <c r="AC342" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="AD342" t="inlineStr"/>
+      <c r="AE342" t="inlineStr"/>
+      <c r="AF342" t="inlineStr"/>
+      <c r="AG342" t="inlineStr"/>
+      <c r="AH342" t="inlineStr"/>
+      <c r="AI342" t="inlineStr"/>
+      <c r="AJ342" t="inlineStr"/>
+      <c r="AK342" t="inlineStr"/>
+      <c r="AL342" t="inlineStr"/>
+      <c r="AM342" t="inlineStr"/>
+      <c r="AN342" t="inlineStr"/>
+      <c r="AO342" t="inlineStr"/>
+      <c r="AP342" t="inlineStr"/>
+      <c r="AQ342" t="n">
+        <v>26.64285714285714</v>
+      </c>
+      <c r="AR342" t="n">
+        <v>176.8571428571429</v>
+      </c>
+      <c r="AS342" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT342" t="n">
+        <v>67.78571428571429</v>
+      </c>
+      <c r="AU342" t="n">
+        <v>1387500</v>
+      </c>
+      <c r="AV342" t="n">
+        <v>71.35714285714286</v>
+      </c>
+      <c r="AW342" t="inlineStr"/>
+      <c r="AX342" t="inlineStr"/>
+      <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr"/>
+      <c r="BA342" t="inlineStr"/>
+      <c r="BB342" t="inlineStr"/>
+      <c r="BC342" t="inlineStr"/>
+      <c r="BD342" t="inlineStr"/>
+      <c r="BE342" t="inlineStr"/>
+      <c r="BF342" t="inlineStr"/>
+      <c r="BG342" t="inlineStr"/>
+      <c r="BH342" t="inlineStr"/>
+      <c r="BI342" t="inlineStr"/>
+      <c r="BJ342" t="inlineStr"/>
+      <c r="BK342" t="inlineStr"/>
+      <c r="BL342" t="inlineStr"/>
+      <c r="BM342" t="inlineStr"/>
+      <c r="BN342" t="inlineStr"/>
+      <c r="BO342" t="inlineStr"/>
+      <c r="BP342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>rkazN4LU</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="n">
+        <v>45532.65625</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F343" t="n">
+        <v>47381</v>
+      </c>
+      <c r="G343" t="n">
+        <v>1</v>
+      </c>
+      <c r="H343" t="n">
+        <v>0</v>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr"/>
+      <c r="L343" t="inlineStr"/>
+      <c r="M343" t="n">
+        <v>46</v>
+      </c>
+      <c r="N343" t="n">
+        <v>54</v>
+      </c>
+      <c r="O343" t="n">
+        <v>15</v>
+      </c>
+      <c r="P343" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>4</v>
+      </c>
+      <c r="R343" t="n">
+        <v>4</v>
+      </c>
+      <c r="S343" t="n">
+        <v>15</v>
+      </c>
+      <c r="T343" t="n">
+        <v>13</v>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="W343" t="n">
+        <v>48</v>
+      </c>
+      <c r="X343" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y343" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z343" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA343" t="inlineStr"/>
+      <c r="AB343" t="inlineStr"/>
+      <c r="AC343" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="AD343" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="AE343" t="n">
+        <v>27.625</v>
+      </c>
+      <c r="AF343" t="n">
+        <v>181.125</v>
+      </c>
+      <c r="AG343" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH343" t="n">
+        <v>79.125</v>
+      </c>
+      <c r="AI343" t="n">
+        <v>18425000</v>
+      </c>
+      <c r="AJ343" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="AK343" t="n">
+        <v>23.88888888888889</v>
+      </c>
+      <c r="AL343" t="n">
+        <v>181.2222222222222</v>
+      </c>
+      <c r="AM343" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AN343" t="n">
+        <v>73.44444444444444</v>
+      </c>
+      <c r="AO343" t="n">
+        <v>6966666.666666667</v>
+      </c>
+      <c r="AP343" t="n">
+        <v>79.22222222222223</v>
+      </c>
+      <c r="AQ343" t="n">
+        <v>25.11764705882353</v>
+      </c>
+      <c r="AR343" t="n">
+        <v>182.0588235294118</v>
+      </c>
+      <c r="AS343" t="n">
+        <v>2.117647058823529</v>
+      </c>
+      <c r="AT343" t="n">
+        <v>78.76470588235294</v>
+      </c>
+      <c r="AU343" t="n">
+        <v>22947058.82352941</v>
+      </c>
+      <c r="AV343" t="n">
+        <v>82.05882352941177</v>
+      </c>
+      <c r="AW343" t="n">
+        <v>22.88235294117647</v>
+      </c>
+      <c r="AX343" t="n">
+        <v>178.2352941176471</v>
+      </c>
+      <c r="AY343" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ343" t="n">
+        <v>74.05882352941177</v>
+      </c>
+      <c r="BA343" t="n">
+        <v>8494117.647058824</v>
+      </c>
+      <c r="BB343" t="n">
+        <v>79.47058823529412</v>
+      </c>
+      <c r="BC343" t="inlineStr"/>
+      <c r="BD343" t="inlineStr"/>
+      <c r="BE343" t="inlineStr"/>
+      <c r="BF343" t="inlineStr"/>
+      <c r="BG343" t="inlineStr"/>
+      <c r="BH343" t="inlineStr"/>
+      <c r="BI343" t="inlineStr"/>
+      <c r="BJ343" t="inlineStr"/>
+      <c r="BK343" t="inlineStr"/>
+      <c r="BL343" t="inlineStr"/>
+      <c r="BM343" t="inlineStr"/>
+      <c r="BN343" t="inlineStr"/>
+      <c r="BO343" t="inlineStr"/>
+      <c r="BP343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>GEugARyP</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="n">
+        <v>45532.64583333334</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>31750</v>
+      </c>
+      <c r="F344" t="n">
+        <v>19236</v>
+      </c>
+      <c r="G344" t="n">
+        <v>2</v>
+      </c>
+      <c r="H344" t="n">
+        <v>0</v>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr"/>
+      <c r="M344" t="n">
+        <v>52</v>
+      </c>
+      <c r="N344" t="n">
+        <v>48</v>
+      </c>
+      <c r="O344" t="n">
+        <v>17</v>
+      </c>
+      <c r="P344" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>6</v>
+      </c>
+      <c r="R344" t="n">
+        <v>0</v>
+      </c>
+      <c r="S344" t="n">
+        <v>14</v>
+      </c>
+      <c r="T344" t="n">
+        <v>12</v>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="W344" t="n">
+        <v>48</v>
+      </c>
+      <c r="X344" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y344" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z344" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA344" t="inlineStr"/>
+      <c r="AB344" t="inlineStr"/>
+      <c r="AC344" t="inlineStr"/>
+      <c r="AD344" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="AE344" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AF344" t="n">
+        <v>180.875</v>
+      </c>
+      <c r="AG344" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH344" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AI344" t="n">
+        <v>7512500</v>
+      </c>
+      <c r="AJ344" t="n">
+        <v>78</v>
+      </c>
+      <c r="AK344" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AL344" t="n">
+        <v>185.2222222222222</v>
+      </c>
+      <c r="AM344" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN344" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="AO344" t="n">
+        <v>3055555.555555556</v>
+      </c>
+      <c r="AP344" t="n">
+        <v>76.77777777777777</v>
+      </c>
+      <c r="AQ344" t="n">
+        <v>27.47058823529412</v>
+      </c>
+      <c r="AR344" t="n">
+        <v>179.8235294117647</v>
+      </c>
+      <c r="AS344" t="n">
+        <v>1.470588235294118</v>
+      </c>
+      <c r="AT344" t="n">
+        <v>76.17647058823529</v>
+      </c>
+      <c r="AU344" t="n">
+        <v>9835294.117647059</v>
+      </c>
+      <c r="AV344" t="n">
+        <v>78.17647058823529</v>
+      </c>
+      <c r="AW344" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AX344" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="AY344" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="AZ344" t="n">
+        <v>71.91666666666667</v>
+      </c>
+      <c r="BA344" t="n">
+        <v>4525000</v>
+      </c>
+      <c r="BB344" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="BC344" t="inlineStr"/>
+      <c r="BD344" t="inlineStr"/>
+      <c r="BE344" t="inlineStr"/>
+      <c r="BF344" t="inlineStr"/>
+      <c r="BG344" t="inlineStr"/>
+      <c r="BH344" t="inlineStr"/>
+      <c r="BI344" t="inlineStr"/>
+      <c r="BJ344" t="inlineStr"/>
+      <c r="BK344" t="inlineStr"/>
+      <c r="BL344" t="inlineStr"/>
+      <c r="BM344" t="inlineStr"/>
+      <c r="BN344" t="inlineStr"/>
+      <c r="BO344" t="inlineStr"/>
+      <c r="BP344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>Wn71woN8</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="n">
+        <v>45531.66666666666</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stroud k 
+  eng </t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  andrew s stadium
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>29409</v>
+      </c>
+      <c r="F345" t="n">
+        <v>11949</v>
+      </c>
+      <c r="G345" t="n">
+        <v>0</v>
+      </c>
+      <c r="H345" t="n">
+        <v>2</v>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>SWk4muv7</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr"/>
+      <c r="M345" t="n">
+        <v>58</v>
+      </c>
+      <c r="N345" t="n">
+        <v>42</v>
+      </c>
+      <c r="O345" t="n">
+        <v>16</v>
+      </c>
+      <c r="P345" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>4</v>
+      </c>
+      <c r="R345" t="n">
+        <v>2</v>
+      </c>
+      <c r="S345" t="n">
+        <v>18</v>
+      </c>
+      <c r="T345" t="n">
+        <v>18</v>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>Uu6L6Igl</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="W345" t="n">
+        <v>48</v>
+      </c>
+      <c r="X345" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y345" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z345" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA345" t="inlineStr"/>
+      <c r="AB345" t="inlineStr"/>
+      <c r="AC345" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="AD345" t="inlineStr"/>
+      <c r="AE345" t="inlineStr"/>
+      <c r="AF345" t="inlineStr"/>
+      <c r="AG345" t="inlineStr"/>
+      <c r="AH345" t="inlineStr"/>
+      <c r="AI345" t="inlineStr"/>
+      <c r="AJ345" t="inlineStr"/>
+      <c r="AK345" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AL345" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="AM345" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN345" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AO345" t="n">
+        <v>6320000</v>
+      </c>
+      <c r="AP345" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AQ345" t="n">
+        <v>25.92857142857143</v>
+      </c>
+      <c r="AR345" t="n">
+        <v>177.7857142857143</v>
+      </c>
+      <c r="AS345" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT345" t="n">
+        <v>67.35714285714286</v>
+      </c>
+      <c r="AU345" t="n">
+        <v>1576785.714285714</v>
+      </c>
+      <c r="AV345" t="n">
+        <v>70.85714285714286</v>
+      </c>
+      <c r="AW345" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AX345" t="n">
+        <v>182.95</v>
+      </c>
+      <c r="AY345" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ345" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="BA345" t="n">
+        <v>9435000</v>
+      </c>
+      <c r="BB345" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="BC345" t="inlineStr"/>
+      <c r="BD345" t="inlineStr"/>
+      <c r="BE345" t="inlineStr"/>
+      <c r="BF345" t="inlineStr"/>
+      <c r="BG345" t="inlineStr"/>
+      <c r="BH345" t="inlineStr"/>
+      <c r="BI345" t="inlineStr"/>
+      <c r="BJ345" t="inlineStr"/>
+      <c r="BK345" t="inlineStr"/>
+      <c r="BL345" t="inlineStr"/>
+      <c r="BM345" t="inlineStr"/>
+      <c r="BN345" t="inlineStr"/>
+      <c r="BO345" t="inlineStr"/>
+      <c r="BP345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>EkqxE9x0</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="n">
+        <v>45531.66666666666</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donohue m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F346" t="n">
+        <v>12503</v>
+      </c>
+      <c r="G346" t="n">
+        <v>4</v>
+      </c>
+      <c r="H346" t="n">
+        <v>0</v>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr"/>
+      <c r="L346" t="inlineStr"/>
+      <c r="M346" t="n">
+        <v>43</v>
+      </c>
+      <c r="N346" t="n">
+        <v>57</v>
+      </c>
+      <c r="O346" t="n">
+        <v>13</v>
+      </c>
+      <c r="P346" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>5</v>
+      </c>
+      <c r="R346" t="n">
+        <v>3</v>
+      </c>
+      <c r="S346" t="n">
+        <v>13</v>
+      </c>
+      <c r="T346" t="n">
+        <v>5</v>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="W346" t="n">
+        <v>48</v>
+      </c>
+      <c r="X346" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y346" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z346" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA346" t="inlineStr"/>
+      <c r="AB346" t="inlineStr"/>
+      <c r="AC346" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="AD346" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="AE346" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="AF346" t="n">
+        <v>181.7777777777778</v>
+      </c>
+      <c r="AG346" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AH346" t="n">
+        <v>77</v>
+      </c>
+      <c r="AI346" t="n">
+        <v>15088888.88888889</v>
+      </c>
+      <c r="AJ346" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK346" t="inlineStr"/>
+      <c r="AL346" t="inlineStr"/>
+      <c r="AM346" t="inlineStr"/>
+      <c r="AN346" t="inlineStr"/>
+      <c r="AO346" t="inlineStr"/>
+      <c r="AP346" t="inlineStr"/>
+      <c r="AQ346" t="n">
+        <v>25.94736842105263</v>
+      </c>
+      <c r="AR346" t="n">
+        <v>184.1052631578947</v>
+      </c>
+      <c r="AS346" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AT346" t="n">
+        <v>75</v>
+      </c>
+      <c r="AU346" t="n">
+        <v>8157894.736842105</v>
+      </c>
+      <c r="AV346" t="n">
+        <v>78.42105263157895</v>
+      </c>
+      <c r="AW346" t="n">
+        <v>26.41666666666667</v>
+      </c>
+      <c r="AX346" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AY346" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ346" t="n">
+        <v>71.91666666666667</v>
+      </c>
+      <c r="BA346" t="n">
+        <v>2841666.666666667</v>
+      </c>
+      <c r="BB346" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="BC346" t="inlineStr"/>
+      <c r="BD346" t="inlineStr"/>
+      <c r="BE346" t="inlineStr"/>
+      <c r="BF346" t="inlineStr"/>
+      <c r="BG346" t="inlineStr"/>
+      <c r="BH346" t="inlineStr"/>
+      <c r="BI346" t="inlineStr"/>
+      <c r="BJ346" t="inlineStr"/>
+      <c r="BK346" t="inlineStr"/>
+      <c r="BL346" t="inlineStr"/>
+      <c r="BM346" t="inlineStr"/>
+      <c r="BN346" t="inlineStr"/>
+      <c r="BO346" t="inlineStr"/>
+      <c r="BP346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>dUjtW2Fr</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reeves t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oakwell
+  barnsley </t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>23287</v>
+      </c>
+      <c r="F347" t="n">
+        <v>10739</v>
+      </c>
+      <c r="G347" t="n">
+        <v>1</v>
+      </c>
+      <c r="H347" t="n">
+        <v>0</v>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>UNGEKMx6</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr"/>
+      <c r="M347" t="n">
+        <v>34</v>
+      </c>
+      <c r="N347" t="n">
+        <v>66</v>
+      </c>
+      <c r="O347" t="n">
+        <v>9</v>
+      </c>
+      <c r="P347" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>2</v>
+      </c>
+      <c r="R347" t="n">
+        <v>4</v>
+      </c>
+      <c r="S347" t="n">
+        <v>14</v>
+      </c>
+      <c r="T347" t="n">
+        <v>6</v>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>bNLzN2wB</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="W347" t="n">
+        <v>48</v>
+      </c>
+      <c r="X347" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y347" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z347" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA347" t="inlineStr"/>
+      <c r="AB347" t="inlineStr"/>
+      <c r="AC347" t="inlineStr"/>
+      <c r="AD347" t="inlineStr"/>
+      <c r="AE347" t="inlineStr"/>
+      <c r="AF347" t="inlineStr"/>
+      <c r="AG347" t="inlineStr"/>
+      <c r="AH347" t="inlineStr"/>
+      <c r="AI347" t="inlineStr"/>
+      <c r="AJ347" t="inlineStr"/>
+      <c r="AK347" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AL347" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="AM347" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN347" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="AO347" t="n">
+        <v>2378125</v>
+      </c>
+      <c r="AP347" t="n">
+        <v>74.875</v>
+      </c>
+      <c r="AQ347" t="inlineStr"/>
+      <c r="AR347" t="inlineStr"/>
+      <c r="AS347" t="inlineStr"/>
+      <c r="AT347" t="inlineStr"/>
+      <c r="AU347" t="inlineStr"/>
+      <c r="AV347" t="inlineStr"/>
+      <c r="AW347" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="AX347" t="n">
+        <v>181</v>
+      </c>
+      <c r="AY347" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ347" t="n">
+        <v>68.85714285714286</v>
+      </c>
+      <c r="BA347" t="n">
+        <v>3255357.142857143</v>
+      </c>
+      <c r="BB347" t="n">
+        <v>75.64285714285714</v>
+      </c>
+      <c r="BC347" t="inlineStr"/>
+      <c r="BD347" t="inlineStr"/>
+      <c r="BE347" t="inlineStr"/>
+      <c r="BF347" t="inlineStr"/>
+      <c r="BG347" t="inlineStr"/>
+      <c r="BH347" t="inlineStr"/>
+      <c r="BI347" t="inlineStr"/>
+      <c r="BJ347" t="inlineStr"/>
+      <c r="BK347" t="inlineStr"/>
+      <c r="BL347" t="inlineStr"/>
+      <c r="BM347" t="inlineStr"/>
+      <c r="BN347" t="inlineStr"/>
+      <c r="BO347" t="inlineStr"/>
+      <c r="BP347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>MFnpCm7C</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stockbridge s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holker street
+  barrow in furness </t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F348" t="n">
+        <v>3003</v>
+      </c>
+      <c r="G348" t="n">
+        <v>1</v>
+      </c>
+      <c r="H348" t="n">
+        <v>0</v>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>KKJL7QXd</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>Iug0YO0Q</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr"/>
+      <c r="L348" t="inlineStr"/>
+      <c r="M348" t="n">
+        <v>47</v>
+      </c>
+      <c r="N348" t="n">
+        <v>53</v>
+      </c>
+      <c r="O348" t="n">
+        <v>13</v>
+      </c>
+      <c r="P348" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>3</v>
+      </c>
+      <c r="R348" t="n">
+        <v>3</v>
+      </c>
+      <c r="S348" t="n">
+        <v>11</v>
+      </c>
+      <c r="T348" t="n">
+        <v>14</v>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>joDBK9gn</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
+      <c r="W348" t="n">
+        <v>48</v>
+      </c>
+      <c r="X348" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y348" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z348" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA348" t="inlineStr"/>
+      <c r="AB348" t="inlineStr"/>
+      <c r="AC348" t="inlineStr"/>
+      <c r="AD348" t="inlineStr"/>
+      <c r="AE348" t="inlineStr"/>
+      <c r="AF348" t="inlineStr"/>
+      <c r="AG348" t="inlineStr"/>
+      <c r="AH348" t="inlineStr"/>
+      <c r="AI348" t="inlineStr"/>
+      <c r="AJ348" t="inlineStr"/>
+      <c r="AK348" t="inlineStr"/>
+      <c r="AL348" t="inlineStr"/>
+      <c r="AM348" t="inlineStr"/>
+      <c r="AN348" t="inlineStr"/>
+      <c r="AO348" t="inlineStr"/>
+      <c r="AP348" t="inlineStr"/>
+      <c r="AQ348" t="inlineStr"/>
+      <c r="AR348" t="inlineStr"/>
+      <c r="AS348" t="inlineStr"/>
+      <c r="AT348" t="inlineStr"/>
+      <c r="AU348" t="inlineStr"/>
+      <c r="AV348" t="inlineStr"/>
+      <c r="AW348" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AX348" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AY348" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ348" t="n">
+        <v>63.125</v>
+      </c>
+      <c r="BA348" t="n">
+        <v>859375</v>
+      </c>
+      <c r="BB348" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="BC348" t="inlineStr"/>
+      <c r="BD348" t="inlineStr"/>
+      <c r="BE348" t="inlineStr"/>
+      <c r="BF348" t="inlineStr"/>
+      <c r="BG348" t="inlineStr"/>
+      <c r="BH348" t="inlineStr"/>
+      <c r="BI348" t="inlineStr"/>
+      <c r="BJ348" t="inlineStr"/>
+      <c r="BK348" t="inlineStr"/>
+      <c r="BL348" t="inlineStr"/>
+      <c r="BM348" t="inlineStr"/>
+      <c r="BN348" t="inlineStr"/>
+      <c r="BO348" t="inlineStr"/>
+      <c r="BP348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>UsklUtpe</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backhouse a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ewood park
+  blackburn </t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>31367</v>
+      </c>
+      <c r="F349" t="n">
+        <v>9418</v>
+      </c>
+      <c r="G349" t="n">
+        <v>1</v>
+      </c>
+      <c r="H349" t="n">
+        <v>2</v>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>8EFIJthC</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr"/>
+      <c r="M349" t="n">
+        <v>61</v>
+      </c>
+      <c r="N349" t="n">
+        <v>39</v>
+      </c>
+      <c r="O349" t="n">
+        <v>14</v>
+      </c>
+      <c r="P349" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>5</v>
+      </c>
+      <c r="R349" t="n">
+        <v>5</v>
+      </c>
+      <c r="S349" t="n">
+        <v>19</v>
+      </c>
+      <c r="T349" t="n">
+        <v>8</v>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>2e9kg9n1</t>
+        </is>
+      </c>
+      <c r="W349" t="n">
+        <v>48</v>
+      </c>
+      <c r="X349" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y349" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z349" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA349" t="inlineStr"/>
+      <c r="AB349" t="inlineStr"/>
+      <c r="AC349" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="AD349" t="inlineStr"/>
+      <c r="AE349" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="AF349" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="AG349" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH349" t="n">
+        <v>68.55555555555556</v>
+      </c>
+      <c r="AI349" t="n">
+        <v>1694444.444444444</v>
+      </c>
+      <c r="AJ349" t="n">
+        <v>73</v>
+      </c>
+      <c r="AK349" t="inlineStr"/>
+      <c r="AL349" t="inlineStr"/>
+      <c r="AM349" t="inlineStr"/>
+      <c r="AN349" t="inlineStr"/>
+      <c r="AO349" t="inlineStr"/>
+      <c r="AP349" t="inlineStr"/>
+      <c r="AQ349" t="n">
+        <v>27.22222222222222</v>
+      </c>
+      <c r="AR349" t="n">
+        <v>182.7222222222222</v>
+      </c>
+      <c r="AS349" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT349" t="n">
+        <v>68.83333333333333</v>
+      </c>
+      <c r="AU349" t="n">
+        <v>1619444.444444444</v>
+      </c>
+      <c r="AV349" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AW349" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="AX349" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="AY349" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ349" t="n">
+        <v>67</v>
+      </c>
+      <c r="BA349" t="n">
+        <v>1141666.666666667</v>
+      </c>
+      <c r="BB349" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="BC349" t="inlineStr"/>
+      <c r="BD349" t="inlineStr"/>
+      <c r="BE349" t="inlineStr"/>
+      <c r="BF349" t="inlineStr"/>
+      <c r="BG349" t="inlineStr"/>
+      <c r="BH349" t="inlineStr"/>
+      <c r="BI349" t="inlineStr"/>
+      <c r="BJ349" t="inlineStr"/>
+      <c r="BK349" t="inlineStr"/>
+      <c r="BL349" t="inlineStr"/>
+      <c r="BM349" t="inlineStr"/>
+      <c r="BN349" t="inlineStr"/>
+      <c r="BO349" t="inlineStr"/>
+      <c r="BP349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>ddFjPf2b</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chilowicz a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F350" t="n">
+        <v>19175</v>
+      </c>
+      <c r="G350" t="n">
+        <v>4</v>
+      </c>
+      <c r="H350" t="n">
+        <v>0</v>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>QVmLl54o</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="M350" t="n">
+        <v>45</v>
+      </c>
+      <c r="N350" t="n">
+        <v>55</v>
+      </c>
+      <c r="O350" t="n">
+        <v>17</v>
+      </c>
+      <c r="P350" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>8</v>
+      </c>
+      <c r="R350" t="n">
+        <v>3</v>
+      </c>
+      <c r="S350" t="n">
+        <v>10</v>
+      </c>
+      <c r="T350" t="n">
+        <v>16</v>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>COqtASrJ</t>
+        </is>
+      </c>
+      <c r="W350" t="n">
+        <v>48</v>
+      </c>
+      <c r="X350" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y350" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z350" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA350" t="inlineStr"/>
+      <c r="AB350" t="inlineStr"/>
+      <c r="AC350" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="AD350" t="inlineStr"/>
+      <c r="AE350" t="n">
+        <v>21.125</v>
+      </c>
+      <c r="AF350" t="n">
+        <v>178.25</v>
+      </c>
+      <c r="AG350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH350" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="AI350" t="n">
+        <v>6331250</v>
+      </c>
+      <c r="AJ350" t="n">
+        <v>81</v>
+      </c>
+      <c r="AK350" t="inlineStr"/>
+      <c r="AL350" t="inlineStr"/>
+      <c r="AM350" t="inlineStr"/>
+      <c r="AN350" t="inlineStr"/>
+      <c r="AO350" t="inlineStr"/>
+      <c r="AP350" t="inlineStr"/>
+      <c r="AQ350" t="n">
+        <v>21.86666666666667</v>
+      </c>
+      <c r="AR350" t="n">
+        <v>176.5333333333333</v>
+      </c>
+      <c r="AS350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT350" t="n">
+        <v>68.86666666666666</v>
+      </c>
+      <c r="AU350" t="n">
+        <v>8218333.333333333</v>
+      </c>
+      <c r="AV350" t="n">
+        <v>78.06666666666666</v>
+      </c>
+      <c r="AW350" t="inlineStr"/>
+      <c r="AX350" t="inlineStr"/>
+      <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr"/>
+      <c r="BA350" t="inlineStr"/>
+      <c r="BB350" t="inlineStr"/>
+      <c r="BC350" t="inlineStr"/>
+      <c r="BD350" t="inlineStr"/>
+      <c r="BE350" t="inlineStr"/>
+      <c r="BF350" t="inlineStr"/>
+      <c r="BG350" t="inlineStr"/>
+      <c r="BH350" t="inlineStr"/>
+      <c r="BI350" t="inlineStr"/>
+      <c r="BJ350" t="inlineStr"/>
+      <c r="BK350" t="inlineStr"/>
+      <c r="BL350" t="inlineStr"/>
+      <c r="BM350" t="inlineStr"/>
+      <c r="BN350" t="inlineStr"/>
+      <c r="BO350" t="inlineStr"/>
+      <c r="BP350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>Sh9BS8ig</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">finnie w 
+  eng </t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coventry building society arena
+  coventry </t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>32753</v>
+      </c>
+      <c r="F351" t="n">
+        <v>11808</v>
+      </c>
+      <c r="G351" t="n">
+        <v>1</v>
+      </c>
+      <c r="H351" t="n">
+        <v>0</v>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>vgOBT43c</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr"/>
+      <c r="M351" t="n">
+        <v>53</v>
+      </c>
+      <c r="N351" t="n">
+        <v>47</v>
+      </c>
+      <c r="O351" t="n">
+        <v>18</v>
+      </c>
+      <c r="P351" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>5</v>
+      </c>
+      <c r="R351" t="n">
+        <v>0</v>
+      </c>
+      <c r="S351" t="n">
+        <v>9</v>
+      </c>
+      <c r="T351" t="n">
+        <v>15</v>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
+      <c r="W351" t="n">
+        <v>48</v>
+      </c>
+      <c r="X351" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y351" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z351" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA351" t="inlineStr"/>
+      <c r="AB351" t="inlineStr"/>
+      <c r="AC351" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="AD351" t="inlineStr"/>
+      <c r="AE351" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AF351" t="n">
+        <v>181.625</v>
+      </c>
+      <c r="AG351" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH351" t="n">
+        <v>69.625</v>
+      </c>
+      <c r="AI351" t="n">
+        <v>2412500</v>
+      </c>
+      <c r="AJ351" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AK351" t="inlineStr"/>
+      <c r="AL351" t="inlineStr"/>
+      <c r="AM351" t="inlineStr"/>
+      <c r="AN351" t="inlineStr"/>
+      <c r="AO351" t="inlineStr"/>
+      <c r="AP351" t="inlineStr"/>
+      <c r="AQ351" t="n">
+        <v>23.95238095238095</v>
+      </c>
+      <c r="AR351" t="n">
+        <v>180</v>
+      </c>
+      <c r="AS351" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT351" t="n">
+        <v>71.47619047619048</v>
+      </c>
+      <c r="AU351" t="n">
+        <v>4709523.80952381</v>
+      </c>
+      <c r="AV351" t="n">
+        <v>77</v>
+      </c>
+      <c r="AW351" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX351" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="AY351" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ351" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="BA351" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="BB351" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BC351" t="inlineStr"/>
+      <c r="BD351" t="inlineStr"/>
+      <c r="BE351" t="inlineStr"/>
+      <c r="BF351" t="inlineStr"/>
+      <c r="BG351" t="inlineStr"/>
+      <c r="BH351" t="inlineStr"/>
+      <c r="BI351" t="inlineStr"/>
+      <c r="BJ351" t="inlineStr"/>
+      <c r="BK351" t="inlineStr"/>
+      <c r="BL351" t="inlineStr"/>
+      <c r="BM351" t="inlineStr"/>
+      <c r="BN351" t="inlineStr"/>
+      <c r="BO351" t="inlineStr"/>
+      <c r="BP351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>dAfPwfHi</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>39572</v>
+      </c>
+      <c r="F352" t="n">
+        <v>37245</v>
+      </c>
+      <c r="G352" t="n">
+        <v>3</v>
+      </c>
+      <c r="H352" t="n">
+        <v>0</v>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>hlzYDy5q</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="M352" t="n">
+        <v>58</v>
+      </c>
+      <c r="N352" t="n">
+        <v>42</v>
+      </c>
+      <c r="O352" t="n">
+        <v>16</v>
+      </c>
+      <c r="P352" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>4</v>
+      </c>
+      <c r="R352" t="n">
+        <v>3</v>
+      </c>
+      <c r="S352" t="n">
+        <v>16</v>
+      </c>
+      <c r="T352" t="n">
+        <v>10</v>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>pSZhI8SM</t>
+        </is>
+      </c>
+      <c r="W352" t="n">
+        <v>48</v>
+      </c>
+      <c r="X352" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y352" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z352" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA352" t="inlineStr"/>
+      <c r="AB352" t="inlineStr"/>
+      <c r="AC352" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="AD352" t="inlineStr"/>
+      <c r="AE352" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AF352" t="n">
+        <v>185.7777777777778</v>
+      </c>
+      <c r="AG352" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AH352" t="n">
+        <v>74.77777777777777</v>
+      </c>
+      <c r="AI352" t="n">
+        <v>9344444.444444444</v>
+      </c>
+      <c r="AJ352" t="n">
+        <v>78.33333333333333</v>
+      </c>
+      <c r="AK352" t="inlineStr"/>
+      <c r="AL352" t="inlineStr"/>
+      <c r="AM352" t="inlineStr"/>
+      <c r="AN352" t="inlineStr"/>
+      <c r="AO352" t="inlineStr"/>
+      <c r="AP352" t="inlineStr"/>
+      <c r="AQ352" t="n">
+        <v>29.3125</v>
+      </c>
+      <c r="AR352" t="n">
+        <v>178.8125</v>
+      </c>
+      <c r="AS352" t="n">
+        <v>1.5625</v>
+      </c>
+      <c r="AT352" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AU352" t="n">
+        <v>4898437.5</v>
+      </c>
+      <c r="AV352" t="n">
+        <v>76</v>
+      </c>
+      <c r="AW352" t="inlineStr"/>
+      <c r="AX352" t="inlineStr"/>
+      <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr"/>
+      <c r="BA352" t="inlineStr"/>
+      <c r="BB352" t="inlineStr"/>
+      <c r="BC352" t="inlineStr"/>
+      <c r="BD352" t="inlineStr"/>
+      <c r="BE352" t="inlineStr"/>
+      <c r="BF352" t="inlineStr"/>
+      <c r="BG352" t="inlineStr"/>
+      <c r="BH352" t="inlineStr"/>
+      <c r="BI352" t="inlineStr"/>
+      <c r="BJ352" t="inlineStr"/>
+      <c r="BK352" t="inlineStr"/>
+      <c r="BL352" t="inlineStr"/>
+      <c r="BM352" t="inlineStr"/>
+      <c r="BN352" t="inlineStr"/>
+      <c r="BO352" t="inlineStr"/>
+      <c r="BP352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>pWQ6LC1N</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joyce r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">highbury stadium
+  fleetwood </t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>5327</v>
+      </c>
+      <c r="F353" t="n">
+        <v>1744</v>
+      </c>
+      <c r="G353" t="n">
+        <v>2</v>
+      </c>
+      <c r="H353" t="n">
+        <v>1</v>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>tCZ3D68d</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>KMfM7P4b</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr"/>
+      <c r="M353" t="n">
+        <v>46</v>
+      </c>
+      <c r="N353" t="n">
+        <v>54</v>
+      </c>
+      <c r="O353" t="n">
+        <v>15</v>
+      </c>
+      <c r="P353" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>5</v>
+      </c>
+      <c r="R353" t="n">
+        <v>5</v>
+      </c>
+      <c r="S353" t="n">
+        <v>11</v>
+      </c>
+      <c r="T353" t="n">
+        <v>12</v>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>d6KwHx8i</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="W353" t="n">
+        <v>48</v>
+      </c>
+      <c r="X353" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y353" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z353" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA353" t="inlineStr"/>
+      <c r="AB353" t="inlineStr"/>
+      <c r="AC353" t="inlineStr"/>
+      <c r="AD353" t="inlineStr"/>
+      <c r="AE353" t="inlineStr"/>
+      <c r="AF353" t="inlineStr"/>
+      <c r="AG353" t="inlineStr"/>
+      <c r="AH353" t="inlineStr"/>
+      <c r="AI353" t="inlineStr"/>
+      <c r="AJ353" t="inlineStr"/>
+      <c r="AK353" t="inlineStr"/>
+      <c r="AL353" t="inlineStr"/>
+      <c r="AM353" t="inlineStr"/>
+      <c r="AN353" t="inlineStr"/>
+      <c r="AO353" t="inlineStr"/>
+      <c r="AP353" t="inlineStr"/>
+      <c r="AQ353" t="inlineStr"/>
+      <c r="AR353" t="inlineStr"/>
+      <c r="AS353" t="inlineStr"/>
+      <c r="AT353" t="inlineStr"/>
+      <c r="AU353" t="inlineStr"/>
+      <c r="AV353" t="inlineStr"/>
+      <c r="AW353" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AX353" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AY353" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ353" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BA353" t="n">
+        <v>13817500</v>
+      </c>
+      <c r="BB353" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="BC353" t="inlineStr"/>
+      <c r="BD353" t="inlineStr"/>
+      <c r="BE353" t="inlineStr"/>
+      <c r="BF353" t="inlineStr"/>
+      <c r="BG353" t="inlineStr"/>
+      <c r="BH353" t="inlineStr"/>
+      <c r="BI353" t="inlineStr"/>
+      <c r="BJ353" t="inlineStr"/>
+      <c r="BK353" t="inlineStr"/>
+      <c r="BL353" t="inlineStr"/>
+      <c r="BM353" t="inlineStr"/>
+      <c r="BN353" t="inlineStr"/>
+      <c r="BO353" t="inlineStr"/>
+      <c r="BP353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>jiUEFsV1</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corlett m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blundell park
+  cleethorpes </t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>9052</v>
+      </c>
+      <c r="F354" t="n">
+        <v>6364</v>
+      </c>
+      <c r="G354" t="n">
+        <v>1</v>
+      </c>
+      <c r="H354" t="n">
+        <v>5</v>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>OEaiS3za</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="n">
+        <v>30</v>
+      </c>
+      <c r="N354" t="n">
+        <v>70</v>
+      </c>
+      <c r="O354" t="n">
+        <v>8</v>
+      </c>
+      <c r="P354" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>2</v>
+      </c>
+      <c r="R354" t="n">
+        <v>6</v>
+      </c>
+      <c r="S354" t="n">
+        <v>9</v>
+      </c>
+      <c r="T354" t="n">
+        <v>12</v>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>SGvTSGmc</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="W354" t="n">
+        <v>48</v>
+      </c>
+      <c r="X354" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y354" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z354" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA354" t="inlineStr"/>
+      <c r="AB354" t="inlineStr"/>
+      <c r="AC354" t="inlineStr"/>
+      <c r="AD354" t="inlineStr"/>
+      <c r="AE354" t="inlineStr"/>
+      <c r="AF354" t="inlineStr"/>
+      <c r="AG354" t="inlineStr"/>
+      <c r="AH354" t="inlineStr"/>
+      <c r="AI354" t="inlineStr"/>
+      <c r="AJ354" t="inlineStr"/>
+      <c r="AK354" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AL354" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AM354" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN354" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AO354" t="n">
+        <v>942500</v>
+      </c>
+      <c r="AP354" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AQ354" t="inlineStr"/>
+      <c r="AR354" t="inlineStr"/>
+      <c r="AS354" t="inlineStr"/>
+      <c r="AT354" t="inlineStr"/>
+      <c r="AU354" t="inlineStr"/>
+      <c r="AV354" t="inlineStr"/>
+      <c r="AW354" t="n">
+        <v>26.57894736842105</v>
+      </c>
+      <c r="AX354" t="n">
+        <v>179.2105263157895</v>
+      </c>
+      <c r="AY354" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ354" t="n">
+        <v>67.89473684210526</v>
+      </c>
+      <c r="BA354" t="n">
+        <v>1405263.157894737</v>
+      </c>
+      <c r="BB354" t="n">
+        <v>71.31578947368421</v>
+      </c>
+      <c r="BC354" t="inlineStr"/>
+      <c r="BD354" t="inlineStr"/>
+      <c r="BE354" t="inlineStr"/>
+      <c r="BF354" t="inlineStr"/>
+      <c r="BG354" t="inlineStr"/>
+      <c r="BH354" t="inlineStr"/>
+      <c r="BI354" t="inlineStr"/>
+      <c r="BJ354" t="inlineStr"/>
+      <c r="BK354" t="inlineStr"/>
+      <c r="BL354" t="inlineStr"/>
+      <c r="BM354" t="inlineStr"/>
+      <c r="BN354" t="inlineStr"/>
+      <c r="BO354" t="inlineStr"/>
+      <c r="BP354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>dY0SOQjI</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">speedie b 
+  eng </t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">envirovent stadium
+  harrogate </t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F355" t="n">
+        <v>2570</v>
+      </c>
+      <c r="G355" t="n">
+        <v>0</v>
+      </c>
+      <c r="H355" t="n">
+        <v>5</v>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>CQv5qrFt</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>x8IDVcbi</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
+      <c r="M355" t="n">
+        <v>33</v>
+      </c>
+      <c r="N355" t="n">
+        <v>67</v>
+      </c>
+      <c r="O355" t="n">
+        <v>6</v>
+      </c>
+      <c r="P355" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>3</v>
+      </c>
+      <c r="R355" t="n">
+        <v>6</v>
+      </c>
+      <c r="S355" t="n">
+        <v>7</v>
+      </c>
+      <c r="T355" t="n">
+        <v>6</v>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>ANwVL1Tp</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>lGE8iEO1</t>
+        </is>
+      </c>
+      <c r="W355" t="n">
+        <v>48</v>
+      </c>
+      <c r="X355" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y355" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z355" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA355" t="inlineStr"/>
+      <c r="AB355" t="inlineStr"/>
+      <c r="AC355" t="inlineStr"/>
+      <c r="AD355" t="inlineStr"/>
+      <c r="AE355" t="inlineStr"/>
+      <c r="AF355" t="inlineStr"/>
+      <c r="AG355" t="inlineStr"/>
+      <c r="AH355" t="inlineStr"/>
+      <c r="AI355" t="inlineStr"/>
+      <c r="AJ355" t="inlineStr"/>
+      <c r="AK355" t="n">
+        <v>26.125</v>
+      </c>
+      <c r="AL355" t="n">
+        <v>184</v>
+      </c>
+      <c r="AM355" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN355" t="n">
+        <v>69.375</v>
+      </c>
+      <c r="AO355" t="n">
+        <v>1687500</v>
+      </c>
+      <c r="AP355" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AQ355" t="inlineStr"/>
+      <c r="AR355" t="inlineStr"/>
+      <c r="AS355" t="inlineStr"/>
+      <c r="AT355" t="inlineStr"/>
+      <c r="AU355" t="inlineStr"/>
+      <c r="AV355" t="inlineStr"/>
+      <c r="AW355" t="n">
+        <v>23.36842105263158</v>
+      </c>
+      <c r="AX355" t="n">
+        <v>184.2105263157895</v>
+      </c>
+      <c r="AY355" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AZ355" t="n">
+        <v>69.05263157894737</v>
+      </c>
+      <c r="BA355" t="n">
+        <v>3768421.052631579</v>
+      </c>
+      <c r="BB355" t="n">
+        <v>75.47368421052632</v>
+      </c>
+      <c r="BC355" t="inlineStr"/>
+      <c r="BD355" t="inlineStr"/>
+      <c r="BE355" t="inlineStr"/>
+      <c r="BF355" t="inlineStr"/>
+      <c r="BG355" t="inlineStr"/>
+      <c r="BH355" t="inlineStr"/>
+      <c r="BI355" t="inlineStr"/>
+      <c r="BJ355" t="inlineStr"/>
+      <c r="BK355" t="inlineStr"/>
+      <c r="BL355" t="inlineStr"/>
+      <c r="BM355" t="inlineStr"/>
+      <c r="BN355" t="inlineStr"/>
+      <c r="BO355" t="inlineStr"/>
+      <c r="BP355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>hO8aNYWA</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>32261</v>
+      </c>
+      <c r="F356" t="n">
+        <v>13011</v>
+      </c>
+      <c r="G356" t="n">
+        <v>4</v>
+      </c>
+      <c r="H356" t="n">
+        <v>0</v>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>jVhkb1QE</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="M356" t="n">
+        <v>74</v>
+      </c>
+      <c r="N356" t="n">
+        <v>26</v>
+      </c>
+      <c r="O356" t="n">
+        <v>24</v>
+      </c>
+      <c r="P356" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>9</v>
+      </c>
+      <c r="R356" t="n">
+        <v>0</v>
+      </c>
+      <c r="S356" t="n">
+        <v>6</v>
+      </c>
+      <c r="T356" t="n">
+        <v>9</v>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>2L1wFbM5</t>
+        </is>
+      </c>
+      <c r="W356" t="n">
+        <v>48</v>
+      </c>
+      <c r="X356" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y356" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z356" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA356" t="inlineStr"/>
+      <c r="AB356" t="inlineStr"/>
+      <c r="AC356" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="AD356" t="inlineStr"/>
+      <c r="AE356" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF356" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="AG356" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH356" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AI356" t="n">
+        <v>8697500</v>
+      </c>
+      <c r="AJ356" t="n">
+        <v>77</v>
+      </c>
+      <c r="AK356" t="inlineStr"/>
+      <c r="AL356" t="inlineStr"/>
+      <c r="AM356" t="inlineStr"/>
+      <c r="AN356" t="inlineStr"/>
+      <c r="AO356" t="inlineStr"/>
+      <c r="AP356" t="inlineStr"/>
+      <c r="AQ356" t="n">
+        <v>23.85714285714286</v>
+      </c>
+      <c r="AR356" t="n">
+        <v>180.0714285714286</v>
+      </c>
+      <c r="AS356" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AT356" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AU356" t="n">
+        <v>5669642.857142857</v>
+      </c>
+      <c r="AV356" t="n">
+        <v>76.85714285714286</v>
+      </c>
+      <c r="AW356" t="inlineStr"/>
+      <c r="AX356" t="inlineStr"/>
+      <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr"/>
+      <c r="BA356" t="inlineStr"/>
+      <c r="BB356" t="inlineStr"/>
+      <c r="BC356" t="inlineStr"/>
+      <c r="BD356" t="inlineStr"/>
+      <c r="BE356" t="inlineStr"/>
+      <c r="BF356" t="inlineStr"/>
+      <c r="BG356" t="inlineStr"/>
+      <c r="BH356" t="inlineStr"/>
+      <c r="BI356" t="inlineStr"/>
+      <c r="BJ356" t="inlineStr"/>
+      <c r="BK356" t="inlineStr"/>
+      <c r="BL356" t="inlineStr"/>
+      <c r="BM356" t="inlineStr"/>
+      <c r="BN356" t="inlineStr"/>
+      <c r="BO356" t="inlineStr"/>
+      <c r="BP356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>vDA9yPiL</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rock d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the den
+  london </t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>20146</v>
+      </c>
+      <c r="F357" t="n">
+        <v>5875</v>
+      </c>
+      <c r="G357" t="n">
+        <v>0</v>
+      </c>
+      <c r="H357" t="n">
+        <v>1</v>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>KKyYcus9</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr"/>
+      <c r="M357" t="n">
+        <v>56</v>
+      </c>
+      <c r="N357" t="n">
+        <v>44</v>
+      </c>
+      <c r="O357" t="n">
+        <v>5</v>
+      </c>
+      <c r="P357" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>0</v>
+      </c>
+      <c r="R357" t="n">
+        <v>1</v>
+      </c>
+      <c r="S357" t="n">
+        <v>18</v>
+      </c>
+      <c r="T357" t="n">
+        <v>20</v>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>C6Wq1Q6e</t>
+        </is>
+      </c>
+      <c r="W357" t="n">
+        <v>48</v>
+      </c>
+      <c r="X357" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y357" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z357" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA357" t="inlineStr"/>
+      <c r="AB357" t="inlineStr"/>
+      <c r="AC357" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="AD357" t="inlineStr"/>
+      <c r="AE357" t="inlineStr"/>
+      <c r="AF357" t="inlineStr"/>
+      <c r="AG357" t="inlineStr"/>
+      <c r="AH357" t="inlineStr"/>
+      <c r="AI357" t="inlineStr"/>
+      <c r="AJ357" t="inlineStr"/>
+      <c r="AK357" t="inlineStr"/>
+      <c r="AL357" t="inlineStr"/>
+      <c r="AM357" t="inlineStr"/>
+      <c r="AN357" t="inlineStr"/>
+      <c r="AO357" t="inlineStr"/>
+      <c r="AP357" t="inlineStr"/>
+      <c r="AQ357" t="n">
+        <v>26.42105263157895</v>
+      </c>
+      <c r="AR357" t="n">
+        <v>177.8421052631579</v>
+      </c>
+      <c r="AS357" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT357" t="n">
+        <v>68</v>
+      </c>
+      <c r="AU357" t="n">
+        <v>1638157.894736842</v>
+      </c>
+      <c r="AV357" t="n">
+        <v>72.73684210526316</v>
+      </c>
+      <c r="AW357" t="n">
+        <v>20.18181818181818</v>
+      </c>
+      <c r="AX357" t="n">
+        <v>182.7272727272727</v>
+      </c>
+      <c r="AY357" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ357" t="n">
+        <v>60.45454545454545</v>
+      </c>
+      <c r="BA357" t="n">
+        <v>756818.1818181818</v>
+      </c>
+      <c r="BB357" t="n">
+        <v>74.45454545454545</v>
+      </c>
+      <c r="BC357" t="inlineStr"/>
+      <c r="BD357" t="inlineStr"/>
+      <c r="BE357" t="inlineStr"/>
+      <c r="BF357" t="inlineStr"/>
+      <c r="BG357" t="inlineStr"/>
+      <c r="BH357" t="inlineStr"/>
+      <c r="BI357" t="inlineStr"/>
+      <c r="BJ357" t="inlineStr"/>
+      <c r="BK357" t="inlineStr"/>
+      <c r="BL357" t="inlineStr"/>
+      <c r="BM357" t="inlineStr"/>
+      <c r="BN357" t="inlineStr"/>
+      <c r="BO357" t="inlineStr"/>
+      <c r="BP357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>hzeTFV7m</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doughty l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">loftus road
+  london </t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>18439</v>
+      </c>
+      <c r="F358" t="n">
+        <v>7132</v>
+      </c>
+      <c r="G358" t="n">
+        <v>2</v>
+      </c>
+      <c r="H358" t="n">
+        <v>1</v>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr"/>
+      <c r="L358" t="inlineStr"/>
+      <c r="M358" t="n">
+        <v>49</v>
+      </c>
+      <c r="N358" t="n">
+        <v>51</v>
+      </c>
+      <c r="O358" t="n">
+        <v>11</v>
+      </c>
+      <c r="P358" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>8</v>
+      </c>
+      <c r="R358" t="n">
+        <v>7</v>
+      </c>
+      <c r="S358" t="n">
+        <v>15</v>
+      </c>
+      <c r="T358" t="n">
+        <v>15</v>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="W358" t="n">
+        <v>48</v>
+      </c>
+      <c r="X358" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y358" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z358" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA358" t="inlineStr"/>
+      <c r="AB358" t="inlineStr"/>
+      <c r="AC358" t="inlineStr"/>
+      <c r="AD358" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="AE358" t="inlineStr"/>
+      <c r="AF358" t="inlineStr"/>
+      <c r="AG358" t="inlineStr"/>
+      <c r="AH358" t="inlineStr"/>
+      <c r="AI358" t="inlineStr"/>
+      <c r="AJ358" t="inlineStr"/>
+      <c r="AK358" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="AL358" t="n">
+        <v>183.9090909090909</v>
+      </c>
+      <c r="AM358" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN358" t="n">
+        <v>69.90909090909091</v>
+      </c>
+      <c r="AO358" t="n">
+        <v>2602272.727272727</v>
+      </c>
+      <c r="AP358" t="n">
+        <v>74.54545454545455</v>
+      </c>
+      <c r="AQ358" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AR358" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AS358" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT358" t="n">
+        <v>68.16666666666667</v>
+      </c>
+      <c r="AU358" t="n">
+        <v>1535416.666666667</v>
+      </c>
+      <c r="AV358" t="n">
+        <v>71.58333333333333</v>
+      </c>
+      <c r="AW358" t="n">
+        <v>26.55555555555556</v>
+      </c>
+      <c r="AX358" t="n">
+        <v>182</v>
+      </c>
+      <c r="AY358" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ358" t="n">
+        <v>70.05555555555556</v>
+      </c>
+      <c r="BA358" t="n">
+        <v>1961111.111111111</v>
+      </c>
+      <c r="BB358" t="n">
+        <v>71.72222222222223</v>
+      </c>
+      <c r="BC358" t="inlineStr"/>
+      <c r="BD358" t="inlineStr"/>
+      <c r="BE358" t="inlineStr"/>
+      <c r="BF358" t="inlineStr"/>
+      <c r="BG358" t="inlineStr"/>
+      <c r="BH358" t="inlineStr"/>
+      <c r="BI358" t="inlineStr"/>
+      <c r="BJ358" t="inlineStr"/>
+      <c r="BK358" t="inlineStr"/>
+      <c r="BL358" t="inlineStr"/>
+      <c r="BM358" t="inlineStr"/>
+      <c r="BN358" t="inlineStr"/>
+      <c r="BO358" t="inlineStr"/>
+      <c r="BP358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>Q9rcSKE7</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gill s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the croud meadow
+  shrewsbury </t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>9877</v>
+      </c>
+      <c r="F359" t="n">
+        <v>3220</v>
+      </c>
+      <c r="G359" t="n">
+        <v>0</v>
+      </c>
+      <c r="H359" t="n">
+        <v>2</v>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>EqfQ6qK4</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>Or1bBrWD</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
+      <c r="M359" t="n">
+        <v>38</v>
+      </c>
+      <c r="N359" t="n">
+        <v>62</v>
+      </c>
+      <c r="O359" t="n">
+        <v>12</v>
+      </c>
+      <c r="P359" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>2</v>
+      </c>
+      <c r="R359" t="n">
+        <v>5</v>
+      </c>
+      <c r="S359" t="n">
+        <v>14</v>
+      </c>
+      <c r="T359" t="n">
+        <v>9</v>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>EqN1jJFK</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>EosAlOi5</t>
+        </is>
+      </c>
+      <c r="W359" t="n">
+        <v>48</v>
+      </c>
+      <c r="X359" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y359" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z359" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA359" t="inlineStr"/>
+      <c r="AB359" t="inlineStr"/>
+      <c r="AC359" t="inlineStr"/>
+      <c r="AD359" t="inlineStr"/>
+      <c r="AE359" t="inlineStr"/>
+      <c r="AF359" t="inlineStr"/>
+      <c r="AG359" t="inlineStr"/>
+      <c r="AH359" t="inlineStr"/>
+      <c r="AI359" t="inlineStr"/>
+      <c r="AJ359" t="inlineStr"/>
+      <c r="AK359" t="inlineStr"/>
+      <c r="AL359" t="inlineStr"/>
+      <c r="AM359" t="inlineStr"/>
+      <c r="AN359" t="inlineStr"/>
+      <c r="AO359" t="inlineStr"/>
+      <c r="AP359" t="inlineStr"/>
+      <c r="AQ359" t="inlineStr"/>
+      <c r="AR359" t="inlineStr"/>
+      <c r="AS359" t="inlineStr"/>
+      <c r="AT359" t="inlineStr"/>
+      <c r="AU359" t="inlineStr"/>
+      <c r="AV359" t="inlineStr"/>
+      <c r="AW359" t="inlineStr"/>
+      <c r="AX359" t="inlineStr"/>
+      <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr"/>
+      <c r="BA359" t="inlineStr"/>
+      <c r="BB359" t="inlineStr"/>
+      <c r="BC359" t="inlineStr"/>
+      <c r="BD359" t="inlineStr"/>
+      <c r="BE359" t="inlineStr"/>
+      <c r="BF359" t="inlineStr"/>
+      <c r="BG359" t="inlineStr"/>
+      <c r="BH359" t="inlineStr"/>
+      <c r="BI359" t="inlineStr"/>
+      <c r="BJ359" t="inlineStr"/>
+      <c r="BK359" t="inlineStr"/>
+      <c r="BL359" t="inlineStr"/>
+      <c r="BM359" t="inlineStr"/>
+      <c r="BN359" t="inlineStr"/>
+      <c r="BO359" t="inlineStr"/>
+      <c r="BP359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>zJCJQnM5</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duckworth e 
+  eng </t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bescot stadium
+  walsall </t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>11300</v>
+      </c>
+      <c r="F360" t="n">
+        <v>3378</v>
+      </c>
+      <c r="G360" t="n">
+        <v>3</v>
+      </c>
+      <c r="H360" t="n">
+        <v>2</v>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>YgrfcLuL</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr"/>
+      <c r="M360" t="n">
+        <v>37</v>
+      </c>
+      <c r="N360" t="n">
+        <v>63</v>
+      </c>
+      <c r="O360" t="n">
+        <v>25</v>
+      </c>
+      <c r="P360" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>7</v>
+      </c>
+      <c r="R360" t="n">
+        <v>2</v>
+      </c>
+      <c r="S360" t="n">
+        <v>15</v>
+      </c>
+      <c r="T360" t="n">
+        <v>12</v>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>YTxm48Ng</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>KGX2o9A5</t>
+        </is>
+      </c>
+      <c r="W360" t="n">
+        <v>48</v>
+      </c>
+      <c r="X360" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y360" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z360" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA360" t="inlineStr"/>
+      <c r="AB360" t="inlineStr"/>
+      <c r="AC360" t="inlineStr"/>
+      <c r="AD360" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="AE360" t="inlineStr"/>
+      <c r="AF360" t="inlineStr"/>
+      <c r="AG360" t="inlineStr"/>
+      <c r="AH360" t="inlineStr"/>
+      <c r="AI360" t="inlineStr"/>
+      <c r="AJ360" t="inlineStr"/>
+      <c r="AK360" t="inlineStr"/>
+      <c r="AL360" t="inlineStr"/>
+      <c r="AM360" t="inlineStr"/>
+      <c r="AN360" t="inlineStr"/>
+      <c r="AO360" t="inlineStr"/>
+      <c r="AP360" t="inlineStr"/>
+      <c r="AQ360" t="inlineStr"/>
+      <c r="AR360" t="inlineStr"/>
+      <c r="AS360" t="inlineStr"/>
+      <c r="AT360" t="inlineStr"/>
+      <c r="AU360" t="inlineStr"/>
+      <c r="AV360" t="inlineStr"/>
+      <c r="AW360" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="AX360" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AY360" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ360" t="n">
+        <v>64.5625</v>
+      </c>
+      <c r="BA360" t="n">
+        <v>1140625</v>
+      </c>
+      <c r="BB360" t="n">
+        <v>72.375</v>
+      </c>
+      <c r="BC360" t="inlineStr"/>
+      <c r="BD360" t="inlineStr"/>
+      <c r="BE360" t="inlineStr"/>
+      <c r="BF360" t="inlineStr"/>
+      <c r="BG360" t="inlineStr"/>
+      <c r="BH360" t="inlineStr"/>
+      <c r="BI360" t="inlineStr"/>
+      <c r="BJ360" t="inlineStr"/>
+      <c r="BK360" t="inlineStr"/>
+      <c r="BL360" t="inlineStr"/>
+      <c r="BM360" t="inlineStr"/>
+      <c r="BN360" t="inlineStr"/>
+      <c r="BO360" t="inlineStr"/>
+      <c r="BP360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>QkntzCGG</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">davies a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vicarage road
+  watford </t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>22200</v>
+      </c>
+      <c r="F361" t="n">
+        <v>8319</v>
+      </c>
+      <c r="G361" t="n">
+        <v>2</v>
+      </c>
+      <c r="H361" t="n">
+        <v>0</v>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr"/>
+      <c r="M361" t="n">
+        <v>49</v>
+      </c>
+      <c r="N361" t="n">
+        <v>51</v>
+      </c>
+      <c r="O361" t="n">
+        <v>17</v>
+      </c>
+      <c r="P361" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>7</v>
+      </c>
+      <c r="R361" t="n">
+        <v>2</v>
+      </c>
+      <c r="S361" t="n">
+        <v>19</v>
+      </c>
+      <c r="T361" t="n">
+        <v>8</v>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>WfXv1DCa</t>
+        </is>
+      </c>
+      <c r="W361" t="n">
+        <v>48</v>
+      </c>
+      <c r="X361" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y361" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z361" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA361" t="inlineStr"/>
+      <c r="AB361" t="inlineStr"/>
+      <c r="AC361" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="AD361" t="inlineStr"/>
+      <c r="AE361" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF361" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="AG361" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH361" t="n">
+        <v>67.77777777777777</v>
+      </c>
+      <c r="AI361" t="n">
+        <v>1811111.111111111</v>
+      </c>
+      <c r="AJ361" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AK361" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AL361" t="n">
+        <v>182.8888888888889</v>
+      </c>
+      <c r="AM361" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN361" t="n">
+        <v>66.11111111111111</v>
+      </c>
+      <c r="AO361" t="n">
+        <v>1452777.777777778</v>
+      </c>
+      <c r="AP361" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="AQ361" t="n">
+        <v>23.44444444444444</v>
+      </c>
+      <c r="AR361" t="n">
+        <v>183.2222222222222</v>
+      </c>
+      <c r="AS361" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT361" t="n">
+        <v>68.88888888888889</v>
+      </c>
+      <c r="AU361" t="n">
+        <v>2077777.777777778</v>
+      </c>
+      <c r="AV361" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="AW361" t="n">
+        <v>23.94444444444444</v>
+      </c>
+      <c r="AX361" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="AY361" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ361" t="n">
+        <v>67.38888888888889</v>
+      </c>
+      <c r="BA361" t="n">
+        <v>1938888.888888889</v>
+      </c>
+      <c r="BB361" t="n">
+        <v>72.88888888888889</v>
+      </c>
+      <c r="BC361" t="inlineStr"/>
+      <c r="BD361" t="inlineStr"/>
+      <c r="BE361" t="inlineStr"/>
+      <c r="BF361" t="inlineStr"/>
+      <c r="BG361" t="inlineStr"/>
+      <c r="BH361" t="inlineStr"/>
+      <c r="BI361" t="inlineStr"/>
+      <c r="BJ361" t="inlineStr"/>
+      <c r="BK361" t="inlineStr"/>
+      <c r="BL361" t="inlineStr"/>
+      <c r="BM361" t="inlineStr"/>
+      <c r="BN361" t="inlineStr"/>
+      <c r="BO361" t="inlineStr"/>
+      <c r="BP361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>rRQ6H30k</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="n">
+        <v>45531.63541666666</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riverside stadium
+  middlesbrough </t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>34742</v>
+      </c>
+      <c r="F362" t="n">
+        <v>17408</v>
+      </c>
+      <c r="G362" t="n">
+        <v>0</v>
+      </c>
+      <c r="H362" t="n">
+        <v>5</v>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>6F0lvLNC</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="n">
+        <v>63</v>
+      </c>
+      <c r="N362" t="n">
+        <v>37</v>
+      </c>
+      <c r="O362" t="n">
+        <v>15</v>
+      </c>
+      <c r="P362" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>3</v>
+      </c>
+      <c r="R362" t="n">
+        <v>5</v>
+      </c>
+      <c r="S362" t="n">
+        <v>5</v>
+      </c>
+      <c r="T362" t="n">
+        <v>8</v>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="W362" t="n">
+        <v>48</v>
+      </c>
+      <c r="X362" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y362" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z362" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA362" t="inlineStr"/>
+      <c r="AB362" t="inlineStr"/>
+      <c r="AC362" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="AD362" t="inlineStr"/>
+      <c r="AE362" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="AF362" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AG362" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AH362" t="n">
+        <v>63.125</v>
+      </c>
+      <c r="AI362" t="n">
+        <v>1197500</v>
+      </c>
+      <c r="AJ362" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AK362" t="n">
+        <v>20.125</v>
+      </c>
+      <c r="AL362" t="n">
+        <v>183.375</v>
+      </c>
+      <c r="AM362" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN362" t="n">
+        <v>65.125</v>
+      </c>
+      <c r="AO362" t="n">
+        <v>1665625</v>
+      </c>
+      <c r="AP362" t="n">
+        <v>76.875</v>
+      </c>
+      <c r="AQ362" t="n">
+        <v>22.88888888888889</v>
+      </c>
+      <c r="AR362" t="n">
+        <v>179.9444444444445</v>
+      </c>
+      <c r="AS362" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AT362" t="n">
+        <v>66.77777777777777</v>
+      </c>
+      <c r="AU362" t="n">
+        <v>1940555.555555556</v>
+      </c>
+      <c r="AV362" t="n">
+        <v>74.72222222222223</v>
+      </c>
+      <c r="AW362" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="AX362" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="AY362" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ362" t="n">
+        <v>67.6875</v>
+      </c>
+      <c r="BA362" t="n">
+        <v>2094375</v>
+      </c>
+      <c r="BB362" t="n">
+        <v>73.8125</v>
+      </c>
+      <c r="BC362" t="inlineStr"/>
+      <c r="BD362" t="inlineStr"/>
+      <c r="BE362" t="inlineStr"/>
+      <c r="BF362" t="inlineStr"/>
+      <c r="BG362" t="inlineStr"/>
+      <c r="BH362" t="inlineStr"/>
+      <c r="BI362" t="inlineStr"/>
+      <c r="BJ362" t="inlineStr"/>
+      <c r="BK362" t="inlineStr"/>
+      <c r="BL362" t="inlineStr"/>
+      <c r="BM362" t="inlineStr"/>
+      <c r="BN362" t="inlineStr"/>
+      <c r="BO362" t="inlineStr"/>
+      <c r="BP362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>YqcO2yDl</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="n">
+        <v>45534.66666666666</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kenilworth road
+  luton </t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>12300</v>
+      </c>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="n">
+        <v>1</v>
+      </c>
+      <c r="H363" t="n">
+        <v>2</v>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr"/>
+      <c r="M363" t="n">
+        <v>59</v>
+      </c>
+      <c r="N363" t="n">
+        <v>41</v>
+      </c>
+      <c r="O363" t="n">
+        <v>13</v>
+      </c>
+      <c r="P363" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>5</v>
+      </c>
+      <c r="R363" t="n">
+        <v>4</v>
+      </c>
+      <c r="S363" t="n">
+        <v>14</v>
+      </c>
+      <c r="T363" t="n">
+        <v>11</v>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="W363" t="n">
+        <v>48</v>
+      </c>
+      <c r="X363" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y363" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z363" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA363" t="inlineStr"/>
+      <c r="AB363" t="inlineStr"/>
+      <c r="AC363" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="AD363" t="inlineStr"/>
+      <c r="AE363" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="AF363" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AG363" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH363" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AI363" t="n">
+        <v>2481818.181818182</v>
+      </c>
+      <c r="AJ363" t="n">
+        <v>74.27272727272727</v>
+      </c>
+      <c r="AK363" t="inlineStr"/>
+      <c r="AL363" t="inlineStr"/>
+      <c r="AM363" t="inlineStr"/>
+      <c r="AN363" t="inlineStr"/>
+      <c r="AO363" t="inlineStr"/>
+      <c r="AP363" t="inlineStr"/>
+      <c r="AQ363" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AR363" t="n">
+        <v>181.625</v>
+      </c>
+      <c r="AS363" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT363" t="n">
+        <v>67.6875</v>
+      </c>
+      <c r="AU363" t="n">
+        <v>2273437.5</v>
+      </c>
+      <c r="AV363" t="n">
+        <v>74.4375</v>
+      </c>
+      <c r="AW363" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AX363" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="AY363" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ363" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="BA363" t="n">
+        <v>1292500</v>
+      </c>
+      <c r="BB363" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="BC363" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BD363" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="BE363" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF363" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG363" t="n">
+        <v>213</v>
+      </c>
+      <c r="BH363" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="BI363" t="n">
+        <v>221</v>
+      </c>
+      <c r="BJ363" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK363" t="n">
+        <v>171</v>
+      </c>
+      <c r="BL363" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM363" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN363" t="n">
+        <v>73</v>
+      </c>
+      <c r="BO363" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="BP363" t="n">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/england/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP490"/>
+  <dimension ref="A1:BP495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89072,6 +89072,968 @@
         <v>217</v>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>75635</v>
+      </c>
+      <c r="F491" t="n">
+        <v>73738</v>
+      </c>
+      <c r="G491" t="n">
+        <v>0</v>
+      </c>
+      <c r="H491" t="n">
+        <v>3</v>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="K491" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L491" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M491" t="n">
+        <v>53</v>
+      </c>
+      <c r="N491" t="n">
+        <v>47</v>
+      </c>
+      <c r="O491" t="n">
+        <v>8</v>
+      </c>
+      <c r="P491" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>3</v>
+      </c>
+      <c r="R491" t="n">
+        <v>3</v>
+      </c>
+      <c r="S491" t="n">
+        <v>7</v>
+      </c>
+      <c r="T491" t="n">
+        <v>7</v>
+      </c>
+      <c r="U491" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="V491" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="W491" t="n">
+        <v>48</v>
+      </c>
+      <c r="X491" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y491" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z491" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA491" t="inlineStr"/>
+      <c r="AB491" t="inlineStr"/>
+      <c r="AC491" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="AD491" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="AE491" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="AF491" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="AG491" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH491" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AI491" t="n">
+        <v>38062500</v>
+      </c>
+      <c r="AJ491" t="n">
+        <v>85.75</v>
+      </c>
+      <c r="AK491" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AL491" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AM491" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN491" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="AO491" t="n">
+        <v>59500000</v>
+      </c>
+      <c r="AP491" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="AQ491" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AR491" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="AS491" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT491" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AU491" t="n">
+        <v>11921000</v>
+      </c>
+      <c r="AV491" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AW491" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="AX491" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="AY491" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ491" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="BA491" t="n">
+        <v>30565000</v>
+      </c>
+      <c r="BB491" t="n">
+        <v>83.65000000000001</v>
+      </c>
+      <c r="BC491" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="BD491" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="BE491" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF491" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG491" t="n">
+        <v>396</v>
+      </c>
+      <c r="BH491" t="n">
+        <v>120500000</v>
+      </c>
+      <c r="BI491" t="n">
+        <v>416</v>
+      </c>
+      <c r="BJ491" t="n">
+        <v>22</v>
+      </c>
+      <c r="BK491" t="n">
+        <v>185</v>
+      </c>
+      <c r="BL491" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM491" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN491" t="n">
+        <v>79</v>
+      </c>
+      <c r="BO491" t="n">
+        <v>25500000</v>
+      </c>
+      <c r="BP491" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>tvOWhxZH</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="n">
+        <v>45536.39583333334</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F492" t="n">
+        <v>39298</v>
+      </c>
+      <c r="G492" t="n">
+        <v>1</v>
+      </c>
+      <c r="H492" t="n">
+        <v>1</v>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="K492" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="L492" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M492" t="n">
+        <v>63</v>
+      </c>
+      <c r="N492" t="n">
+        <v>37</v>
+      </c>
+      <c r="O492" t="n">
+        <v>13</v>
+      </c>
+      <c r="P492" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q492" t="n">
+        <v>7</v>
+      </c>
+      <c r="R492" t="n">
+        <v>3</v>
+      </c>
+      <c r="S492" t="n">
+        <v>9</v>
+      </c>
+      <c r="T492" t="n">
+        <v>13</v>
+      </c>
+      <c r="U492" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="V492" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="W492" t="n">
+        <v>48</v>
+      </c>
+      <c r="X492" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y492" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z492" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA492" t="inlineStr"/>
+      <c r="AB492" t="inlineStr"/>
+      <c r="AC492" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="AD492" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="AE492" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF492" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="AG492" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH492" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="AI492" t="n">
+        <v>24400000</v>
+      </c>
+      <c r="AJ492" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="AK492" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AL492" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AM492" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN492" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AO492" t="n">
+        <v>12530000</v>
+      </c>
+      <c r="AP492" t="n">
+        <v>80</v>
+      </c>
+      <c r="AQ492" t="n">
+        <v>23.16666666666667</v>
+      </c>
+      <c r="AR492" t="n">
+        <v>180.1666666666667</v>
+      </c>
+      <c r="AS492" t="n">
+        <v>1.583333333333333</v>
+      </c>
+      <c r="AT492" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AU492" t="n">
+        <v>30866666.66666667</v>
+      </c>
+      <c r="AV492" t="n">
+        <v>83.91666666666667</v>
+      </c>
+      <c r="AW492" t="n">
+        <v>26.63636363636364</v>
+      </c>
+      <c r="AX492" t="n">
+        <v>183.3636363636364</v>
+      </c>
+      <c r="AY492" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ492" t="n">
+        <v>72.54545454545455</v>
+      </c>
+      <c r="BA492" t="n">
+        <v>8704545.454545455</v>
+      </c>
+      <c r="BB492" t="n">
+        <v>75.54545454545455</v>
+      </c>
+      <c r="BC492" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD492" t="n">
+        <v>181</v>
+      </c>
+      <c r="BE492" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF492" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG492" t="n">
+        <v>73</v>
+      </c>
+      <c r="BH492" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="BI492" t="n">
+        <v>86</v>
+      </c>
+      <c r="BJ492" t="inlineStr"/>
+      <c r="BK492" t="inlineStr"/>
+      <c r="BL492" t="inlineStr"/>
+      <c r="BM492" t="inlineStr"/>
+      <c r="BN492" t="inlineStr"/>
+      <c r="BO492" t="inlineStr"/>
+      <c r="BP492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="n">
+        <v>45536.39583333334</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>52305</v>
+      </c>
+      <c r="F493" t="n">
+        <v>52211</v>
+      </c>
+      <c r="G493" t="n">
+        <v>2</v>
+      </c>
+      <c r="H493" t="n">
+        <v>1</v>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="K493" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L493" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M493" t="n">
+        <v>34</v>
+      </c>
+      <c r="N493" t="n">
+        <v>66</v>
+      </c>
+      <c r="O493" t="n">
+        <v>9</v>
+      </c>
+      <c r="P493" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>3</v>
+      </c>
+      <c r="R493" t="n">
+        <v>6</v>
+      </c>
+      <c r="S493" t="n">
+        <v>16</v>
+      </c>
+      <c r="T493" t="n">
+        <v>13</v>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="W493" t="n">
+        <v>48</v>
+      </c>
+      <c r="X493" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y493" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z493" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA493" t="inlineStr"/>
+      <c r="AB493" t="inlineStr"/>
+      <c r="AC493" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="AD493" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="AE493" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF493" t="n">
+        <v>187.9</v>
+      </c>
+      <c r="AG493" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH493" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="AI493" t="n">
+        <v>24080000</v>
+      </c>
+      <c r="AJ493" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="AK493" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AL493" t="n">
+        <v>183.875</v>
+      </c>
+      <c r="AM493" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="AN493" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="AO493" t="n">
+        <v>39537500</v>
+      </c>
+      <c r="AP493" t="n">
+        <v>85</v>
+      </c>
+      <c r="AQ493" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AR493" t="n">
+        <v>180.55</v>
+      </c>
+      <c r="AS493" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT493" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AU493" t="n">
+        <v>23025000</v>
+      </c>
+      <c r="AV493" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="AW493" t="n">
+        <v>23.94117647058824</v>
+      </c>
+      <c r="AX493" t="n">
+        <v>183</v>
+      </c>
+      <c r="AY493" t="n">
+        <v>1.705882352941176</v>
+      </c>
+      <c r="AZ493" t="n">
+        <v>77.17647058823529</v>
+      </c>
+      <c r="BA493" t="n">
+        <v>21269117.64705882</v>
+      </c>
+      <c r="BB493" t="n">
+        <v>82.58823529411765</v>
+      </c>
+      <c r="BC493" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="BD493" t="n">
+        <v>187.6</v>
+      </c>
+      <c r="BE493" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF493" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG493" t="n">
+        <v>393</v>
+      </c>
+      <c r="BH493" t="n">
+        <v>103600000</v>
+      </c>
+      <c r="BI493" t="n">
+        <v>412</v>
+      </c>
+      <c r="BJ493" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BK493" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BL493" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM493" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN493" t="n">
+        <v>158</v>
+      </c>
+      <c r="BO493" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="BP493" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>SWRIzxdS</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="n">
+        <v>45536.41666666666</v>
+      </c>
+      <c r="C494" t="inlineStr"/>
+      <c r="D494" t="inlineStr"/>
+      <c r="E494" t="inlineStr"/>
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="n">
+        <v>1</v>
+      </c>
+      <c r="H494" t="n">
+        <v>2</v>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>KY3WutAL</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>Io6VnVE8</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr"/>
+      <c r="L494" t="inlineStr"/>
+      <c r="M494" t="inlineStr"/>
+      <c r="N494" t="inlineStr"/>
+      <c r="O494" t="inlineStr"/>
+      <c r="P494" t="inlineStr"/>
+      <c r="Q494" t="inlineStr"/>
+      <c r="R494" t="inlineStr"/>
+      <c r="S494" t="inlineStr"/>
+      <c r="T494" t="inlineStr"/>
+      <c r="U494" t="inlineStr"/>
+      <c r="V494" t="inlineStr"/>
+      <c r="W494" t="n">
+        <v>48</v>
+      </c>
+      <c r="X494" t="n">
+        <v>483</v>
+      </c>
+      <c r="Y494" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z494" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA494" t="inlineStr"/>
+      <c r="AB494" t="inlineStr"/>
+      <c r="AC494" t="inlineStr"/>
+      <c r="AD494" t="inlineStr"/>
+      <c r="AE494" t="inlineStr"/>
+      <c r="AF494" t="inlineStr"/>
+      <c r="AG494" t="inlineStr"/>
+      <c r="AH494" t="inlineStr"/>
+      <c r="AI494" t="inlineStr"/>
+      <c r="AJ494" t="inlineStr"/>
+      <c r="AK494" t="inlineStr"/>
+      <c r="AL494" t="inlineStr"/>
+      <c r="AM494" t="inlineStr"/>
+      <c r="AN494" t="inlineStr"/>
+      <c r="AO494" t="inlineStr"/>
+      <c r="AP494" t="inlineStr"/>
+      <c r="AQ494" t="inlineStr"/>
+      <c r="AR494" t="inlineStr"/>
+      <c r="AS494" t="inlineStr"/>
+      <c r="AT494" t="inlineStr"/>
+      <c r="AU494" t="inlineStr"/>
+      <c r="AV494" t="inlineStr"/>
+      <c r="AW494" t="inlineStr"/>
+      <c r="AX494" t="inlineStr"/>
+      <c r="AY494" t="inlineStr"/>
+      <c r="AZ494" t="inlineStr"/>
+      <c r="BA494" t="inlineStr"/>
+      <c r="BB494" t="inlineStr"/>
+      <c r="BC494" t="inlineStr"/>
+      <c r="BD494" t="inlineStr"/>
+      <c r="BE494" t="inlineStr"/>
+      <c r="BF494" t="inlineStr"/>
+      <c r="BG494" t="inlineStr"/>
+      <c r="BH494" t="inlineStr"/>
+      <c r="BI494" t="inlineStr"/>
+      <c r="BJ494" t="inlineStr"/>
+      <c r="BK494" t="inlineStr"/>
+      <c r="BL494" t="inlineStr"/>
+      <c r="BM494" t="inlineStr"/>
+      <c r="BN494" t="inlineStr"/>
+      <c r="BO494" t="inlineStr"/>
+      <c r="BP494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>KGmbFEdf</t>
+        </is>
+      </c>
+      <c r="B495" s="2" t="n">
+        <v>45536.45833333334</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kitchen a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bramall lane
+  sheffield </t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>32050</v>
+      </c>
+      <c r="F495" t="n">
+        <v>26914</v>
+      </c>
+      <c r="G495" t="n">
+        <v>1</v>
+      </c>
+      <c r="H495" t="n">
+        <v>0</v>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr"/>
+      <c r="L495" t="inlineStr"/>
+      <c r="M495" t="n">
+        <v>50</v>
+      </c>
+      <c r="N495" t="n">
+        <v>50</v>
+      </c>
+      <c r="O495" t="n">
+        <v>20</v>
+      </c>
+      <c r="P495" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>7</v>
+      </c>
+      <c r="R495" t="n">
+        <v>1</v>
+      </c>
+      <c r="S495" t="n">
+        <v>16</v>
+      </c>
+      <c r="T495" t="n">
+        <v>14</v>
+      </c>
+      <c r="U495" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="V495" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="W495" t="n">
+        <v>48</v>
+      </c>
+      <c r="X495" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y495" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z495" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA495" t="inlineStr"/>
+      <c r="AB495" t="inlineStr"/>
+      <c r="AC495" t="inlineStr"/>
+      <c r="AD495" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="AE495" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AF495" t="n">
+        <v>184</v>
+      </c>
+      <c r="AG495" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH495" t="n">
+        <v>70.77777777777777</v>
+      </c>
+      <c r="AI495" t="n">
+        <v>3877777.777777778</v>
+      </c>
+      <c r="AJ495" t="n">
+        <v>77.66666666666667</v>
+      </c>
+      <c r="AK495" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AL495" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="AM495" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN495" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="AO495" t="n">
+        <v>1788888.888888889</v>
+      </c>
+      <c r="AP495" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="AQ495" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="AR495" t="n">
+        <v>178.1333333333333</v>
+      </c>
+      <c r="AS495" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT495" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="AU495" t="n">
+        <v>2356666.666666667</v>
+      </c>
+      <c r="AV495" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AW495" t="n">
+        <v>24.22222222222222</v>
+      </c>
+      <c r="AX495" t="n">
+        <v>183.1111111111111</v>
+      </c>
+      <c r="AY495" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ495" t="n">
+        <v>66.94444444444444</v>
+      </c>
+      <c r="BA495" t="n">
+        <v>1533333.333333333</v>
+      </c>
+      <c r="BB495" t="n">
+        <v>73</v>
+      </c>
+      <c r="BC495" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD495" t="n">
+        <v>183</v>
+      </c>
+      <c r="BE495" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF495" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG495" t="n">
+        <v>60</v>
+      </c>
+      <c r="BH495" t="n">
+        <v>525000</v>
+      </c>
+      <c r="BI495" t="n">
+        <v>71</v>
+      </c>
+      <c r="BJ495" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK495" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL495" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM495" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN495" t="n">
+        <v>73</v>
+      </c>
+      <c r="BO495" t="n">
+        <v>4100000</v>
+      </c>
+      <c r="BP495" t="n">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
